--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1995" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8663EE-3A00-4C15-91FE-6CC9FCBB3301}"/>
+  <xr:revisionPtr revIDLastSave="1998" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F82749D2-BFDB-456B-BCE3-96167605ED29}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="5" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -22707,7 +22707,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0EC0B64-C2CB-4C70-B5D8-D555B967CBAD}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0EC0B64-C2CB-4C70-B5D8-D555B967CBAD}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:C36" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -22927,7 +22927,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76983AB9-3760-4F7C-9E77-6BC7D4A5EEB7}" name="TablaDinámica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76983AB9-3760-4F7C-9E77-6BC7D4A5EEB7}" name="TablaDinámica5" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -51277,6 +51277,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:U510" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
@@ -53317,7 +53318,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="28">
         <v>210</v>
       </c>
@@ -53597,7 +53598,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28">
         <v>233</v>
       </c>
@@ -53863,7 +53864,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="28">
         <v>253</v>
       </c>
@@ -53905,7 +53906,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="28">
         <v>256</v>
       </c>
@@ -53919,7 +53920,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="28">
         <v>257</v>
       </c>
@@ -54451,7 +54452,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="28">
         <v>296</v>
       </c>
@@ -54465,7 +54466,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="28">
         <v>297</v>
       </c>
@@ -54479,7 +54480,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="28">
         <v>298</v>
       </c>
@@ -54591,7 +54592,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="28">
         <v>307</v>
       </c>
@@ -54675,7 +54676,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="28">
         <v>313</v>
       </c>
@@ -54689,7 +54690,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="28">
         <v>314</v>
       </c>
@@ -54703,7 +54704,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="28">
         <v>315</v>
       </c>
@@ -54717,7 +54718,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="28">
         <v>316</v>
       </c>
@@ -54731,7 +54732,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="28">
         <v>317</v>
       </c>
@@ -54745,7 +54746,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="28">
         <v>318</v>
       </c>
@@ -54759,7 +54760,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="28">
         <v>319</v>
       </c>
@@ -54773,7 +54774,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="28">
         <v>320</v>
       </c>
@@ -54787,7 +54788,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="28">
         <v>321</v>
       </c>
@@ -54871,7 +54872,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="28">
         <v>328</v>
       </c>
@@ -54955,7 +54956,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="28">
         <v>336</v>
       </c>
@@ -55039,7 +55040,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="28">
         <v>344</v>
       </c>
@@ -55109,7 +55110,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="28">
         <v>349</v>
       </c>
@@ -55123,7 +55124,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="28">
         <v>350</v>
       </c>
@@ -55305,7 +55306,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="28">
         <v>363</v>
       </c>
@@ -55319,7 +55320,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="28">
         <v>364</v>
       </c>
@@ -55389,7 +55390,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="28">
         <v>369</v>
       </c>
@@ -55515,7 +55516,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="28">
         <v>378</v>
       </c>
@@ -55697,7 +55698,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="28">
         <v>391</v>
       </c>
@@ -55739,7 +55740,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="28">
         <v>394</v>
       </c>
@@ -55753,7 +55754,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="28">
         <v>395</v>
       </c>
@@ -55767,7 +55768,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="28">
         <v>396</v>
       </c>
@@ -55795,7 +55796,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="28">
         <v>398</v>
       </c>
@@ -55809,7 +55810,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="28">
         <v>399</v>
       </c>
@@ -55823,7 +55824,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="28">
         <v>400</v>
       </c>
@@ -55837,7 +55838,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="28">
         <v>401</v>
       </c>
@@ -55851,7 +55852,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="28">
         <v>402</v>
       </c>
@@ -55977,7 +55978,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="28">
         <v>411</v>
       </c>
@@ -55991,7 +55992,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="28">
         <v>412</v>
       </c>
@@ -56005,7 +56006,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="28">
         <v>413</v>
       </c>
@@ -56117,7 +56118,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="28">
         <v>421</v>
       </c>
@@ -56131,7 +56132,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="28">
         <v>422</v>
       </c>
@@ -56145,7 +56146,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="28">
         <v>423</v>
       </c>
@@ -56159,7 +56160,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="28">
         <v>424</v>
       </c>
@@ -56173,7 +56174,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="28">
         <v>425</v>
       </c>
@@ -56383,7 +56384,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="28">
         <v>11</v>
       </c>
@@ -56509,7 +56510,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="28">
         <v>20</v>
       </c>
@@ -56943,7 +56944,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="28">
         <v>51</v>
       </c>
@@ -56957,7 +56958,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="28">
         <v>52</v>
       </c>
@@ -57279,7 +57280,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="28">
         <v>96</v>
       </c>
@@ -57293,7 +57294,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="28" t="s">
         <v>548</v>
       </c>
@@ -57307,7 +57308,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="28" t="s">
         <v>551</v>
       </c>
@@ -57321,7 +57322,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="28" t="s">
         <v>553</v>
       </c>
@@ -57335,7 +57336,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="28" t="s">
         <v>555</v>
       </c>
@@ -57391,7 +57392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="28" t="s">
         <v>563</v>
       </c>
@@ -57405,7 +57406,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="28" t="s">
         <v>565</v>
       </c>
@@ -57419,7 +57420,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="28" t="s">
         <v>567</v>
       </c>
@@ -57433,7 +57434,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="28" t="s">
         <v>569</v>
       </c>
@@ -57447,7 +57448,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="28" t="s">
         <v>571</v>
       </c>
@@ -57475,7 +57476,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="28" t="s">
         <v>575</v>
       </c>
@@ -57503,7 +57504,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="28" t="s">
         <v>579</v>
       </c>
@@ -57517,7 +57518,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="28" t="s">
         <v>581</v>
       </c>
@@ -57531,7 +57532,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="28" t="s">
         <v>583</v>
       </c>
@@ -57545,7 +57546,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="28" t="s">
         <v>585</v>
       </c>
@@ -57559,7 +57560,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="28" t="s">
         <v>587</v>
       </c>
@@ -57601,7 +57602,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="28" t="s">
         <v>593</v>
       </c>
@@ -58133,7 +58134,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="28" t="s">
         <v>657</v>
       </c>
@@ -58189,7 +58190,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="28">
         <v>440</v>
       </c>
@@ -58273,7 +58274,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="28">
         <v>444</v>
       </c>
@@ -58371,7 +58372,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="28">
         <v>451</v>
       </c>
@@ -58511,7 +58512,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="28">
         <v>462</v>
       </c>
@@ -58553,7 +58554,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="28">
         <v>465</v>
       </c>
@@ -58595,7 +58596,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="28">
         <v>468</v>
       </c>
@@ -58623,7 +58624,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="28">
         <v>470</v>
       </c>
@@ -58693,7 +58694,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="28">
         <v>902</v>
       </c>
@@ -58721,7 +58722,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="28">
         <v>904</v>
       </c>
@@ -58749,7 +58750,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="28">
         <v>906</v>
       </c>
@@ -58763,7 +58764,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="28">
         <v>907</v>
       </c>
@@ -58889,7 +58890,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="28" t="s">
         <v>723</v>
       </c>
@@ -59042,15 +59043,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
@@ -59059,6 +59051,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59297,20 +59298,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
     <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Indicadores_Oportunidad_Mejora/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1998" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F82749D2-BFDB-456B-BCE3-96167605ED29}"/>
+  <xr:revisionPtr revIDLastSave="2046" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{784D4C14-E1B9-4A6B-8617-56A26CE899E1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja4" sheetId="5" r:id="rId1"/>
@@ -26,8 +26,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
-    <pivotCache cacheId="5" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6662" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7138" uniqueCount="1017">
   <si>
     <t>Linea</t>
   </si>
@@ -3557,6 +3557,189 @@
   </si>
   <si>
     <t>Pricing</t>
+  </si>
+  <si>
+    <t>Número Impactados Talleres de formación</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Gestión de proyectos</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Gestión Jurídica Y Normativa</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Administración De Servicios Generales</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Planeación Financiera</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Datos y analítica</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Servicio de Salud</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Gestión, evaluación e innovación curricular</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Formación para la investigación, creación e innovación</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Gestión de Unidades Académicas</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - LEI</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Mercadeo de programas académicos</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Diseño y contenido virtual</t>
+  </si>
+  <si>
+    <t>Asignaturas o modulos con mecanismos de evaluación implementados</t>
+  </si>
+  <si>
+    <t>Participación de Grupos de Interés en la construcción del nuevo plan de desarrollo (PDI)</t>
+  </si>
+  <si>
+    <t>Participación de la comunidad en la Rendición de Cuentas</t>
+  </si>
+  <si>
+    <t>Participación de graduados en actividades de empleabilidad y relacionamiento</t>
+  </si>
+  <si>
+    <t>Tasa de cotización del graduado - Metrica</t>
+  </si>
+  <si>
+    <t>Tasa de participación de graduados en instrumentos de seguimiento (M0, M1, M5)</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción del graduado con la institución</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Gestión de la Responsabilidad Social</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Inscripción, admisión y matrícula de estudiantes nuevos</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan de formación Institucional</t>
+  </si>
+  <si>
+    <t>Oportunidad en el cierre de acciones</t>
+  </si>
+  <si>
+    <t>Oportunidad en el cierre de actividades de los planes de mejora</t>
+  </si>
+  <si>
+    <t>Cumplimiento a cronograma de proyectos 2025</t>
+  </si>
+  <si>
+    <t>Número de renovaciones de registro calificado radicadas al MEN</t>
+  </si>
+  <si>
+    <t>Programas con planes de estudios definidos por escuela (Programas Renovación, modificación y acreditación)</t>
+  </si>
+  <si>
+    <t>Programas con planes de estudios definidos por escuela (Mantenimiento de programas)</t>
+  </si>
+  <si>
+    <t>Programas con resultados de aprendizaje definidos por escuela (Nuevos Programas)</t>
+  </si>
+  <si>
+    <t>Programas con resultados de aprendizaje definidos por escuela (Programas Renovación, modificación y acreditación)</t>
+  </si>
+  <si>
+    <t>Solicitudes de documentación completadas</t>
+  </si>
+  <si>
+    <t>Número de visitas a la página web</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Cultura y Deporte</t>
+  </si>
+  <si>
+    <t>Respuesta ante nuevas necesidades de control</t>
+  </si>
+  <si>
+    <t>Porcentaje de procesos de control implementados</t>
+  </si>
+  <si>
+    <t>Porcentaje de colaboradores formados en ciberseguridad</t>
+  </si>
+  <si>
+    <t>% de publicaciones con sentimiento neutro o negativo</t>
+  </si>
+  <si>
+    <t>Índice de Cumplimiento del Sprint</t>
+  </si>
+  <si>
+    <t>Eficiencia de capacidad instalada</t>
+  </si>
+  <si>
+    <t>Actividades de Cooperación en Internacionalización</t>
+  </si>
+  <si>
+    <t>Participación de estudiantes externos invitados a actividades de cooperación nacional e internacional</t>
+  </si>
+  <si>
+    <t>Participación de estudiantes POLI en actividades de cooperación nacional e internacional</t>
+  </si>
+  <si>
+    <t>Participación de profesores externos invitados a actividades de cooperación nacional e internacional</t>
+  </si>
+  <si>
+    <t>Participación de profesores POLI en actividades de cooperación nacional e internacional</t>
+  </si>
+  <si>
+    <t>FCR- Resolución en primer contacto</t>
+  </si>
+  <si>
+    <t>Cumplimiento de sesiones de socialización de planeación académica</t>
+  </si>
+  <si>
+    <t>CES emisión de certificados</t>
+  </si>
+  <si>
+    <t>Nivel de Calidad de los Datos Cargados al SNIES</t>
+  </si>
+  <si>
+    <t>Tasa de interacción por usuario</t>
+  </si>
+  <si>
+    <t>Producción de ambientes inmersivos LEI</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción con las actividades de formación</t>
+  </si>
+  <si>
+    <t>Evaluación del desempeño de los mentores</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Permanencia</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados -Mercadeo y venta de educación para la vida</t>
+  </si>
+  <si>
+    <t>Frecuencia de incidentes de riesgos</t>
+  </si>
+  <si>
+    <t>Eficacia de controles</t>
+  </si>
+  <si>
+    <t>Nivel de cumplimiento del plan de seguimiento a controles</t>
+  </si>
+  <si>
+    <t>Cumplimiento Politica Polisigs</t>
+  </si>
+  <si>
+    <t>Oportunidad en la solución de solicitudes de infraestructura</t>
+  </si>
+  <si>
+    <t>Gestión de Unidades Académicas</t>
   </si>
 </sst>
 </file>
@@ -22707,7 +22890,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0EC0B64-C2CB-4C70-B5D8-D555B967CBAD}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0EC0B64-C2CB-4C70-B5D8-D555B967CBAD}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:C36" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="19">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -22927,7 +23110,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76983AB9-3760-4F7C-9E77-6BC7D4A5EEB7}" name="TablaDinámica5" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76983AB9-3760-4F7C-9E77-6BC7D4A5EEB7}" name="TablaDinámica5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -23797,7 +23980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U510"/>
+  <dimension ref="A1:U578"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -51275,9 +51458,2864 @@
         <v>1</v>
       </c>
     </row>
+    <row r="511" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A511" s="33">
+        <v>487</v>
+      </c>
+      <c r="B511" s="33" t="s">
+        <v>956</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D511" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E511" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F511" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G511" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H511" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I511" s="5"/>
+      <c r="J511" s="5"/>
+      <c r="K511" s="5"/>
+      <c r="L511" s="5"/>
+      <c r="M511" s="5"/>
+      <c r="N511" s="5"/>
+      <c r="O511" s="5">
+        <v>1</v>
+      </c>
+      <c r="P511" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q511" s="5"/>
+      <c r="R511" s="5"/>
+      <c r="S511" s="5"/>
+      <c r="T511" s="35"/>
+    </row>
+    <row r="512" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A512" s="33">
+        <v>490</v>
+      </c>
+      <c r="B512" s="33" t="s">
+        <v>632</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D512" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E512" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F512" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G512" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H512" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I512" s="5"/>
+      <c r="J512" s="5"/>
+      <c r="K512" s="5"/>
+      <c r="L512" s="5"/>
+      <c r="M512" s="5"/>
+      <c r="N512" s="5"/>
+      <c r="O512" s="5">
+        <v>1</v>
+      </c>
+      <c r="P512" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q512" s="5"/>
+      <c r="R512" s="5"/>
+      <c r="S512" s="5"/>
+      <c r="T512" s="35"/>
+    </row>
+    <row r="513" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A513" s="33">
+        <v>491</v>
+      </c>
+      <c r="B513" s="33" t="s">
+        <v>957</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D513" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E513" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F513" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G513" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H513" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I513" s="5"/>
+      <c r="J513" s="5"/>
+      <c r="K513" s="5"/>
+      <c r="L513" s="5"/>
+      <c r="M513" s="5"/>
+      <c r="N513" s="5"/>
+      <c r="O513" s="5">
+        <v>1</v>
+      </c>
+      <c r="P513" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q513" s="5"/>
+      <c r="R513" s="5"/>
+      <c r="S513" s="5"/>
+      <c r="T513" s="35"/>
+    </row>
+    <row r="514" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A514" s="33">
+        <v>492</v>
+      </c>
+      <c r="B514" s="33" t="s">
+        <v>651</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D514" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E514" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F514" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G514" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H514" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I514" s="5"/>
+      <c r="J514" s="5"/>
+      <c r="K514" s="5"/>
+      <c r="L514" s="5"/>
+      <c r="M514" s="5"/>
+      <c r="N514" s="5"/>
+      <c r="O514" s="5">
+        <v>1</v>
+      </c>
+      <c r="P514" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q514" s="5"/>
+      <c r="R514" s="5"/>
+      <c r="S514" s="5"/>
+      <c r="T514" s="35"/>
+    </row>
+    <row r="515" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A515" s="33">
+        <v>493</v>
+      </c>
+      <c r="B515" s="33" t="s">
+        <v>958</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D515" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="E515" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F515" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G515" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H515" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I515" s="5"/>
+      <c r="J515" s="5"/>
+      <c r="K515" s="5"/>
+      <c r="L515" s="5"/>
+      <c r="M515" s="5"/>
+      <c r="N515" s="5"/>
+      <c r="O515" s="5">
+        <v>1</v>
+      </c>
+      <c r="P515" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q515" s="5"/>
+      <c r="R515" s="5"/>
+      <c r="S515" s="5"/>
+      <c r="T515" s="35"/>
+    </row>
+    <row r="516" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A516" s="33">
+        <v>494</v>
+      </c>
+      <c r="B516" s="33" t="s">
+        <v>959</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D516" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="E516" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F516" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G516" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H516" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I516" s="5"/>
+      <c r="J516" s="5"/>
+      <c r="K516" s="5"/>
+      <c r="L516" s="5"/>
+      <c r="M516" s="5"/>
+      <c r="N516" s="5"/>
+      <c r="O516" s="5">
+        <v>1</v>
+      </c>
+      <c r="P516" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q516" s="5"/>
+      <c r="R516" s="5"/>
+      <c r="S516" s="5"/>
+      <c r="T516" s="35"/>
+    </row>
+    <row r="517" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A517" s="33">
+        <v>495</v>
+      </c>
+      <c r="B517" s="33" t="s">
+        <v>640</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D517" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="E517" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F517" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G517" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H517" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I517" s="5"/>
+      <c r="J517" s="5"/>
+      <c r="K517" s="5"/>
+      <c r="L517" s="5"/>
+      <c r="M517" s="5"/>
+      <c r="N517" s="5"/>
+      <c r="O517" s="5">
+        <v>1</v>
+      </c>
+      <c r="P517" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q517" s="5"/>
+      <c r="R517" s="5"/>
+      <c r="S517" s="5"/>
+      <c r="T517" s="35"/>
+    </row>
+    <row r="518" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A518" s="33">
+        <v>496</v>
+      </c>
+      <c r="B518" s="33" t="s">
+        <v>960</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D518" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E518" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F518" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G518" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H518" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I518" s="5"/>
+      <c r="J518" s="5"/>
+      <c r="K518" s="5"/>
+      <c r="L518" s="5"/>
+      <c r="M518" s="5"/>
+      <c r="N518" s="5"/>
+      <c r="O518" s="5">
+        <v>1</v>
+      </c>
+      <c r="P518" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q518" s="5"/>
+      <c r="R518" s="5"/>
+      <c r="S518" s="5"/>
+      <c r="T518" s="35"/>
+    </row>
+    <row r="519" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A519" s="33">
+        <v>498</v>
+      </c>
+      <c r="B519" s="33" t="s">
+        <v>649</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D519" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E519" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G519" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H519" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I519" s="5"/>
+      <c r="J519" s="5"/>
+      <c r="K519" s="5"/>
+      <c r="L519" s="5"/>
+      <c r="M519" s="5"/>
+      <c r="N519" s="5"/>
+      <c r="O519" s="5">
+        <v>1</v>
+      </c>
+      <c r="P519" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q519" s="5"/>
+      <c r="R519" s="5"/>
+      <c r="S519" s="5"/>
+      <c r="T519" s="35"/>
+    </row>
+    <row r="520" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A520" s="33">
+        <v>499</v>
+      </c>
+      <c r="B520" s="33" t="s">
+        <v>961</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D520" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="E520" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F520" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G520" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H520" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I520" s="5"/>
+      <c r="J520" s="5"/>
+      <c r="K520" s="5"/>
+      <c r="L520" s="5"/>
+      <c r="M520" s="5"/>
+      <c r="N520" s="5"/>
+      <c r="O520" s="5">
+        <v>1</v>
+      </c>
+      <c r="P520" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q520" s="5"/>
+      <c r="R520" s="5"/>
+      <c r="S520" s="5"/>
+      <c r="T520" s="35"/>
+    </row>
+    <row r="521" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A521" s="33">
+        <v>500</v>
+      </c>
+      <c r="B521" s="33" t="s">
+        <v>962</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D521" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="E521" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F521" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G521" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H521" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I521" s="5"/>
+      <c r="J521" s="5"/>
+      <c r="K521" s="5"/>
+      <c r="L521" s="5"/>
+      <c r="M521" s="5"/>
+      <c r="N521" s="5"/>
+      <c r="O521" s="5">
+        <v>1</v>
+      </c>
+      <c r="P521" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q521" s="5"/>
+      <c r="R521" s="5"/>
+      <c r="S521" s="5"/>
+      <c r="T521" s="35"/>
+    </row>
+    <row r="522" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A522" s="33">
+        <v>501</v>
+      </c>
+      <c r="B522" s="33" t="s">
+        <v>963</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D522" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E522" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F522" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G522" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H522" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I522" s="5"/>
+      <c r="J522" s="5"/>
+      <c r="K522" s="5"/>
+      <c r="L522" s="5"/>
+      <c r="M522" s="5"/>
+      <c r="N522" s="5"/>
+      <c r="O522" s="5">
+        <v>1</v>
+      </c>
+      <c r="P522" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q522" s="5"/>
+      <c r="R522" s="5"/>
+      <c r="S522" s="5"/>
+      <c r="T522" s="35"/>
+    </row>
+    <row r="523" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A523" s="33">
+        <v>502</v>
+      </c>
+      <c r="B523" s="33" t="s">
+        <v>964</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D523" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E523" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F523" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G523" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H523" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I523" s="5"/>
+      <c r="J523" s="5"/>
+      <c r="K523" s="5"/>
+      <c r="L523" s="5"/>
+      <c r="M523" s="5"/>
+      <c r="N523" s="5"/>
+      <c r="O523" s="5">
+        <v>1</v>
+      </c>
+      <c r="P523" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q523" s="5"/>
+      <c r="R523" s="5"/>
+      <c r="S523" s="5"/>
+      <c r="T523" s="35"/>
+    </row>
+    <row r="524" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A524" s="33">
+        <v>503</v>
+      </c>
+      <c r="B524" s="33" t="s">
+        <v>965</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D524" s="33" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E524" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F524" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G524" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H524" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I524" s="5"/>
+      <c r="J524" s="5"/>
+      <c r="K524" s="5"/>
+      <c r="L524" s="5"/>
+      <c r="M524" s="5"/>
+      <c r="N524" s="5"/>
+      <c r="O524" s="5">
+        <v>1</v>
+      </c>
+      <c r="P524" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q524" s="5"/>
+      <c r="R524" s="5"/>
+      <c r="S524" s="5"/>
+      <c r="T524" s="35"/>
+    </row>
+    <row r="525" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A525" s="33">
+        <v>504</v>
+      </c>
+      <c r="B525" s="33" t="s">
+        <v>966</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D525" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E525" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F525" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G525" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H525" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I525" s="5"/>
+      <c r="J525" s="5"/>
+      <c r="K525" s="5"/>
+      <c r="L525" s="5"/>
+      <c r="M525" s="5"/>
+      <c r="N525" s="5"/>
+      <c r="O525" s="5">
+        <v>1</v>
+      </c>
+      <c r="P525" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q525" s="5"/>
+      <c r="R525" s="5"/>
+      <c r="S525" s="5"/>
+      <c r="T525" s="35"/>
+    </row>
+    <row r="526" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A526" s="33">
+        <v>505</v>
+      </c>
+      <c r="B526" s="33" t="s">
+        <v>967</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D526" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="E526" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F526" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G526" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H526" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I526" s="5"/>
+      <c r="J526" s="5"/>
+      <c r="K526" s="5"/>
+      <c r="L526" s="5"/>
+      <c r="M526" s="5"/>
+      <c r="N526" s="5"/>
+      <c r="O526" s="5">
+        <v>1</v>
+      </c>
+      <c r="P526" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q526" s="5"/>
+      <c r="R526" s="5"/>
+      <c r="S526" s="5"/>
+      <c r="T526" s="35"/>
+    </row>
+    <row r="527" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A527" s="33">
+        <v>508</v>
+      </c>
+      <c r="B527" s="33" t="s">
+        <v>968</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D527" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="E527" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F527" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G527" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H527" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I527" s="5"/>
+      <c r="J527" s="5"/>
+      <c r="K527" s="5"/>
+      <c r="L527" s="5"/>
+      <c r="M527" s="5"/>
+      <c r="N527" s="5"/>
+      <c r="O527" s="5">
+        <v>1</v>
+      </c>
+      <c r="P527" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q527" s="5"/>
+      <c r="R527" s="5"/>
+      <c r="S527" s="5"/>
+      <c r="T527" s="35"/>
+    </row>
+    <row r="528" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A528" s="33">
+        <v>522</v>
+      </c>
+      <c r="B528" s="33" t="s">
+        <v>969</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D528" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E528" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F528" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G528" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H528" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I528" s="5"/>
+      <c r="J528" s="5"/>
+      <c r="K528" s="5"/>
+      <c r="L528" s="5"/>
+      <c r="M528" s="5"/>
+      <c r="N528" s="5"/>
+      <c r="O528" s="5">
+        <v>1</v>
+      </c>
+      <c r="P528" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q528" s="5"/>
+      <c r="R528" s="5"/>
+      <c r="S528" s="5"/>
+      <c r="T528" s="35"/>
+    </row>
+    <row r="529" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A529" s="33">
+        <v>527</v>
+      </c>
+      <c r="B529" s="33" t="s">
+        <v>970</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D529" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E529" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F529" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G529" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H529" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I529" s="5"/>
+      <c r="J529" s="5"/>
+      <c r="K529" s="5"/>
+      <c r="L529" s="5"/>
+      <c r="M529" s="5"/>
+      <c r="N529" s="5"/>
+      <c r="O529" s="5">
+        <v>1</v>
+      </c>
+      <c r="P529" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q529" s="5"/>
+      <c r="R529" s="5"/>
+      <c r="S529" s="5"/>
+      <c r="T529" s="35"/>
+    </row>
+    <row r="530" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A530" s="33">
+        <v>528</v>
+      </c>
+      <c r="B530" s="33" t="s">
+        <v>971</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D530" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="E530" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F530" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G530" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H530" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I530" s="5"/>
+      <c r="J530" s="5"/>
+      <c r="K530" s="5"/>
+      <c r="L530" s="5"/>
+      <c r="M530" s="5"/>
+      <c r="N530" s="5"/>
+      <c r="O530" s="5">
+        <v>1</v>
+      </c>
+      <c r="P530" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q530" s="5"/>
+      <c r="R530" s="5"/>
+      <c r="S530" s="5"/>
+      <c r="T530" s="35"/>
+    </row>
+    <row r="531" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A531" s="33">
+        <v>541</v>
+      </c>
+      <c r="B531" s="33" t="s">
+        <v>972</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D531" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="E531" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F531" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G531" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H531" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I531" s="5"/>
+      <c r="J531" s="5"/>
+      <c r="K531" s="5"/>
+      <c r="L531" s="5"/>
+      <c r="M531" s="5"/>
+      <c r="N531" s="5"/>
+      <c r="O531" s="5">
+        <v>1</v>
+      </c>
+      <c r="P531" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q531" s="5"/>
+      <c r="R531" s="5"/>
+      <c r="S531" s="5"/>
+      <c r="T531" s="35"/>
+    </row>
+    <row r="532" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A532" s="33">
+        <v>542</v>
+      </c>
+      <c r="B532" s="33" t="s">
+        <v>973</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D532" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="E532" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G532" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H532" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I532" s="5"/>
+      <c r="J532" s="5"/>
+      <c r="K532" s="5"/>
+      <c r="L532" s="5"/>
+      <c r="M532" s="5"/>
+      <c r="N532" s="5"/>
+      <c r="O532" s="5">
+        <v>1</v>
+      </c>
+      <c r="P532" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q532" s="5"/>
+      <c r="R532" s="5"/>
+      <c r="S532" s="5"/>
+      <c r="T532" s="35"/>
+    </row>
+    <row r="533" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A533" s="33">
+        <v>546</v>
+      </c>
+      <c r="B533" s="33" t="s">
+        <v>974</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D533" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="E533" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F533" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G533" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H533" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I533" s="5"/>
+      <c r="J533" s="5"/>
+      <c r="K533" s="5"/>
+      <c r="L533" s="5"/>
+      <c r="M533" s="5"/>
+      <c r="N533" s="5"/>
+      <c r="O533" s="5">
+        <v>1</v>
+      </c>
+      <c r="P533" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q533" s="5"/>
+      <c r="R533" s="5"/>
+      <c r="S533" s="5"/>
+      <c r="T533" s="35"/>
+    </row>
+    <row r="534" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A534" s="33">
+        <v>547</v>
+      </c>
+      <c r="B534" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D534" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="E534" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F534" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G534" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H534" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I534" s="5"/>
+      <c r="J534" s="5"/>
+      <c r="K534" s="5"/>
+      <c r="L534" s="5"/>
+      <c r="M534" s="5"/>
+      <c r="N534" s="5"/>
+      <c r="O534" s="5">
+        <v>1</v>
+      </c>
+      <c r="P534" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q534" s="5"/>
+      <c r="R534" s="5"/>
+      <c r="S534" s="5"/>
+      <c r="T534" s="35"/>
+    </row>
+    <row r="535" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A535" s="33">
+        <v>552</v>
+      </c>
+      <c r="B535" s="33" t="s">
+        <v>976</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D535" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="E535" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F535" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G535" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H535" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I535" s="5"/>
+      <c r="J535" s="5"/>
+      <c r="K535" s="5"/>
+      <c r="L535" s="5"/>
+      <c r="M535" s="5"/>
+      <c r="N535" s="5"/>
+      <c r="O535" s="5">
+        <v>1</v>
+      </c>
+      <c r="P535" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q535" s="5"/>
+      <c r="R535" s="5"/>
+      <c r="S535" s="5"/>
+      <c r="T535" s="35"/>
+    </row>
+    <row r="536" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A536" s="33">
+        <v>553</v>
+      </c>
+      <c r="B536" s="33" t="s">
+        <v>977</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D536" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="E536" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F536" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G536" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H536" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I536" s="5"/>
+      <c r="J536" s="5"/>
+      <c r="K536" s="5"/>
+      <c r="L536" s="5"/>
+      <c r="M536" s="5"/>
+      <c r="N536" s="5"/>
+      <c r="O536" s="5">
+        <v>1</v>
+      </c>
+      <c r="P536" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q536" s="5"/>
+      <c r="R536" s="5"/>
+      <c r="S536" s="5"/>
+      <c r="T536" s="35"/>
+    </row>
+    <row r="537" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A537" s="33">
+        <v>556</v>
+      </c>
+      <c r="B537" s="33" t="s">
+        <v>978</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D537" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="E537" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F537" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G537" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H537" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I537" s="5"/>
+      <c r="J537" s="5"/>
+      <c r="K537" s="5"/>
+      <c r="L537" s="5"/>
+      <c r="M537" s="5"/>
+      <c r="N537" s="5"/>
+      <c r="O537" s="5">
+        <v>1</v>
+      </c>
+      <c r="P537" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q537" s="5"/>
+      <c r="R537" s="5"/>
+      <c r="S537" s="5"/>
+      <c r="T537" s="35"/>
+    </row>
+    <row r="538" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A538" s="33">
+        <v>485</v>
+      </c>
+      <c r="B538" s="33" t="s">
+        <v>979</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D538" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E538" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F538" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G538" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H538" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I538" s="5"/>
+      <c r="J538" s="5"/>
+      <c r="K538" s="5"/>
+      <c r="L538" s="5"/>
+      <c r="M538" s="5"/>
+      <c r="N538" s="5"/>
+      <c r="O538" s="5">
+        <v>1</v>
+      </c>
+      <c r="P538" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q538" s="5"/>
+      <c r="R538" s="5"/>
+      <c r="S538" s="5"/>
+      <c r="T538" s="35"/>
+    </row>
+    <row r="539" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A539" s="33">
+        <v>488</v>
+      </c>
+      <c r="B539" s="33" t="s">
+        <v>980</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D539" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E539" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F539" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G539" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H539" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I539" s="5"/>
+      <c r="J539" s="5"/>
+      <c r="K539" s="5"/>
+      <c r="L539" s="5"/>
+      <c r="M539" s="5"/>
+      <c r="N539" s="5"/>
+      <c r="O539" s="5">
+        <v>1</v>
+      </c>
+      <c r="P539" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q539" s="5"/>
+      <c r="R539" s="5"/>
+      <c r="S539" s="5"/>
+      <c r="T539" s="35"/>
+    </row>
+    <row r="540" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A540" s="33">
+        <v>509</v>
+      </c>
+      <c r="B540" s="33" t="s">
+        <v>981</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D540" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E540" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F540" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G540" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H540" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I540" s="5"/>
+      <c r="J540" s="5"/>
+      <c r="K540" s="5"/>
+      <c r="L540" s="5"/>
+      <c r="M540" s="5"/>
+      <c r="N540" s="5"/>
+      <c r="O540" s="5">
+        <v>1</v>
+      </c>
+      <c r="P540" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q540" s="5"/>
+      <c r="R540" s="5"/>
+      <c r="S540" s="5"/>
+      <c r="T540" s="35"/>
+    </row>
+    <row r="541" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A541" s="33">
+        <v>475</v>
+      </c>
+      <c r="B541" s="33" t="s">
+        <v>982</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D541" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="E541" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F541" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G541" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H541" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I541" s="5"/>
+      <c r="J541" s="5"/>
+      <c r="K541" s="5"/>
+      <c r="L541" s="5"/>
+      <c r="M541" s="5"/>
+      <c r="N541" s="5"/>
+      <c r="O541" s="5">
+        <v>1</v>
+      </c>
+      <c r="P541" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q541" s="5"/>
+      <c r="R541" s="5"/>
+      <c r="S541" s="5"/>
+      <c r="T541" s="35"/>
+    </row>
+    <row r="542" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A542" s="33">
+        <v>477</v>
+      </c>
+      <c r="B542" s="33" t="s">
+        <v>983</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D542" s="33" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E542" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F542" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G542" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H542" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I542" s="5"/>
+      <c r="J542" s="5"/>
+      <c r="K542" s="5"/>
+      <c r="L542" s="5"/>
+      <c r="M542" s="5"/>
+      <c r="N542" s="5"/>
+      <c r="O542" s="5">
+        <v>1</v>
+      </c>
+      <c r="P542" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q542" s="5"/>
+      <c r="R542" s="5"/>
+      <c r="S542" s="5"/>
+      <c r="T542" s="35"/>
+    </row>
+    <row r="543" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A543" s="33">
+        <v>478</v>
+      </c>
+      <c r="B543" s="33" t="s">
+        <v>984</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D543" s="33" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E543" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F543" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G543" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H543" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I543" s="5"/>
+      <c r="J543" s="5"/>
+      <c r="K543" s="5"/>
+      <c r="L543" s="5"/>
+      <c r="M543" s="5"/>
+      <c r="N543" s="5"/>
+      <c r="O543" s="5">
+        <v>1</v>
+      </c>
+      <c r="P543" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q543" s="5"/>
+      <c r="R543" s="5"/>
+      <c r="S543" s="5"/>
+      <c r="T543" s="35"/>
+    </row>
+    <row r="544" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A544" s="33">
+        <v>479</v>
+      </c>
+      <c r="B544" s="33" t="s">
+        <v>985</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D544" s="33" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E544" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F544" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G544" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H544" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I544" s="5"/>
+      <c r="J544" s="5"/>
+      <c r="K544" s="5"/>
+      <c r="L544" s="5"/>
+      <c r="M544" s="5"/>
+      <c r="N544" s="5"/>
+      <c r="O544" s="5">
+        <v>1</v>
+      </c>
+      <c r="P544" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q544" s="5"/>
+      <c r="R544" s="5"/>
+      <c r="S544" s="5"/>
+      <c r="T544" s="35"/>
+    </row>
+    <row r="545" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A545" s="33">
+        <v>480</v>
+      </c>
+      <c r="B545" s="33" t="s">
+        <v>986</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D545" s="33" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E545" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F545" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G545" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H545" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I545" s="5"/>
+      <c r="J545" s="5"/>
+      <c r="K545" s="5"/>
+      <c r="L545" s="5"/>
+      <c r="M545" s="5"/>
+      <c r="N545" s="5"/>
+      <c r="O545" s="5">
+        <v>1</v>
+      </c>
+      <c r="P545" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q545" s="5"/>
+      <c r="R545" s="5"/>
+      <c r="S545" s="5"/>
+      <c r="T545" s="35"/>
+    </row>
+    <row r="546" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A546" s="33">
+        <v>481</v>
+      </c>
+      <c r="B546" s="33" t="s">
+        <v>987</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D546" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E546" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F546" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G546" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H546" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I546" s="5"/>
+      <c r="J546" s="5"/>
+      <c r="K546" s="5"/>
+      <c r="L546" s="5"/>
+      <c r="M546" s="5"/>
+      <c r="N546" s="5"/>
+      <c r="O546" s="5">
+        <v>1</v>
+      </c>
+      <c r="P546" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q546" s="5"/>
+      <c r="R546" s="5"/>
+      <c r="S546" s="5"/>
+      <c r="T546" s="35"/>
+    </row>
+    <row r="547" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A547" s="33">
+        <v>486</v>
+      </c>
+      <c r="B547" s="33" t="s">
+        <v>988</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D547" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="E547" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F547" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G547" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H547" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I547" s="5"/>
+      <c r="J547" s="5"/>
+      <c r="K547" s="5"/>
+      <c r="L547" s="5"/>
+      <c r="M547" s="5"/>
+      <c r="N547" s="5"/>
+      <c r="O547" s="5">
+        <v>1</v>
+      </c>
+      <c r="P547" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q547" s="5"/>
+      <c r="R547" s="5"/>
+      <c r="S547" s="5"/>
+      <c r="T547" s="35"/>
+    </row>
+    <row r="548" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A548" s="33">
+        <v>506</v>
+      </c>
+      <c r="B548" s="33" t="s">
+        <v>655</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D548" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="E548" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F548" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G548" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H548" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I548" s="5"/>
+      <c r="J548" s="5"/>
+      <c r="K548" s="5"/>
+      <c r="L548" s="5"/>
+      <c r="M548" s="5"/>
+      <c r="N548" s="5"/>
+      <c r="O548" s="5">
+        <v>1</v>
+      </c>
+      <c r="P548" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q548" s="5"/>
+      <c r="R548" s="5"/>
+      <c r="S548" s="5"/>
+      <c r="T548" s="35"/>
+    </row>
+    <row r="549" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A549" s="33">
+        <v>507</v>
+      </c>
+      <c r="B549" s="33" t="s">
+        <v>989</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D549" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E549" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F549" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G549" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H549" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I549" s="5"/>
+      <c r="J549" s="5"/>
+      <c r="K549" s="5"/>
+      <c r="L549" s="5"/>
+      <c r="M549" s="5"/>
+      <c r="N549" s="5"/>
+      <c r="O549" s="5">
+        <v>1</v>
+      </c>
+      <c r="P549" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q549" s="5"/>
+      <c r="R549" s="5"/>
+      <c r="S549" s="5"/>
+      <c r="T549" s="35"/>
+    </row>
+    <row r="550" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A550" s="33">
+        <v>514</v>
+      </c>
+      <c r="B550" s="33" t="s">
+        <v>990</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D550" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E550" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F550" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G550" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H550" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I550" s="5"/>
+      <c r="J550" s="5"/>
+      <c r="K550" s="5"/>
+      <c r="L550" s="5"/>
+      <c r="M550" s="5"/>
+      <c r="N550" s="5"/>
+      <c r="O550" s="5">
+        <v>1</v>
+      </c>
+      <c r="P550" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q550" s="5"/>
+      <c r="R550" s="5"/>
+      <c r="S550" s="5"/>
+      <c r="T550" s="35"/>
+    </row>
+    <row r="551" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A551" s="33">
+        <v>515</v>
+      </c>
+      <c r="B551" s="33" t="s">
+        <v>991</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D551" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E551" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F551" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G551" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H551" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I551" s="5"/>
+      <c r="J551" s="5"/>
+      <c r="K551" s="5"/>
+      <c r="L551" s="5"/>
+      <c r="M551" s="5"/>
+      <c r="N551" s="5"/>
+      <c r="O551" s="5">
+        <v>1</v>
+      </c>
+      <c r="P551" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q551" s="5"/>
+      <c r="R551" s="5"/>
+      <c r="S551" s="5"/>
+      <c r="T551" s="35"/>
+    </row>
+    <row r="552" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A552" s="33">
+        <v>516</v>
+      </c>
+      <c r="B552" s="33" t="s">
+        <v>992</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D552" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E552" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F552" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G552" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H552" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I552" s="5"/>
+      <c r="J552" s="5"/>
+      <c r="K552" s="5"/>
+      <c r="L552" s="5"/>
+      <c r="M552" s="5"/>
+      <c r="N552" s="5"/>
+      <c r="O552" s="5">
+        <v>1</v>
+      </c>
+      <c r="P552" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q552" s="5"/>
+      <c r="R552" s="5"/>
+      <c r="S552" s="5"/>
+      <c r="T552" s="35"/>
+    </row>
+    <row r="553" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A553" s="33">
+        <v>519</v>
+      </c>
+      <c r="B553" s="33" t="s">
+        <v>993</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D553" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="E553" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F553" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G553" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H553" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I553" s="5"/>
+      <c r="J553" s="5"/>
+      <c r="K553" s="5"/>
+      <c r="L553" s="5"/>
+      <c r="M553" s="5"/>
+      <c r="N553" s="5"/>
+      <c r="O553" s="5">
+        <v>1</v>
+      </c>
+      <c r="P553" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q553" s="5"/>
+      <c r="R553" s="5"/>
+      <c r="S553" s="5"/>
+      <c r="T553" s="35"/>
+    </row>
+    <row r="554" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A554" s="33">
+        <v>523</v>
+      </c>
+      <c r="B554" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D554" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E554" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F554" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G554" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H554" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I554" s="5"/>
+      <c r="J554" s="5"/>
+      <c r="K554" s="5"/>
+      <c r="L554" s="5"/>
+      <c r="M554" s="5"/>
+      <c r="N554" s="5"/>
+      <c r="O554" s="5">
+        <v>1</v>
+      </c>
+      <c r="P554" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q554" s="5"/>
+      <c r="R554" s="5"/>
+      <c r="S554" s="5"/>
+      <c r="T554" s="35"/>
+    </row>
+    <row r="555" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A555" s="33">
+        <v>524</v>
+      </c>
+      <c r="B555" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D555" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="E555" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F555" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G555" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H555" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I555" s="5"/>
+      <c r="J555" s="5"/>
+      <c r="K555" s="5"/>
+      <c r="L555" s="5"/>
+      <c r="M555" s="5"/>
+      <c r="N555" s="5"/>
+      <c r="O555" s="5">
+        <v>1</v>
+      </c>
+      <c r="P555" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q555" s="5"/>
+      <c r="R555" s="5"/>
+      <c r="S555" s="5"/>
+      <c r="T555" s="35"/>
+    </row>
+    <row r="556" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A556" s="33">
+        <v>530</v>
+      </c>
+      <c r="B556" s="33" t="s">
+        <v>994</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D556" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E556" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F556" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G556" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H556" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I556" s="5"/>
+      <c r="J556" s="5"/>
+      <c r="K556" s="5"/>
+      <c r="L556" s="5"/>
+      <c r="M556" s="5"/>
+      <c r="N556" s="5"/>
+      <c r="O556" s="5">
+        <v>1</v>
+      </c>
+      <c r="P556" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q556" s="5"/>
+      <c r="R556" s="5"/>
+      <c r="S556" s="5"/>
+      <c r="T556" s="35"/>
+    </row>
+    <row r="557" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A557" s="33">
+        <v>531</v>
+      </c>
+      <c r="B557" s="33" t="s">
+        <v>995</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D557" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E557" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F557" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G557" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H557" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I557" s="5"/>
+      <c r="J557" s="5"/>
+      <c r="K557" s="5"/>
+      <c r="L557" s="5"/>
+      <c r="M557" s="5"/>
+      <c r="N557" s="5"/>
+      <c r="O557" s="5">
+        <v>1</v>
+      </c>
+      <c r="P557" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q557" s="5"/>
+      <c r="R557" s="5"/>
+      <c r="S557" s="5"/>
+      <c r="T557" s="35"/>
+    </row>
+    <row r="558" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A558" s="33">
+        <v>532</v>
+      </c>
+      <c r="B558" s="33" t="s">
+        <v>996</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D558" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E558" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F558" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G558" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H558" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I558" s="5"/>
+      <c r="J558" s="5"/>
+      <c r="K558" s="5"/>
+      <c r="L558" s="5"/>
+      <c r="M558" s="5"/>
+      <c r="N558" s="5"/>
+      <c r="O558" s="5">
+        <v>1</v>
+      </c>
+      <c r="P558" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q558" s="5"/>
+      <c r="R558" s="5"/>
+      <c r="S558" s="5"/>
+      <c r="T558" s="35"/>
+    </row>
+    <row r="559" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A559" s="33">
+        <v>533</v>
+      </c>
+      <c r="B559" s="33" t="s">
+        <v>997</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D559" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E559" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F559" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G559" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H559" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I559" s="5"/>
+      <c r="J559" s="5"/>
+      <c r="K559" s="5"/>
+      <c r="L559" s="5"/>
+      <c r="M559" s="5"/>
+      <c r="N559" s="5"/>
+      <c r="O559" s="5">
+        <v>1</v>
+      </c>
+      <c r="P559" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q559" s="5"/>
+      <c r="R559" s="5"/>
+      <c r="S559" s="5"/>
+      <c r="T559" s="35"/>
+    </row>
+    <row r="560" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A560" s="33">
+        <v>534</v>
+      </c>
+      <c r="B560" s="33" t="s">
+        <v>998</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D560" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E560" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F560" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G560" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H560" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I560" s="5"/>
+      <c r="J560" s="5"/>
+      <c r="K560" s="5"/>
+      <c r="L560" s="5"/>
+      <c r="M560" s="5"/>
+      <c r="N560" s="5"/>
+      <c r="O560" s="5">
+        <v>1</v>
+      </c>
+      <c r="P560" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q560" s="5"/>
+      <c r="R560" s="5"/>
+      <c r="S560" s="5"/>
+      <c r="T560" s="35"/>
+    </row>
+    <row r="561" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A561" s="33">
+        <v>535</v>
+      </c>
+      <c r="B561" s="33" t="s">
+        <v>999</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D561" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E561" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F561" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G561" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H561" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I561" s="5"/>
+      <c r="J561" s="5"/>
+      <c r="K561" s="5"/>
+      <c r="L561" s="5"/>
+      <c r="M561" s="5"/>
+      <c r="N561" s="5"/>
+      <c r="O561" s="5">
+        <v>1</v>
+      </c>
+      <c r="P561" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q561" s="5"/>
+      <c r="R561" s="5"/>
+      <c r="S561" s="5"/>
+      <c r="T561" s="35"/>
+    </row>
+    <row r="562" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A562" s="33">
+        <v>536</v>
+      </c>
+      <c r="B562" s="33" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D562" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E562" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F562" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G562" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H562" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I562" s="5"/>
+      <c r="J562" s="5"/>
+      <c r="K562" s="5"/>
+      <c r="L562" s="5"/>
+      <c r="M562" s="5"/>
+      <c r="N562" s="5"/>
+      <c r="O562" s="5">
+        <v>1</v>
+      </c>
+      <c r="P562" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q562" s="5"/>
+      <c r="R562" s="5"/>
+      <c r="S562" s="5"/>
+      <c r="T562" s="35"/>
+    </row>
+    <row r="563" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A563" s="33">
+        <v>537</v>
+      </c>
+      <c r="B563" s="33" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D563" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E563" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F563" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G563" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H563" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I563" s="5"/>
+      <c r="J563" s="5"/>
+      <c r="K563" s="5"/>
+      <c r="L563" s="5"/>
+      <c r="M563" s="5"/>
+      <c r="N563" s="5"/>
+      <c r="O563" s="5">
+        <v>1</v>
+      </c>
+      <c r="P563" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q563" s="5"/>
+      <c r="R563" s="5"/>
+      <c r="S563" s="5"/>
+      <c r="T563" s="35"/>
+    </row>
+    <row r="564" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A564" s="33">
+        <v>538</v>
+      </c>
+      <c r="B564" s="33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D564" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E564" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F564" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G564" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H564" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I564" s="5"/>
+      <c r="J564" s="5"/>
+      <c r="K564" s="5"/>
+      <c r="L564" s="5"/>
+      <c r="M564" s="5"/>
+      <c r="N564" s="5"/>
+      <c r="O564" s="5">
+        <v>1</v>
+      </c>
+      <c r="P564" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q564" s="5"/>
+      <c r="R564" s="5"/>
+      <c r="S564" s="5"/>
+      <c r="T564" s="35"/>
+    </row>
+    <row r="565" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A565" s="33">
+        <v>539</v>
+      </c>
+      <c r="B565" s="33" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D565" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E565" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F565" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G565" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H565" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I565" s="5"/>
+      <c r="J565" s="5"/>
+      <c r="K565" s="5"/>
+      <c r="L565" s="5"/>
+      <c r="M565" s="5"/>
+      <c r="N565" s="5"/>
+      <c r="O565" s="5">
+        <v>1</v>
+      </c>
+      <c r="P565" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q565" s="5"/>
+      <c r="R565" s="5"/>
+      <c r="S565" s="5"/>
+      <c r="T565" s="35"/>
+    </row>
+    <row r="566" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A566" s="33">
+        <v>540</v>
+      </c>
+      <c r="B566" s="33" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D566" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="E566" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F566" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G566" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H566" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I566" s="5"/>
+      <c r="J566" s="5"/>
+      <c r="K566" s="5"/>
+      <c r="L566" s="5"/>
+      <c r="M566" s="5"/>
+      <c r="N566" s="5"/>
+      <c r="O566" s="5">
+        <v>1</v>
+      </c>
+      <c r="P566" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q566" s="5"/>
+      <c r="R566" s="5"/>
+      <c r="S566" s="5"/>
+      <c r="T566" s="35"/>
+    </row>
+    <row r="567" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A567" s="33">
+        <v>543</v>
+      </c>
+      <c r="B567" s="33" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D567" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="E567" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F567" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G567" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H567" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I567" s="5"/>
+      <c r="J567" s="5"/>
+      <c r="K567" s="5"/>
+      <c r="L567" s="5"/>
+      <c r="M567" s="5"/>
+      <c r="N567" s="5"/>
+      <c r="O567" s="5">
+        <v>1</v>
+      </c>
+      <c r="P567" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q567" s="5"/>
+      <c r="R567" s="5"/>
+      <c r="S567" s="5"/>
+      <c r="T567" s="35"/>
+    </row>
+    <row r="568" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A568" s="33">
+        <v>544</v>
+      </c>
+      <c r="B568" s="33" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D568" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E568" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F568" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G568" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H568" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I568" s="5"/>
+      <c r="J568" s="5"/>
+      <c r="K568" s="5"/>
+      <c r="L568" s="5"/>
+      <c r="M568" s="5"/>
+      <c r="N568" s="5"/>
+      <c r="O568" s="5">
+        <v>1</v>
+      </c>
+      <c r="P568" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q568" s="5"/>
+      <c r="R568" s="5"/>
+      <c r="S568" s="5"/>
+      <c r="T568" s="35"/>
+    </row>
+    <row r="569" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A569" s="33">
+        <v>550</v>
+      </c>
+      <c r="B569" s="33" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D569" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E569" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F569" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G569" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H569" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I569" s="5"/>
+      <c r="J569" s="5"/>
+      <c r="K569" s="5"/>
+      <c r="L569" s="5"/>
+      <c r="M569" s="5"/>
+      <c r="N569" s="5"/>
+      <c r="O569" s="5">
+        <v>1</v>
+      </c>
+      <c r="P569" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q569" s="5"/>
+      <c r="R569" s="5"/>
+      <c r="S569" s="5"/>
+      <c r="T569" s="35"/>
+    </row>
+    <row r="570" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A570" s="33">
+        <v>551</v>
+      </c>
+      <c r="B570" s="33" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D570" s="33" t="s">
+        <v>422</v>
+      </c>
+      <c r="E570" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F570" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G570" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H570" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I570" s="5"/>
+      <c r="J570" s="5"/>
+      <c r="K570" s="5"/>
+      <c r="L570" s="5"/>
+      <c r="M570" s="5"/>
+      <c r="N570" s="5"/>
+      <c r="O570" s="5">
+        <v>1</v>
+      </c>
+      <c r="P570" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q570" s="5"/>
+      <c r="R570" s="5"/>
+      <c r="S570" s="5"/>
+      <c r="T570" s="35"/>
+    </row>
+    <row r="571" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A571" s="33">
+        <v>554</v>
+      </c>
+      <c r="B571" s="33" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D571" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E571" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F571" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G571" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H571" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I571" s="5"/>
+      <c r="J571" s="5"/>
+      <c r="K571" s="5"/>
+      <c r="L571" s="5"/>
+      <c r="M571" s="5"/>
+      <c r="N571" s="5"/>
+      <c r="O571" s="5">
+        <v>1</v>
+      </c>
+      <c r="P571" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q571" s="5"/>
+      <c r="R571" s="5"/>
+      <c r="S571" s="5"/>
+      <c r="T571" s="35"/>
+    </row>
+    <row r="572" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A572" s="33">
+        <v>555</v>
+      </c>
+      <c r="B572" s="33" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D572" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="E572" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F572" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G572" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H572" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I572" s="5"/>
+      <c r="J572" s="5"/>
+      <c r="K572" s="5"/>
+      <c r="L572" s="5"/>
+      <c r="M572" s="5"/>
+      <c r="N572" s="5"/>
+      <c r="O572" s="5">
+        <v>1</v>
+      </c>
+      <c r="P572" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q572" s="5"/>
+      <c r="R572" s="5"/>
+      <c r="S572" s="5"/>
+      <c r="T572" s="35"/>
+    </row>
+    <row r="573" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A573" s="33">
+        <v>510</v>
+      </c>
+      <c r="B573" s="33" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D573" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G573" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H573" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I573" s="5"/>
+      <c r="J573" s="5"/>
+      <c r="K573" s="5"/>
+      <c r="L573" s="5"/>
+      <c r="M573" s="5"/>
+      <c r="N573" s="5"/>
+      <c r="O573" s="5">
+        <v>1</v>
+      </c>
+      <c r="P573" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q573" s="5"/>
+      <c r="R573" s="5"/>
+      <c r="S573" s="5"/>
+      <c r="T573" s="35"/>
+    </row>
+    <row r="574" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A574" s="33">
+        <v>511</v>
+      </c>
+      <c r="B574" s="33" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D574" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E574" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F574" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G574" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H574" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I574" s="5"/>
+      <c r="J574" s="5"/>
+      <c r="K574" s="5"/>
+      <c r="L574" s="5"/>
+      <c r="M574" s="5"/>
+      <c r="N574" s="5"/>
+      <c r="O574" s="5">
+        <v>1</v>
+      </c>
+      <c r="P574" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q574" s="5"/>
+      <c r="R574" s="5"/>
+      <c r="S574" s="5"/>
+      <c r="T574" s="35"/>
+    </row>
+    <row r="575" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A575" s="33">
+        <v>513</v>
+      </c>
+      <c r="B575" s="33" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D575" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E575" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F575" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G575" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H575" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I575" s="5"/>
+      <c r="J575" s="5"/>
+      <c r="K575" s="5"/>
+      <c r="L575" s="5"/>
+      <c r="M575" s="5"/>
+      <c r="N575" s="5"/>
+      <c r="O575" s="5">
+        <v>1</v>
+      </c>
+      <c r="P575" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q575" s="5"/>
+      <c r="R575" s="5"/>
+      <c r="S575" s="5"/>
+      <c r="T575" s="35"/>
+    </row>
+    <row r="576" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A576" s="33">
+        <v>518</v>
+      </c>
+      <c r="B576" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D576" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="E576" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F576" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G576" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H576" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I576" s="5"/>
+      <c r="J576" s="5"/>
+      <c r="K576" s="5"/>
+      <c r="L576" s="5"/>
+      <c r="M576" s="5"/>
+      <c r="N576" s="5"/>
+      <c r="O576" s="5">
+        <v>1</v>
+      </c>
+      <c r="P576" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q576" s="5"/>
+      <c r="R576" s="5"/>
+      <c r="S576" s="5"/>
+      <c r="T576" s="35"/>
+    </row>
+    <row r="577" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A577" s="33">
+        <v>526</v>
+      </c>
+      <c r="B577" s="33" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D577" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E577" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F577" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G577" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H577" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I577" s="5"/>
+      <c r="J577" s="5"/>
+      <c r="K577" s="5"/>
+      <c r="L577" s="5"/>
+      <c r="M577" s="5"/>
+      <c r="N577" s="5"/>
+      <c r="O577" s="5">
+        <v>1</v>
+      </c>
+      <c r="P577" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q577" s="5"/>
+      <c r="R577" s="5"/>
+      <c r="S577" s="5"/>
+      <c r="T577" s="35"/>
+    </row>
+    <row r="578" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A578" s="33">
+        <v>529</v>
+      </c>
+      <c r="B578" s="33" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C578" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D578" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E578" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F578" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G578" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H578" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I578" s="5"/>
+      <c r="J578" s="5"/>
+      <c r="K578" s="5"/>
+      <c r="L578" s="5"/>
+      <c r="M578" s="5"/>
+      <c r="N578" s="5"/>
+      <c r="O578" s="5">
+        <v>1</v>
+      </c>
+      <c r="P578" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q578" s="5"/>
+      <c r="R578" s="5"/>
+      <c r="S578" s="5"/>
+      <c r="T578" s="35"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:U510" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
@@ -51315,61 +54353,61 @@
     <cfRule type="duplicateValues" dxfId="75" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
     <cfRule type="duplicateValues" dxfId="73" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="61"/>
     <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="55" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="47"/>
     <cfRule type="duplicateValues" dxfId="54" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
     <cfRule type="duplicateValues" dxfId="48" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
     <cfRule type="duplicateValues" dxfId="44" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="31"/>
     <cfRule type="duplicateValues" dxfId="37" priority="32"/>
     <cfRule type="duplicateValues" dxfId="36" priority="33"/>
   </conditionalFormatting>
@@ -51379,19 +54417,19 @@
     <cfRule type="duplicateValues" dxfId="33" priority="20"/>
     <cfRule type="duplicateValues" dxfId="32" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A510">
+  <conditionalFormatting sqref="A510:A578">
     <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
     <cfRule type="duplicateValues" dxfId="29" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
     <cfRule type="duplicateValues" dxfId="23" priority="77"/>
@@ -51406,8 +54444,8 @@
     <cfRule type="duplicateValues" dxfId="18" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
     <cfRule type="duplicateValues" dxfId="15" priority="54"/>
@@ -51418,8 +54456,8 @@
     <cfRule type="duplicateValues" dxfId="12" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
     <cfRule type="duplicateValues" dxfId="9" priority="36"/>
@@ -51430,16 +54468,16 @@
     <cfRule type="duplicateValues" dxfId="6" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="5" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B510">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="B510:B578">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -53318,7 +56356,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="28">
         <v>210</v>
       </c>
@@ -53598,7 +56636,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28">
         <v>233</v>
       </c>
@@ -53864,7 +56902,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="28">
         <v>253</v>
       </c>
@@ -53906,7 +56944,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="28">
         <v>256</v>
       </c>
@@ -53920,7 +56958,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="28">
         <v>257</v>
       </c>
@@ -54452,7 +57490,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="28">
         <v>296</v>
       </c>
@@ -54466,7 +57504,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="28">
         <v>297</v>
       </c>
@@ -54480,7 +57518,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="28">
         <v>298</v>
       </c>
@@ -54592,7 +57630,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="28">
         <v>307</v>
       </c>
@@ -54676,7 +57714,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="28">
         <v>313</v>
       </c>
@@ -54690,7 +57728,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="28">
         <v>314</v>
       </c>
@@ -54704,7 +57742,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="28">
         <v>315</v>
       </c>
@@ -54718,7 +57756,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="28">
         <v>316</v>
       </c>
@@ -54732,7 +57770,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="28">
         <v>317</v>
       </c>
@@ -54746,7 +57784,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="28">
         <v>318</v>
       </c>
@@ -54760,7 +57798,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="28">
         <v>319</v>
       </c>
@@ -54774,7 +57812,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="28">
         <v>320</v>
       </c>
@@ -54788,7 +57826,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="28">
         <v>321</v>
       </c>
@@ -54872,7 +57910,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="28">
         <v>328</v>
       </c>
@@ -54956,7 +57994,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="28">
         <v>336</v>
       </c>
@@ -55040,7 +58078,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="28">
         <v>344</v>
       </c>
@@ -55110,7 +58148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="28">
         <v>349</v>
       </c>
@@ -55124,7 +58162,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="28">
         <v>350</v>
       </c>
@@ -55306,7 +58344,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="28">
         <v>363</v>
       </c>
@@ -55320,7 +58358,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="28">
         <v>364</v>
       </c>
@@ -55390,7 +58428,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="28">
         <v>369</v>
       </c>
@@ -55516,7 +58554,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="28">
         <v>378</v>
       </c>
@@ -55698,7 +58736,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="28">
         <v>391</v>
       </c>
@@ -55740,7 +58778,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="28">
         <v>394</v>
       </c>
@@ -55754,7 +58792,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="28">
         <v>395</v>
       </c>
@@ -55768,7 +58806,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="28">
         <v>396</v>
       </c>
@@ -55796,7 +58834,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="28">
         <v>398</v>
       </c>
@@ -55810,7 +58848,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="28">
         <v>399</v>
       </c>
@@ -55824,7 +58862,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="28">
         <v>400</v>
       </c>
@@ -55838,7 +58876,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="28">
         <v>401</v>
       </c>
@@ -55852,7 +58890,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="28">
         <v>402</v>
       </c>
@@ -55978,7 +59016,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="28">
         <v>411</v>
       </c>
@@ -55992,7 +59030,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="28">
         <v>412</v>
       </c>
@@ -56006,7 +59044,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="28">
         <v>413</v>
       </c>
@@ -56118,7 +59156,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="28">
         <v>421</v>
       </c>
@@ -56132,7 +59170,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="28">
         <v>422</v>
       </c>
@@ -56146,7 +59184,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="28">
         <v>423</v>
       </c>
@@ -56160,7 +59198,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="28">
         <v>424</v>
       </c>
@@ -56174,7 +59212,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="28">
         <v>425</v>
       </c>
@@ -56384,7 +59422,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="28">
         <v>11</v>
       </c>
@@ -56510,7 +59548,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="28">
         <v>20</v>
       </c>
@@ -56944,7 +59982,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="28">
         <v>51</v>
       </c>
@@ -56958,7 +59996,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="28">
         <v>52</v>
       </c>
@@ -57280,7 +60318,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="28">
         <v>96</v>
       </c>
@@ -57294,7 +60332,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="28" t="s">
         <v>548</v>
       </c>
@@ -57308,7 +60346,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="28" t="s">
         <v>551</v>
       </c>
@@ -57322,7 +60360,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="28" t="s">
         <v>553</v>
       </c>
@@ -57336,7 +60374,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="28" t="s">
         <v>555</v>
       </c>
@@ -57392,7 +60430,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="28" t="s">
         <v>563</v>
       </c>
@@ -57406,7 +60444,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="28" t="s">
         <v>565</v>
       </c>
@@ -57420,7 +60458,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="28" t="s">
         <v>567</v>
       </c>
@@ -57434,7 +60472,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="28" t="s">
         <v>569</v>
       </c>
@@ -57448,7 +60486,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="28" t="s">
         <v>571</v>
       </c>
@@ -57476,7 +60514,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="28" t="s">
         <v>575</v>
       </c>
@@ -57504,7 +60542,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="28" t="s">
         <v>579</v>
       </c>
@@ -57518,7 +60556,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="28" t="s">
         <v>581</v>
       </c>
@@ -57532,7 +60570,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="28" t="s">
         <v>583</v>
       </c>
@@ -57546,7 +60584,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="28" t="s">
         <v>585</v>
       </c>
@@ -57560,7 +60598,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="28" t="s">
         <v>587</v>
       </c>
@@ -57602,7 +60640,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="28" t="s">
         <v>593</v>
       </c>
@@ -58134,7 +61172,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="28" t="s">
         <v>657</v>
       </c>
@@ -58190,7 +61228,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="28">
         <v>440</v>
       </c>
@@ -58274,7 +61312,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="28">
         <v>444</v>
       </c>
@@ -58372,7 +61410,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="28">
         <v>451</v>
       </c>
@@ -58512,7 +61550,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="28">
         <v>462</v>
       </c>
@@ -58554,7 +61592,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="28">
         <v>465</v>
       </c>
@@ -58596,7 +61634,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="28">
         <v>468</v>
       </c>
@@ -58624,7 +61662,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="28">
         <v>470</v>
       </c>
@@ -58694,7 +61732,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="28">
         <v>902</v>
       </c>
@@ -58722,7 +61760,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="28">
         <v>904</v>
       </c>
@@ -58750,7 +61788,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="28">
         <v>906</v>
       </c>
@@ -58764,7 +61802,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="28">
         <v>907</v>
       </c>
@@ -58890,7 +61928,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="28" t="s">
         <v>723</v>
       </c>
@@ -59043,26 +62081,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -59297,26 +62315,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -59333,4 +62352,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -36206,61 +36206,61 @@
     <cfRule type="duplicateValues" dxfId="75" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
     <cfRule type="duplicateValues" dxfId="73" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="71" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
     <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="59" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="55" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="51"/>
     <cfRule type="duplicateValues" dxfId="54" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
     <cfRule type="duplicateValues" dxfId="48" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="47" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
     <cfRule type="duplicateValues" dxfId="44" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="43" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="39" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
     <cfRule type="duplicateValues" dxfId="37" priority="32"/>
     <cfRule type="duplicateValues" dxfId="36" priority="33"/>
   </conditionalFormatting>
@@ -36272,17 +36272,17 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
     <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
     <cfRule type="duplicateValues" dxfId="29" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
     <cfRule type="duplicateValues" dxfId="23" priority="77"/>
@@ -36297,8 +36297,8 @@
     <cfRule type="duplicateValues" dxfId="18" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="17" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
     <cfRule type="duplicateValues" dxfId="15" priority="54"/>
@@ -36309,8 +36309,8 @@
     <cfRule type="duplicateValues" dxfId="12" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
     <cfRule type="duplicateValues" dxfId="9" priority="36"/>
@@ -36321,16 +36321,16 @@
     <cfRule type="duplicateValues" dxfId="6" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -37183,6 +37183,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37417,27 +37437,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37454,23 +37473,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2183" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85EA8C7-1425-4E88-A2B2-D9203A800DE9}"/>
@@ -37179,6 +37179,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37413,27 +37433,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37450,23 +37469,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2184" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD558F55-0728-4FC4-AE82-EF8F9BC11E43}"/>
@@ -37189,17 +37189,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37434,6 +37423,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
@@ -37443,17 +37443,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37470,4 +37459,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -37183,14 +37183,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37429,21 +37427,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37468,9 +37465,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2233" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D10D71-E4C4-4E9E-9527-09F72FD43EB4}"/>
+  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73603424-E420-4C68-8A74-517CB8E2B317}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21940,7 +21940,7 @@
       <c r="M307" s="4"/>
       <c r="N307" s="4"/>
       <c r="O307" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P307" s="4"/>
       <c r="Q307" s="4">
@@ -21993,7 +21993,7 @@
       <c r="M308" s="4"/>
       <c r="N308" s="4"/>
       <c r="O308" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P308" s="4"/>
       <c r="Q308" s="4">
@@ -22046,7 +22046,7 @@
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
       <c r="O309" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P309" s="4"/>
       <c r="Q309" s="4">
@@ -22099,7 +22099,7 @@
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
       <c r="O310" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P310" s="4"/>
       <c r="Q310" s="4">
@@ -37192,6 +37192,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37426,17 +37437,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
@@ -37446,6 +37446,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37462,15 +37473,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -37183,26 +37183,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37437,10 +37417,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37457,20 +37468,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2243" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73603424-E420-4C68-8A74-517CB8E2B317}"/>
+  <xr:revisionPtr revIDLastSave="2250" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC68B6D-C7E8-435A-B847-3D5C8B60D939}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4886,10 +4886,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -5187,6 +5183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V578"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5278,7 +5275,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>68</v>
       </c>
@@ -5331,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>69</v>
       </c>
@@ -5384,7 +5381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>73</v>
       </c>
@@ -5437,7 +5434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>74</v>
       </c>
@@ -5490,7 +5487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>77</v>
       </c>
@@ -5552,7 +5549,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>78</v>
       </c>
@@ -5607,7 +5604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>79</v>
       </c>
@@ -5660,7 +5657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>84</v>
       </c>
@@ -5713,7 +5710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>85</v>
       </c>
@@ -5766,7 +5763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>86</v>
       </c>
@@ -5819,7 +5816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>87</v>
       </c>
@@ -5872,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>88</v>
       </c>
@@ -5925,7 +5922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>89</v>
       </c>
@@ -5978,7 +5975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>90</v>
       </c>
@@ -6031,7 +6028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>91</v>
       </c>
@@ -6084,7 +6081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>92</v>
       </c>
@@ -6137,7 +6134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>94</v>
       </c>
@@ -6190,7 +6187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>95</v>
       </c>
@@ -6243,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>100</v>
       </c>
@@ -6296,7 +6293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>104</v>
       </c>
@@ -6349,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>106</v>
       </c>
@@ -6402,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>108</v>
       </c>
@@ -6455,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>110</v>
       </c>
@@ -6508,7 +6505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>111</v>
       </c>
@@ -6561,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>112</v>
       </c>
@@ -6614,7 +6611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>113</v>
       </c>
@@ -6667,7 +6664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>114</v>
       </c>
@@ -6720,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>115</v>
       </c>
@@ -6773,7 +6770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>116</v>
       </c>
@@ -6826,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>118</v>
       </c>
@@ -6879,7 +6876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>121</v>
       </c>
@@ -6932,7 +6929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>122</v>
       </c>
@@ -6985,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>124</v>
       </c>
@@ -7038,7 +7035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>125</v>
       </c>
@@ -7091,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>126</v>
       </c>
@@ -7144,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>127</v>
       </c>
@@ -7197,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>128</v>
       </c>
@@ -7250,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>133</v>
       </c>
@@ -7303,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>136</v>
       </c>
@@ -7356,7 +7353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>137</v>
       </c>
@@ -7409,7 +7406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>139</v>
       </c>
@@ -7462,7 +7459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>143</v>
       </c>
@@ -7517,7 +7514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>144</v>
       </c>
@@ -7572,7 +7569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>145</v>
       </c>
@@ -7625,7 +7622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>146</v>
       </c>
@@ -7678,7 +7675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>147</v>
       </c>
@@ -7733,7 +7730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>148</v>
       </c>
@@ -7795,7 +7792,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>150</v>
       </c>
@@ -7848,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>151</v>
       </c>
@@ -7901,7 +7898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>157</v>
       </c>
@@ -7954,7 +7951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>159</v>
       </c>
@@ -8007,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>167</v>
       </c>
@@ -8060,7 +8057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>171</v>
       </c>
@@ -8113,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>172</v>
       </c>
@@ -8168,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>174</v>
       </c>
@@ -8221,7 +8218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>176</v>
       </c>
@@ -8276,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>193</v>
       </c>
@@ -8338,7 +8335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>194</v>
       </c>
@@ -8400,7 +8397,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>195</v>
       </c>
@@ -8455,7 +8452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>196</v>
       </c>
@@ -8508,7 +8505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>197</v>
       </c>
@@ -8561,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>199</v>
       </c>
@@ -8614,7 +8611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>200</v>
       </c>
@@ -8674,7 +8671,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>202</v>
       </c>
@@ -8736,7 +8733,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>203</v>
       </c>
@@ -8798,7 +8795,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>204</v>
       </c>
@@ -8860,7 +8857,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>205</v>
       </c>
@@ -8920,7 +8917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>206</v>
       </c>
@@ -8980,7 +8977,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>207</v>
       </c>
@@ -9040,7 +9037,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>208</v>
       </c>
@@ -9093,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>210</v>
       </c>
@@ -9146,7 +9143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>213</v>
       </c>
@@ -9199,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>214</v>
       </c>
@@ -9252,7 +9249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>215</v>
       </c>
@@ -9305,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>216</v>
       </c>
@@ -9358,7 +9355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>217</v>
       </c>
@@ -9411,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>218</v>
       </c>
@@ -9464,7 +9461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>219</v>
       </c>
@@ -9517,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>220</v>
       </c>
@@ -9570,7 +9567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>221</v>
       </c>
@@ -9623,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>222</v>
       </c>
@@ -9676,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>223</v>
       </c>
@@ -9729,7 +9726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>224</v>
       </c>
@@ -9782,7 +9779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>225</v>
       </c>
@@ -9835,7 +9832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>226</v>
       </c>
@@ -9888,7 +9885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>227</v>
       </c>
@@ -9941,7 +9938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>228</v>
       </c>
@@ -10001,7 +9998,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>230</v>
       </c>
@@ -10054,7 +10051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>231</v>
       </c>
@@ -10107,7 +10104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>232</v>
       </c>
@@ -10160,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>233</v>
       </c>
@@ -10213,7 +10210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>234</v>
       </c>
@@ -10266,7 +10263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>235</v>
       </c>
@@ -10319,7 +10316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>236</v>
       </c>
@@ -10372,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>237</v>
       </c>
@@ -10427,7 +10424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>238</v>
       </c>
@@ -10480,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>239</v>
       </c>
@@ -10533,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>240</v>
       </c>
@@ -10588,7 +10585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>241</v>
       </c>
@@ -10641,7 +10638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>242</v>
       </c>
@@ -10694,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>243</v>
       </c>
@@ -10747,7 +10744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>244</v>
       </c>
@@ -10807,7 +10804,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>245</v>
       </c>
@@ -10871,7 +10868,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>246</v>
       </c>
@@ -10922,7 +10919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>247</v>
       </c>
@@ -10975,7 +10972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>248</v>
       </c>
@@ -11033,7 +11030,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>249</v>
       </c>
@@ -11093,7 +11090,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>254</v>
       </c>
@@ -11146,7 +11143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>251</v>
       </c>
@@ -11201,7 +11198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>252</v>
       </c>
@@ -11256,7 +11253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>253</v>
       </c>
@@ -11309,7 +11306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>255</v>
       </c>
@@ -11362,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>256</v>
       </c>
@@ -11415,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>257</v>
       </c>
@@ -11468,7 +11465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>259</v>
       </c>
@@ -11523,7 +11520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>260</v>
       </c>
@@ -11576,7 +11573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>261</v>
       </c>
@@ -11629,7 +11626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>262</v>
       </c>
@@ -11682,7 +11679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>263</v>
       </c>
@@ -11735,7 +11732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>264</v>
       </c>
@@ -11788,7 +11785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>265</v>
       </c>
@@ -11841,7 +11838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>266</v>
       </c>
@@ -11894,7 +11891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>267</v>
       </c>
@@ -11947,7 +11944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>268</v>
       </c>
@@ -12000,7 +11997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>269</v>
       </c>
@@ -12053,7 +12050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>270</v>
       </c>
@@ -12106,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>271</v>
       </c>
@@ -12159,7 +12156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>272</v>
       </c>
@@ -12212,7 +12209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>273</v>
       </c>
@@ -12265,7 +12262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12">
         <v>274</v>
       </c>
@@ -12327,7 +12324,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>275</v>
       </c>
@@ -12380,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14">
         <v>276</v>
       </c>
@@ -12444,7 +12441,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>277</v>
       </c>
@@ -12503,7 +12500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>278</v>
       </c>
@@ -12556,7 +12553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>279</v>
       </c>
@@ -12609,7 +12606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>280</v>
       </c>
@@ -12662,7 +12659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>281</v>
       </c>
@@ -12715,7 +12712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>282</v>
       </c>
@@ -12768,7 +12765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>283</v>
       </c>
@@ -12823,7 +12820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>284</v>
       </c>
@@ -12876,7 +12873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>285</v>
       </c>
@@ -12929,7 +12926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>286</v>
       </c>
@@ -12984,7 +12981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>287</v>
       </c>
@@ -13037,7 +13034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>288</v>
       </c>
@@ -13090,7 +13087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>289</v>
       </c>
@@ -13143,7 +13140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>290</v>
       </c>
@@ -13196,7 +13193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>291</v>
       </c>
@@ -13249,7 +13246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>292</v>
       </c>
@@ -13304,7 +13301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>293</v>
       </c>
@@ -13357,7 +13354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>294</v>
       </c>
@@ -13412,7 +13409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>295</v>
       </c>
@@ -13465,7 +13462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>296</v>
       </c>
@@ -13518,7 +13515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>297</v>
       </c>
@@ -13571,7 +13568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>298</v>
       </c>
@@ -13624,7 +13621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>300</v>
       </c>
@@ -13677,7 +13674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>301</v>
       </c>
@@ -13730,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>302</v>
       </c>
@@ -13783,7 +13780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>303</v>
       </c>
@@ -13836,7 +13833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>304</v>
       </c>
@@ -13889,7 +13886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>305</v>
       </c>
@@ -13942,7 +13939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>306</v>
       </c>
@@ -13997,7 +13994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>307</v>
       </c>
@@ -14050,7 +14047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>308</v>
       </c>
@@ -14103,7 +14100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>309</v>
       </c>
@@ -14156,7 +14153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>310</v>
       </c>
@@ -14209,7 +14206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>311</v>
       </c>
@@ -14262,7 +14259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>312</v>
       </c>
@@ -14315,7 +14312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>313</v>
       </c>
@@ -14368,7 +14365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>314</v>
       </c>
@@ -14421,7 +14418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>315</v>
       </c>
@@ -14474,7 +14471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>316</v>
       </c>
@@ -14527,7 +14524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>317</v>
       </c>
@@ -14580,7 +14577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>318</v>
       </c>
@@ -14633,7 +14630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>319</v>
       </c>
@@ -14686,7 +14683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>320</v>
       </c>
@@ -14739,7 +14736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>321</v>
       </c>
@@ -14792,7 +14789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12">
         <v>323</v>
       </c>
@@ -14856,7 +14853,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>324</v>
       </c>
@@ -14909,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12">
         <v>325</v>
       </c>
@@ -14973,7 +14970,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>326</v>
       </c>
@@ -15026,7 +15023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12">
         <v>327</v>
       </c>
@@ -15083,7 +15080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>328</v>
       </c>
@@ -15136,7 +15133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>329</v>
       </c>
@@ -15189,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>331</v>
       </c>
@@ -15249,7 +15246,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12">
         <v>332</v>
       </c>
@@ -15311,7 +15308,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>334</v>
       </c>
@@ -15375,7 +15372,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>335</v>
       </c>
@@ -15433,7 +15430,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>336</v>
       </c>
@@ -15486,7 +15483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>337</v>
       </c>
@@ -15539,7 +15536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>338</v>
       </c>
@@ -15596,7 +15593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>339</v>
       </c>
@@ -15660,7 +15657,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>340</v>
       </c>
@@ -15713,7 +15710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>341</v>
       </c>
@@ -15766,7 +15763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>344</v>
       </c>
@@ -15819,7 +15816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="32">
         <v>345</v>
       </c>
@@ -15881,7 +15878,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>346</v>
       </c>
@@ -15934,7 +15931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>347</v>
       </c>
@@ -15987,7 +15984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>348</v>
       </c>
@@ -16040,7 +16037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>349</v>
       </c>
@@ -16093,7 +16090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>350</v>
       </c>
@@ -16146,7 +16143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>351</v>
       </c>
@@ -16199,7 +16196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>352</v>
       </c>
@@ -16252,7 +16249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="32">
         <v>353</v>
       </c>
@@ -16312,7 +16309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>354</v>
       </c>
@@ -16365,7 +16362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>355</v>
       </c>
@@ -16418,7 +16415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>356</v>
       </c>
@@ -16471,7 +16468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>357</v>
       </c>
@@ -16524,7 +16521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>358</v>
       </c>
@@ -16577,7 +16574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>359</v>
       </c>
@@ -16630,7 +16627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>360</v>
       </c>
@@ -16683,7 +16680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:22" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>361</v>
       </c>
@@ -16745,7 +16742,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>362</v>
       </c>
@@ -16798,7 +16795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>363</v>
       </c>
@@ -16851,7 +16848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12">
         <v>364</v>
       </c>
@@ -16913,7 +16910,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>365</v>
       </c>
@@ -16966,7 +16963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>366</v>
       </c>
@@ -17019,7 +17016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:22" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>367</v>
       </c>
@@ -17083,7 +17080,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="219" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>368</v>
       </c>
@@ -17136,7 +17133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="14">
         <v>369</v>
       </c>
@@ -17196,7 +17193,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>370</v>
       </c>
@@ -17249,7 +17246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>371</v>
       </c>
@@ -17302,7 +17299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>372</v>
       </c>
@@ -17355,7 +17352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>373</v>
       </c>
@@ -17408,7 +17405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>374</v>
       </c>
@@ -17461,7 +17458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>375</v>
       </c>
@@ -17514,7 +17511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>376</v>
       </c>
@@ -17576,7 +17573,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>377</v>
       </c>
@@ -17636,7 +17633,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>378</v>
       </c>
@@ -17689,7 +17686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12">
         <v>379</v>
       </c>
@@ -17751,7 +17748,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>380</v>
       </c>
@@ -17804,7 +17801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>381</v>
       </c>
@@ -17857,7 +17854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>382</v>
       </c>
@@ -17910,7 +17907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>383</v>
       </c>
@@ -17963,7 +17960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>384</v>
       </c>
@@ -18016,7 +18013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12">
         <v>385</v>
       </c>
@@ -18078,7 +18075,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>386</v>
       </c>
@@ -18131,7 +18128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>387</v>
       </c>
@@ -18186,7 +18183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>388</v>
       </c>
@@ -18239,7 +18236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>389</v>
       </c>
@@ -18292,7 +18289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>390</v>
       </c>
@@ -18345,7 +18342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>391</v>
       </c>
@@ -18398,7 +18395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>392</v>
       </c>
@@ -18451,7 +18448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>393</v>
       </c>
@@ -18504,7 +18501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>394</v>
       </c>
@@ -18557,7 +18554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>395</v>
       </c>
@@ -18610,7 +18607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>396</v>
       </c>
@@ -18663,7 +18660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>397</v>
       </c>
@@ -18716,7 +18713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>398</v>
       </c>
@@ -18769,7 +18766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>399</v>
       </c>
@@ -18822,7 +18819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>400</v>
       </c>
@@ -18875,7 +18872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>401</v>
       </c>
@@ -18930,7 +18927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>402</v>
       </c>
@@ -18983,7 +18980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>403</v>
       </c>
@@ -19036,7 +19033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>404</v>
       </c>
@@ -19089,7 +19086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>405</v>
       </c>
@@ -19142,7 +19139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>406</v>
       </c>
@@ -19195,7 +19192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>407</v>
       </c>
@@ -19248,7 +19245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>408</v>
       </c>
@@ -19301,7 +19298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>409</v>
       </c>
@@ -19354,7 +19351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>410</v>
       </c>
@@ -19407,7 +19404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>411</v>
       </c>
@@ -19460,7 +19457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>412</v>
       </c>
@@ -19513,7 +19510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>413</v>
       </c>
@@ -19566,7 +19563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>414</v>
       </c>
@@ -19617,7 +19614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>415</v>
       </c>
@@ -19668,7 +19665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>416</v>
       </c>
@@ -19719,7 +19716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>417</v>
       </c>
@@ -19770,7 +19767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>418</v>
       </c>
@@ -19821,7 +19818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>419</v>
       </c>
@@ -19874,7 +19871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>420</v>
       </c>
@@ -19927,7 +19924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>421</v>
       </c>
@@ -19980,7 +19977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>422</v>
       </c>
@@ -20033,7 +20030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="33">
         <v>423</v>
       </c>
@@ -20093,7 +20090,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="33">
         <v>424</v>
       </c>
@@ -20153,7 +20150,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>425</v>
       </c>
@@ -20206,7 +20203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>426</v>
       </c>
@@ -20259,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:22" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:22" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>82</v>
       </c>
@@ -20312,7 +20309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>83</v>
       </c>
@@ -20365,7 +20362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>93</v>
       </c>
@@ -21206,7 +21203,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="294" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12">
         <v>14</v>
       </c>
@@ -21268,7 +21265,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="295" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>15</v>
       </c>
@@ -21321,7 +21318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>16</v>
       </c>
@@ -21374,7 +21371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>17</v>
       </c>
@@ -21427,7 +21424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>18</v>
       </c>
@@ -21480,7 +21477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>19</v>
       </c>
@@ -21533,7 +21530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>20</v>
       </c>
@@ -21586,7 +21583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>21</v>
       </c>
@@ -21639,7 +21636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>22</v>
       </c>
@@ -21692,7 +21689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>23</v>
       </c>
@@ -21745,7 +21742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>24</v>
       </c>
@@ -21798,7 +21795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>25</v>
       </c>
@@ -21851,7 +21848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>26</v>
       </c>
@@ -21904,7 +21901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>27</v>
       </c>
@@ -21957,7 +21954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>28</v>
       </c>
@@ -22010,7 +22007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>29</v>
       </c>
@@ -22063,7 +22060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>30</v>
       </c>
@@ -22116,7 +22113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>31</v>
       </c>
@@ -22167,7 +22164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>32</v>
       </c>
@@ -22220,7 +22217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>33</v>
       </c>
@@ -22271,7 +22268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>34</v>
       </c>
@@ -22324,7 +22321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="27" t="s">
         <v>486</v>
       </c>
@@ -22377,7 +22374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="27" t="s">
         <v>488</v>
       </c>
@@ -22430,7 +22427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>490</v>
       </c>
@@ -22483,7 +22480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>493</v>
       </c>
@@ -22536,7 +22533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>495</v>
       </c>
@@ -22589,7 +22586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>497</v>
       </c>
@@ -22642,7 +22639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>500</v>
       </c>
@@ -22695,7 +22692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>42</v>
       </c>
@@ -22748,7 +22745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>43</v>
       </c>
@@ -22801,7 +22798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>44</v>
       </c>
@@ -22854,7 +22851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>45</v>
       </c>
@@ -22907,7 +22904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>46</v>
       </c>
@@ -22960,7 +22957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>47</v>
       </c>
@@ -23011,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>48</v>
       </c>
@@ -23064,7 +23061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>49</v>
       </c>
@@ -23117,7 +23114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>510</v>
       </c>
@@ -23170,7 +23167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>512</v>
       </c>
@@ -23223,7 +23220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>514</v>
       </c>
@@ -23276,7 +23273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>516</v>
       </c>
@@ -23329,7 +23326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>518</v>
       </c>
@@ -23382,7 +23379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>520</v>
       </c>
@@ -23435,7 +23432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>522</v>
       </c>
@@ -23488,7 +23485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>524</v>
       </c>
@@ -23541,7 +23538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>526</v>
       </c>
@@ -23594,7 +23591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>59</v>
       </c>
@@ -23647,7 +23644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>60</v>
       </c>
@@ -23700,7 +23697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>61</v>
       </c>
@@ -23753,7 +23750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>62</v>
       </c>
@@ -23806,7 +23803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>63</v>
       </c>
@@ -23859,7 +23856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>64</v>
       </c>
@@ -23912,7 +23909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>65</v>
       </c>
@@ -23965,7 +23962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>66</v>
       </c>
@@ -24018,7 +24015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>67</v>
       </c>
@@ -24071,7 +24068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>75</v>
       </c>
@@ -24124,7 +24121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>76</v>
       </c>
@@ -24177,7 +24174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="12">
         <v>96</v>
       </c>
@@ -24241,7 +24238,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="351" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
         <v>540</v>
       </c>
@@ -24301,7 +24298,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="352" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
         <v>543</v>
       </c>
@@ -24361,7 +24358,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="353" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
         <v>545</v>
       </c>
@@ -24421,7 +24418,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="354" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="12" t="s">
         <v>547</v>
       </c>
@@ -24481,7 +24478,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="355" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
         <v>549</v>
       </c>
@@ -24541,7 +24538,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="356" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="12" t="s">
         <v>551</v>
       </c>
@@ -24601,7 +24598,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="357" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
         <v>553</v>
       </c>
@@ -24661,7 +24658,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="358" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>555</v>
       </c>
@@ -24716,7 +24713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>557</v>
       </c>
@@ -24771,7 +24768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>559</v>
       </c>
@@ -24826,7 +24823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>561</v>
       </c>
@@ -24881,7 +24878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>563</v>
       </c>
@@ -24936,7 +24933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>565</v>
       </c>
@@ -24991,7 +24988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>567</v>
       </c>
@@ -25046,7 +25043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>569</v>
       </c>
@@ -25101,7 +25098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>571</v>
       </c>
@@ -25156,7 +25153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>573</v>
       </c>
@@ -25211,7 +25208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>575</v>
       </c>
@@ -25266,7 +25263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>577</v>
       </c>
@@ -25321,7 +25318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>579</v>
       </c>
@@ -25376,7 +25373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>581</v>
       </c>
@@ -25431,7 +25428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>583</v>
       </c>
@@ -25486,7 +25483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>585</v>
       </c>
@@ -25541,7 +25538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>587</v>
       </c>
@@ -25596,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>589</v>
       </c>
@@ -25651,7 +25648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>591</v>
       </c>
@@ -25706,7 +25703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>593</v>
       </c>
@@ -25761,7 +25758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>595</v>
       </c>
@@ -25816,7 +25813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>597</v>
       </c>
@@ -25871,7 +25868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>599</v>
       </c>
@@ -25926,7 +25923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>601</v>
       </c>
@@ -25979,7 +25976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>603</v>
       </c>
@@ -26154,7 +26151,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="385" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>97</v>
       </c>
@@ -26214,7 +26211,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="386" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>98</v>
       </c>
@@ -26274,7 +26271,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="387" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>427</v>
       </c>
@@ -26327,7 +26324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>428</v>
       </c>
@@ -26380,7 +26377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>429</v>
       </c>
@@ -26433,7 +26430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>430</v>
       </c>
@@ -26486,7 +26483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>431</v>
       </c>
@@ -26539,7 +26536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>432</v>
       </c>
@@ -26592,7 +26589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>433</v>
       </c>
@@ -26645,7 +26642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>434</v>
       </c>
@@ -26698,7 +26695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>435</v>
       </c>
@@ -26751,7 +26748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>436</v>
       </c>
@@ -26804,7 +26801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>623</v>
       </c>
@@ -26857,7 +26854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>625</v>
       </c>
@@ -26910,7 +26907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>117</v>
       </c>
@@ -26963,7 +26960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="29">
         <v>109</v>
       </c>
@@ -27021,7 +27018,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="401" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>629</v>
       </c>
@@ -27074,7 +27071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>631</v>
       </c>
@@ -27127,7 +27124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>633</v>
       </c>
@@ -27180,7 +27177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>635</v>
       </c>
@@ -27233,7 +27230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>437</v>
       </c>
@@ -27286,7 +27283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>638</v>
       </c>
@@ -27339,7 +27336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>640</v>
       </c>
@@ -27392,7 +27389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>642</v>
       </c>
@@ -27445,7 +27442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>644</v>
       </c>
@@ -27498,7 +27495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>646</v>
       </c>
@@ -27551,7 +27548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>649</v>
       </c>
@@ -27604,7 +27601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>651</v>
       </c>
@@ -27657,7 +27654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>438</v>
       </c>
@@ -27710,7 +27707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>439</v>
       </c>
@@ -27763,7 +27760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>440</v>
       </c>
@@ -27816,7 +27813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>999</v>
       </c>
@@ -27869,7 +27866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>998</v>
       </c>
@@ -27922,7 +27919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>441</v>
       </c>
@@ -27975,7 +27972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>442</v>
       </c>
@@ -28028,7 +28025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>443</v>
       </c>
@@ -28081,7 +28078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>444</v>
       </c>
@@ -28134,7 +28131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>445</v>
       </c>
@@ -28187,7 +28184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>446</v>
       </c>
@@ -28240,7 +28237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>447</v>
       </c>
@@ -28293,7 +28290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>448</v>
       </c>
@@ -28346,7 +28343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>449</v>
       </c>
@@ -28399,7 +28396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>450</v>
       </c>
@@ -28452,7 +28449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>451</v>
       </c>
@@ -28505,7 +28502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>452</v>
       </c>
@@ -28558,7 +28555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>453</v>
       </c>
@@ -28611,7 +28608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>454</v>
       </c>
@@ -28664,7 +28661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>455</v>
       </c>
@@ -28717,7 +28714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>456</v>
       </c>
@@ -28772,7 +28769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>457</v>
       </c>
@@ -28827,7 +28824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>458</v>
       </c>
@@ -28880,7 +28877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>459</v>
       </c>
@@ -28933,7 +28930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>460</v>
       </c>
@@ -28995,7 +28992,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="438" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>462</v>
       </c>
@@ -29048,7 +29045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>463</v>
       </c>
@@ -29110,7 +29107,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="440" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>464</v>
       </c>
@@ -29163,7 +29160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>465</v>
       </c>
@@ -29223,7 +29220,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="442" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>466</v>
       </c>
@@ -29285,7 +29282,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="443" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>467</v>
       </c>
@@ -29338,7 +29335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>468</v>
       </c>
@@ -29391,7 +29388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>469</v>
       </c>
@@ -29444,7 +29441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>470</v>
       </c>
@@ -29497,7 +29494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>471</v>
       </c>
@@ -29550,7 +29547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>472</v>
       </c>
@@ -30182,7 +30179,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="458" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>473</v>
       </c>
@@ -30242,7 +30239,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="459" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="34" t="s">
         <v>700</v>
       </c>
@@ -30302,7 +30299,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="460" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="34" t="s">
         <v>702</v>
       </c>
@@ -30362,7 +30359,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="461" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>704</v>
       </c>
@@ -30422,7 +30419,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="462" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>706</v>
       </c>
@@ -30482,7 +30479,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="463" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>708</v>
       </c>
@@ -30542,7 +30539,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="464" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="26" t="s">
         <v>710</v>
       </c>
@@ -30604,7 +30601,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="465" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>712</v>
       </c>
@@ -30664,7 +30661,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="466" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>714</v>
       </c>
@@ -30724,7 +30721,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="467" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>716</v>
       </c>
@@ -30784,7 +30781,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="468" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>718</v>
       </c>
@@ -30844,7 +30841,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="469" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>720</v>
       </c>
@@ -30904,7 +30901,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="470" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>722</v>
       </c>
@@ -30964,7 +30961,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="471" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>724</v>
       </c>
@@ -31024,7 +31021,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="472" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>726</v>
       </c>
@@ -31084,7 +31081,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="473" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>728</v>
       </c>
@@ -31144,7 +31141,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="474" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>730</v>
       </c>
@@ -31204,7 +31201,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="475" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="27" t="s">
         <v>732</v>
       </c>
@@ -31257,7 +31254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="27" t="s">
         <v>734</v>
       </c>
@@ -31310,7 +31307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="27" t="s">
         <v>736</v>
       </c>
@@ -31363,7 +31360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="27" t="s">
         <v>738</v>
       </c>
@@ -31416,7 +31413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="27" t="s">
         <v>740</v>
       </c>
@@ -31469,7 +31466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>742</v>
       </c>
@@ -31522,7 +31519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>744</v>
       </c>
@@ -31573,7 +31570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>746</v>
       </c>
@@ -31626,7 +31623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>748</v>
       </c>
@@ -31679,7 +31676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>750</v>
       </c>
@@ -31732,7 +31729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>752</v>
       </c>
@@ -31785,7 +31782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>754</v>
       </c>
@@ -31838,7 +31835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="29">
         <v>484</v>
       </c>
@@ -31891,7 +31888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>476</v>
       </c>
@@ -31953,7 +31950,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="489" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>474</v>
       </c>
@@ -32013,7 +32010,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="490" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>525</v>
       </c>
@@ -32060,7 +32057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>795</v>
       </c>
@@ -32107,7 +32104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>797</v>
       </c>
@@ -32154,7 +32151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>799</v>
       </c>
@@ -33219,7 +33216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="29">
         <v>487</v>
       </c>
@@ -33260,9 +33257,11 @@
       <c r="R511" s="4"/>
       <c r="S511" s="4"/>
       <c r="T511" s="4"/>
-      <c r="U511" s="31"/>
-    </row>
-    <row r="512" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U511" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="29">
         <v>490</v>
       </c>
@@ -33303,9 +33302,11 @@
       <c r="R512" s="4"/>
       <c r="S512" s="4"/>
       <c r="T512" s="4"/>
-      <c r="U512" s="31"/>
-    </row>
-    <row r="513" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U512" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="29">
         <v>491</v>
       </c>
@@ -33346,9 +33347,11 @@
       <c r="R513" s="4"/>
       <c r="S513" s="4"/>
       <c r="T513" s="4"/>
-      <c r="U513" s="31"/>
-    </row>
-    <row r="514" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U513" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="29">
         <v>492</v>
       </c>
@@ -33389,9 +33392,11 @@
       <c r="R514" s="4"/>
       <c r="S514" s="4"/>
       <c r="T514" s="4"/>
-      <c r="U514" s="31"/>
-    </row>
-    <row r="515" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U514" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="29">
         <v>493</v>
       </c>
@@ -33432,9 +33437,11 @@
       <c r="R515" s="4"/>
       <c r="S515" s="4"/>
       <c r="T515" s="4"/>
-      <c r="U515" s="31"/>
-    </row>
-    <row r="516" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U515" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="29">
         <v>494</v>
       </c>
@@ -33475,9 +33482,11 @@
       <c r="R516" s="4"/>
       <c r="S516" s="4"/>
       <c r="T516" s="4"/>
-      <c r="U516" s="31"/>
-    </row>
-    <row r="517" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U516" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="29">
         <v>495</v>
       </c>
@@ -33518,9 +33527,11 @@
       <c r="R517" s="4"/>
       <c r="S517" s="4"/>
       <c r="T517" s="4"/>
-      <c r="U517" s="31"/>
-    </row>
-    <row r="518" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U517" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="29">
         <v>496</v>
       </c>
@@ -33561,9 +33572,11 @@
       <c r="R518" s="4"/>
       <c r="S518" s="4"/>
       <c r="T518" s="4"/>
-      <c r="U518" s="31"/>
-    </row>
-    <row r="519" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U518" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="29">
         <v>498</v>
       </c>
@@ -33604,9 +33617,11 @@
       <c r="R519" s="4"/>
       <c r="S519" s="4"/>
       <c r="T519" s="4"/>
-      <c r="U519" s="31"/>
-    </row>
-    <row r="520" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U519" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="29">
         <v>499</v>
       </c>
@@ -33647,9 +33662,11 @@
       <c r="R520" s="4"/>
       <c r="S520" s="4"/>
       <c r="T520" s="4"/>
-      <c r="U520" s="31"/>
-    </row>
-    <row r="521" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U520" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="29">
         <v>500</v>
       </c>
@@ -33690,9 +33707,11 @@
       <c r="R521" s="4"/>
       <c r="S521" s="4"/>
       <c r="T521" s="4"/>
-      <c r="U521" s="31"/>
-    </row>
-    <row r="522" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U521" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="29">
         <v>501</v>
       </c>
@@ -33733,9 +33752,11 @@
       <c r="R522" s="4"/>
       <c r="S522" s="4"/>
       <c r="T522" s="4"/>
-      <c r="U522" s="31"/>
-    </row>
-    <row r="523" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U522" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="29">
         <v>502</v>
       </c>
@@ -33776,9 +33797,11 @@
       <c r="R523" s="4"/>
       <c r="S523" s="4"/>
       <c r="T523" s="4"/>
-      <c r="U523" s="31"/>
-    </row>
-    <row r="524" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U523" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="29">
         <v>503</v>
       </c>
@@ -33819,9 +33842,11 @@
       <c r="R524" s="4"/>
       <c r="S524" s="4"/>
       <c r="T524" s="4"/>
-      <c r="U524" s="31"/>
-    </row>
-    <row r="525" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U524" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="29">
         <v>504</v>
       </c>
@@ -33862,9 +33887,11 @@
       <c r="R525" s="4"/>
       <c r="S525" s="4"/>
       <c r="T525" s="4"/>
-      <c r="U525" s="31"/>
-    </row>
-    <row r="526" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U525" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="29">
         <v>505</v>
       </c>
@@ -33905,9 +33932,11 @@
       <c r="R526" s="4"/>
       <c r="S526" s="4"/>
       <c r="T526" s="4"/>
-      <c r="U526" s="31"/>
-    </row>
-    <row r="527" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U526" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="29">
         <v>508</v>
       </c>
@@ -33948,9 +33977,11 @@
       <c r="R527" s="4"/>
       <c r="S527" s="4"/>
       <c r="T527" s="4"/>
-      <c r="U527" s="31"/>
-    </row>
-    <row r="528" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U527" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="29">
         <v>522</v>
       </c>
@@ -33991,9 +34022,11 @@
       <c r="R528" s="4"/>
       <c r="S528" s="4"/>
       <c r="T528" s="4"/>
-      <c r="U528" s="31"/>
-    </row>
-    <row r="529" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U528" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="29">
         <v>527</v>
       </c>
@@ -34034,9 +34067,11 @@
       <c r="R529" s="4"/>
       <c r="S529" s="4"/>
       <c r="T529" s="4"/>
-      <c r="U529" s="31"/>
-    </row>
-    <row r="530" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U529" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="29">
         <v>528</v>
       </c>
@@ -34079,9 +34114,11 @@
       <c r="R530" s="4"/>
       <c r="S530" s="4"/>
       <c r="T530" s="4"/>
-      <c r="U530" s="31"/>
-    </row>
-    <row r="531" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U530" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="29">
         <v>541</v>
       </c>
@@ -34124,9 +34161,11 @@
       <c r="R531" s="4"/>
       <c r="S531" s="4"/>
       <c r="T531" s="4"/>
-      <c r="U531" s="31"/>
-    </row>
-    <row r="532" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U531" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="29">
         <v>542</v>
       </c>
@@ -34169,9 +34208,11 @@
       <c r="R532" s="4"/>
       <c r="S532" s="4"/>
       <c r="T532" s="4"/>
-      <c r="U532" s="31"/>
-    </row>
-    <row r="533" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U532" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="29">
         <v>546</v>
       </c>
@@ -34214,9 +34255,11 @@
       <c r="R533" s="4"/>
       <c r="S533" s="4"/>
       <c r="T533" s="4"/>
-      <c r="U533" s="31"/>
-    </row>
-    <row r="534" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U533" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="29">
         <v>547</v>
       </c>
@@ -34259,9 +34302,11 @@
       <c r="R534" s="4"/>
       <c r="S534" s="4"/>
       <c r="T534" s="4"/>
-      <c r="U534" s="31"/>
-    </row>
-    <row r="535" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U534" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="29">
         <v>552</v>
       </c>
@@ -34302,9 +34347,11 @@
       <c r="R535" s="4"/>
       <c r="S535" s="4"/>
       <c r="T535" s="4"/>
-      <c r="U535" s="31"/>
-    </row>
-    <row r="536" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U535" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="29">
         <v>553</v>
       </c>
@@ -34345,9 +34392,11 @@
       <c r="R536" s="4"/>
       <c r="S536" s="4"/>
       <c r="T536" s="4"/>
-      <c r="U536" s="31"/>
-    </row>
-    <row r="537" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U536" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="29">
         <v>556</v>
       </c>
@@ -34388,9 +34437,11 @@
       <c r="R537" s="4"/>
       <c r="S537" s="4"/>
       <c r="T537" s="4"/>
-      <c r="U537" s="31"/>
-    </row>
-    <row r="538" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U537" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="29">
         <v>485</v>
       </c>
@@ -34431,9 +34482,11 @@
       <c r="R538" s="4"/>
       <c r="S538" s="4"/>
       <c r="T538" s="4"/>
-      <c r="U538" s="31"/>
-    </row>
-    <row r="539" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U538" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="29">
         <v>488</v>
       </c>
@@ -34474,9 +34527,11 @@
       <c r="R539" s="4"/>
       <c r="S539" s="4"/>
       <c r="T539" s="4"/>
-      <c r="U539" s="31"/>
-    </row>
-    <row r="540" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U539" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="29">
         <v>509</v>
       </c>
@@ -34517,9 +34572,11 @@
       <c r="R540" s="4"/>
       <c r="S540" s="4"/>
       <c r="T540" s="4"/>
-      <c r="U540" s="31"/>
-    </row>
-    <row r="541" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U540" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="29">
         <v>475</v>
       </c>
@@ -34560,9 +34617,11 @@
       <c r="R541" s="4"/>
       <c r="S541" s="4"/>
       <c r="T541" s="4"/>
-      <c r="U541" s="31"/>
-    </row>
-    <row r="542" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U541" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="29">
         <v>477</v>
       </c>
@@ -34603,9 +34662,11 @@
       <c r="R542" s="4"/>
       <c r="S542" s="4"/>
       <c r="T542" s="4"/>
-      <c r="U542" s="31"/>
-    </row>
-    <row r="543" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U542" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="29">
         <v>478</v>
       </c>
@@ -34646,9 +34707,11 @@
       <c r="R543" s="4"/>
       <c r="S543" s="4"/>
       <c r="T543" s="4"/>
-      <c r="U543" s="31"/>
-    </row>
-    <row r="544" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U543" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="29">
         <v>479</v>
       </c>
@@ -34689,9 +34752,11 @@
       <c r="R544" s="4"/>
       <c r="S544" s="4"/>
       <c r="T544" s="4"/>
-      <c r="U544" s="31"/>
-    </row>
-    <row r="545" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U544" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="29">
         <v>480</v>
       </c>
@@ -34732,9 +34797,11 @@
       <c r="R545" s="4"/>
       <c r="S545" s="4"/>
       <c r="T545" s="4"/>
-      <c r="U545" s="31"/>
-    </row>
-    <row r="546" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U545" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="29">
         <v>481</v>
       </c>
@@ -34775,9 +34842,11 @@
       <c r="R546" s="4"/>
       <c r="S546" s="4"/>
       <c r="T546" s="4"/>
-      <c r="U546" s="31"/>
-    </row>
-    <row r="547" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U546" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="29">
         <v>486</v>
       </c>
@@ -34818,9 +34887,11 @@
       <c r="R547" s="4"/>
       <c r="S547" s="4"/>
       <c r="T547" s="4"/>
-      <c r="U547" s="31"/>
-    </row>
-    <row r="548" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U547" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="29">
         <v>506</v>
       </c>
@@ -34861,9 +34932,11 @@
       <c r="R548" s="4"/>
       <c r="S548" s="4"/>
       <c r="T548" s="4"/>
-      <c r="U548" s="31"/>
-    </row>
-    <row r="549" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U548" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="29">
         <v>507</v>
       </c>
@@ -34904,9 +34977,11 @@
       <c r="R549" s="4"/>
       <c r="S549" s="4"/>
       <c r="T549" s="4"/>
-      <c r="U549" s="31"/>
-    </row>
-    <row r="550" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U549" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="29">
         <v>514</v>
       </c>
@@ -34947,9 +35022,11 @@
       <c r="R550" s="4"/>
       <c r="S550" s="4"/>
       <c r="T550" s="4"/>
-      <c r="U550" s="31"/>
-    </row>
-    <row r="551" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U550" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="29">
         <v>515</v>
       </c>
@@ -34990,9 +35067,11 @@
       <c r="R551" s="4"/>
       <c r="S551" s="4"/>
       <c r="T551" s="4"/>
-      <c r="U551" s="31"/>
-    </row>
-    <row r="552" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U551" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="29">
         <v>516</v>
       </c>
@@ -35033,9 +35112,11 @@
       <c r="R552" s="4"/>
       <c r="S552" s="4"/>
       <c r="T552" s="4"/>
-      <c r="U552" s="31"/>
-    </row>
-    <row r="553" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U552" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="29">
         <v>519</v>
       </c>
@@ -35076,9 +35157,11 @@
       <c r="R553" s="4"/>
       <c r="S553" s="4"/>
       <c r="T553" s="4"/>
-      <c r="U553" s="31"/>
-    </row>
-    <row r="554" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U553" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="29">
         <v>523</v>
       </c>
@@ -35119,9 +35202,11 @@
       <c r="R554" s="4"/>
       <c r="S554" s="4"/>
       <c r="T554" s="4"/>
-      <c r="U554" s="31"/>
-    </row>
-    <row r="555" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U554" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="29">
         <v>524</v>
       </c>
@@ -35164,9 +35249,11 @@
       <c r="R555" s="4"/>
       <c r="S555" s="4"/>
       <c r="T555" s="4"/>
-      <c r="U555" s="31"/>
-    </row>
-    <row r="556" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U555" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="29">
         <v>530</v>
       </c>
@@ -35207,9 +35294,11 @@
       <c r="R556" s="4"/>
       <c r="S556" s="4"/>
       <c r="T556" s="4"/>
-      <c r="U556" s="31"/>
-    </row>
-    <row r="557" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U556" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="29">
         <v>531</v>
       </c>
@@ -35250,9 +35339,11 @@
       <c r="R557" s="4"/>
       <c r="S557" s="4"/>
       <c r="T557" s="4"/>
-      <c r="U557" s="31"/>
-    </row>
-    <row r="558" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U557" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="29">
         <v>532</v>
       </c>
@@ -35295,9 +35386,11 @@
       <c r="R558" s="4"/>
       <c r="S558" s="4"/>
       <c r="T558" s="4"/>
-      <c r="U558" s="31"/>
-    </row>
-    <row r="559" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U558" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="29">
         <v>533</v>
       </c>
@@ -35340,9 +35433,11 @@
       <c r="R559" s="4"/>
       <c r="S559" s="4"/>
       <c r="T559" s="4"/>
-      <c r="U559" s="31"/>
-    </row>
-    <row r="560" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U559" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="29">
         <v>534</v>
       </c>
@@ -35385,9 +35480,11 @@
       <c r="R560" s="4"/>
       <c r="S560" s="4"/>
       <c r="T560" s="4"/>
-      <c r="U560" s="31"/>
-    </row>
-    <row r="561" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U560" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="29">
         <v>535</v>
       </c>
@@ -35430,9 +35527,11 @@
       <c r="R561" s="4"/>
       <c r="S561" s="4"/>
       <c r="T561" s="4"/>
-      <c r="U561" s="31"/>
-    </row>
-    <row r="562" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U561" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="29">
         <v>536</v>
       </c>
@@ -35475,9 +35574,11 @@
       <c r="R562" s="4"/>
       <c r="S562" s="4"/>
       <c r="T562" s="4"/>
-      <c r="U562" s="31"/>
-    </row>
-    <row r="563" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U562" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="29">
         <v>537</v>
       </c>
@@ -35518,9 +35619,11 @@
       <c r="R563" s="4"/>
       <c r="S563" s="4"/>
       <c r="T563" s="4"/>
-      <c r="U563" s="31"/>
-    </row>
-    <row r="564" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U563" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="29">
         <v>538</v>
       </c>
@@ -35561,9 +35664,11 @@
       <c r="R564" s="4"/>
       <c r="S564" s="4"/>
       <c r="T564" s="4"/>
-      <c r="U564" s="31"/>
-    </row>
-    <row r="565" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U564" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="29">
         <v>539</v>
       </c>
@@ -35604,9 +35709,11 @@
       <c r="R565" s="4"/>
       <c r="S565" s="4"/>
       <c r="T565" s="4"/>
-      <c r="U565" s="31"/>
-    </row>
-    <row r="566" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U565" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="29">
         <v>540</v>
       </c>
@@ -35647,9 +35754,11 @@
       <c r="R566" s="4"/>
       <c r="S566" s="4"/>
       <c r="T566" s="4"/>
-      <c r="U566" s="31"/>
-    </row>
-    <row r="567" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U566" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="29">
         <v>543</v>
       </c>
@@ -35690,9 +35799,11 @@
       <c r="R567" s="4"/>
       <c r="S567" s="4"/>
       <c r="T567" s="4"/>
-      <c r="U567" s="31"/>
-    </row>
-    <row r="568" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U567" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="29">
         <v>544</v>
       </c>
@@ -35735,9 +35846,11 @@
       <c r="R568" s="4"/>
       <c r="S568" s="4"/>
       <c r="T568" s="4"/>
-      <c r="U568" s="31"/>
-    </row>
-    <row r="569" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U568" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="29">
         <v>550</v>
       </c>
@@ -35778,9 +35891,11 @@
       <c r="R569" s="4"/>
       <c r="S569" s="4"/>
       <c r="T569" s="4"/>
-      <c r="U569" s="31"/>
-    </row>
-    <row r="570" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U569" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="29">
         <v>551</v>
       </c>
@@ -35821,9 +35936,11 @@
       <c r="R570" s="4"/>
       <c r="S570" s="4"/>
       <c r="T570" s="4"/>
-      <c r="U570" s="31"/>
-    </row>
-    <row r="571" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U570" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="29">
         <v>554</v>
       </c>
@@ -35864,9 +35981,11 @@
       <c r="R571" s="4"/>
       <c r="S571" s="4"/>
       <c r="T571" s="4"/>
-      <c r="U571" s="31"/>
-    </row>
-    <row r="572" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U571" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="29">
         <v>555</v>
       </c>
@@ -35907,9 +36026,11 @@
       <c r="R572" s="4"/>
       <c r="S572" s="4"/>
       <c r="T572" s="4"/>
-      <c r="U572" s="31"/>
-    </row>
-    <row r="573" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U572" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="29">
         <v>510</v>
       </c>
@@ -35950,9 +36071,11 @@
       <c r="R573" s="4"/>
       <c r="S573" s="4"/>
       <c r="T573" s="4"/>
-      <c r="U573" s="31"/>
-    </row>
-    <row r="574" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U573" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="29">
         <v>511</v>
       </c>
@@ -35993,9 +36116,11 @@
       <c r="R574" s="4"/>
       <c r="S574" s="4"/>
       <c r="T574" s="4"/>
-      <c r="U574" s="31"/>
-    </row>
-    <row r="575" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U574" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="29">
         <v>513</v>
       </c>
@@ -36036,9 +36161,11 @@
       <c r="R575" s="4"/>
       <c r="S575" s="4"/>
       <c r="T575" s="4"/>
-      <c r="U575" s="31"/>
-    </row>
-    <row r="576" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U575" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="29">
         <v>518</v>
       </c>
@@ -36079,9 +36206,11 @@
       <c r="R576" s="4"/>
       <c r="S576" s="4"/>
       <c r="T576" s="4"/>
-      <c r="U576" s="31"/>
-    </row>
-    <row r="577" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U576" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="29">
         <v>526</v>
       </c>
@@ -36122,9 +36251,11 @@
       <c r="R577" s="4"/>
       <c r="S577" s="4"/>
       <c r="T577" s="4"/>
-      <c r="U577" s="31"/>
-    </row>
-    <row r="578" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U577" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="29">
         <v>529</v>
       </c>
@@ -36165,10 +36296,19 @@
       <c r="R578" s="4"/>
       <c r="S578" s="4"/>
       <c r="T578" s="4"/>
-      <c r="U578" s="31"/>
+      <c r="U578" s="31">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:V578" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="20">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
@@ -37183,6 +37323,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37417,27 +37577,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37454,23 +37613,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2250" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC68B6D-C7E8-435A-B847-3D5C8B60D939}"/>
+  <xr:revisionPtr revIDLastSave="2338" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A426938-EF02-4BC9-A198-FFC240C3553C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$C$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$V$578</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$V$581</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5601" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5637" uniqueCount="935">
   <si>
     <t>Linea</t>
   </si>
@@ -1402,9 +1402,6 @@
     <t>% avance plan de implementación</t>
   </si>
   <si>
-    <t>Innovación curricular - Fase I</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -1420,9 +1417,6 @@
     <t>Equidad de Genero</t>
   </si>
   <si>
-    <t>Portal Universitario</t>
-  </si>
-  <si>
     <t>Data Lake Institucional</t>
   </si>
   <si>
@@ -2123,9 +2117,6 @@
   </si>
   <si>
     <t>Característica 31: Experiencia del estudiante</t>
-  </si>
-  <si>
-    <t>CREA Centro de Recursos y Experiencias para el aprendizaje - Fase de Adecuación</t>
   </si>
   <si>
     <t>Ecosistema E3</t>
@@ -3118,12 +3109,6 @@
     <t>Herramientas de Gestión para el mejoramiento continuo</t>
   </si>
   <si>
-    <t>Proyectos Ilumno Self Service S&amp;P</t>
-  </si>
-  <si>
-    <t>Reingenia de aplicaciones</t>
-  </si>
-  <si>
     <t>SOPHIA Sistema de optimización y programación horaria institucional</t>
   </si>
   <si>
@@ -3501,6 +3486,30 @@
   </si>
   <si>
     <t>Plan anual</t>
+  </si>
+  <si>
+    <t>CREA Centro de Recursos y Experiencias para el aprendizaje</t>
+  </si>
+  <si>
+    <t>Innovación curricular</t>
+  </si>
+  <si>
+    <t>Fortalecimiento del proceso de visibilidad nacional e internacional</t>
+  </si>
+  <si>
+    <t>Sistema de medición de resultados de aprendizaje</t>
+  </si>
+  <si>
+    <t>Portal Web Universitario</t>
+  </si>
+  <si>
+    <t>Ilumno Self Service S&amp;P</t>
+  </si>
+  <si>
+    <t>Titulación Autogestionada</t>
+  </si>
+  <si>
+    <t>Reingeniería de aplicaciones</t>
   </si>
 </sst>
 </file>
@@ -3932,7 +3941,127 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{B753E483-50E8-4755-BA53-9118C26C170F}"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{ADCD9E6A-B374-41A4-9E99-CB4D3005E09B}"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="99">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5183,8 +5312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:V578"/>
+  <dimension ref="A1:V581"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -5254,7 +5382,7 @@
         <v>60</v>
       </c>
       <c r="P1" s="51" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>61</v>
@@ -5266,7 +5394,7 @@
         <v>63</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>64</v>
@@ -5275,7 +5403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>68</v>
       </c>
@@ -5328,7 +5456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>69</v>
       </c>
@@ -5381,7 +5509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>73</v>
       </c>
@@ -5434,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>74</v>
       </c>
@@ -5487,7 +5615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>77</v>
       </c>
@@ -5549,7 +5677,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>78</v>
       </c>
@@ -5575,7 +5703,7 @@
         <v>45</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>89</v>
@@ -5604,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>79</v>
       </c>
@@ -5657,7 +5785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>84</v>
       </c>
@@ -5710,7 +5838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>85</v>
       </c>
@@ -5763,7 +5891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>86</v>
       </c>
@@ -5816,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>87</v>
       </c>
@@ -5869,7 +5997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>88</v>
       </c>
@@ -5922,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>89</v>
       </c>
@@ -5975,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>90</v>
       </c>
@@ -6028,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>91</v>
       </c>
@@ -6081,7 +6209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>92</v>
       </c>
@@ -6134,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>94</v>
       </c>
@@ -6187,7 +6315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>95</v>
       </c>
@@ -6240,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>100</v>
       </c>
@@ -6293,7 +6421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>104</v>
       </c>
@@ -6346,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>106</v>
       </c>
@@ -6399,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>108</v>
       </c>
@@ -6452,7 +6580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>110</v>
       </c>
@@ -6505,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>111</v>
       </c>
@@ -6558,7 +6686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>112</v>
       </c>
@@ -6611,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>113</v>
       </c>
@@ -6664,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>114</v>
       </c>
@@ -6717,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>115</v>
       </c>
@@ -6770,7 +6898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>116</v>
       </c>
@@ -6823,7 +6951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>118</v>
       </c>
@@ -6876,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>121</v>
       </c>
@@ -6929,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>122</v>
       </c>
@@ -6982,7 +7110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>124</v>
       </c>
@@ -7035,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>125</v>
       </c>
@@ -7088,7 +7216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>126</v>
       </c>
@@ -7141,7 +7269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>127</v>
       </c>
@@ -7194,7 +7322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>128</v>
       </c>
@@ -7247,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>133</v>
       </c>
@@ -7300,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>136</v>
       </c>
@@ -7353,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>137</v>
       </c>
@@ -7406,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>139</v>
       </c>
@@ -7459,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>143</v>
       </c>
@@ -7514,7 +7642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>144</v>
       </c>
@@ -7569,7 +7697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>145</v>
       </c>
@@ -7622,7 +7750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>146</v>
       </c>
@@ -7675,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>147</v>
       </c>
@@ -7730,7 +7858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>148</v>
       </c>
@@ -7792,7 +7920,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>150</v>
       </c>
@@ -7845,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>151</v>
       </c>
@@ -7898,7 +8026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>157</v>
       </c>
@@ -7951,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>159</v>
       </c>
@@ -8004,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>167</v>
       </c>
@@ -8057,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>171</v>
       </c>
@@ -8110,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>172</v>
       </c>
@@ -8165,7 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>174</v>
       </c>
@@ -8218,7 +8346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>176</v>
       </c>
@@ -8244,7 +8372,7 @@
         <v>45</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>89</v>
@@ -8273,7 +8401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>193</v>
       </c>
@@ -8335,7 +8463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>194</v>
       </c>
@@ -8397,7 +8525,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>195</v>
       </c>
@@ -8452,7 +8580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>196</v>
       </c>
@@ -8505,7 +8633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>197</v>
       </c>
@@ -8558,7 +8686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>199</v>
       </c>
@@ -8611,7 +8739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>200</v>
       </c>
@@ -8671,7 +8799,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>202</v>
       </c>
@@ -8733,7 +8861,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>203</v>
       </c>
@@ -8795,7 +8923,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>204</v>
       </c>
@@ -8857,7 +8985,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>205</v>
       </c>
@@ -8917,7 +9045,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>206</v>
       </c>
@@ -8977,7 +9105,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>207</v>
       </c>
@@ -9037,7 +9165,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>208</v>
       </c>
@@ -9090,7 +9218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>210</v>
       </c>
@@ -9143,7 +9271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>213</v>
       </c>
@@ -9196,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>214</v>
       </c>
@@ -9249,7 +9377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>215</v>
       </c>
@@ -9302,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>216</v>
       </c>
@@ -9355,7 +9483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>217</v>
       </c>
@@ -9408,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>218</v>
       </c>
@@ -9461,7 +9589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>219</v>
       </c>
@@ -9514,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>220</v>
       </c>
@@ -9567,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>221</v>
       </c>
@@ -9620,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>222</v>
       </c>
@@ -9673,7 +9801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>223</v>
       </c>
@@ -9726,7 +9854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>224</v>
       </c>
@@ -9779,7 +9907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>225</v>
       </c>
@@ -9832,7 +9960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>226</v>
       </c>
@@ -9885,7 +10013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>227</v>
       </c>
@@ -9938,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>228</v>
       </c>
@@ -9998,7 +10126,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>230</v>
       </c>
@@ -10051,7 +10179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>231</v>
       </c>
@@ -10104,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>232</v>
       </c>
@@ -10157,7 +10285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>233</v>
       </c>
@@ -10210,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>234</v>
       </c>
@@ -10263,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>235</v>
       </c>
@@ -10316,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>236</v>
       </c>
@@ -10369,7 +10497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>237</v>
       </c>
@@ -10424,7 +10552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>238</v>
       </c>
@@ -10477,7 +10605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>239</v>
       </c>
@@ -10530,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>240</v>
       </c>
@@ -10556,7 +10684,7 @@
         <v>45</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>71</v>
@@ -10585,7 +10713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>241</v>
       </c>
@@ -10638,7 +10766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>242</v>
       </c>
@@ -10691,7 +10819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>243</v>
       </c>
@@ -10744,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>244</v>
       </c>
@@ -10804,7 +10932,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="104" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>245</v>
       </c>
@@ -10868,7 +10996,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>246</v>
       </c>
@@ -10919,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>247</v>
       </c>
@@ -10972,7 +11100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>248</v>
       </c>
@@ -11030,7 +11158,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>249</v>
       </c>
@@ -11090,7 +11218,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>254</v>
       </c>
@@ -11143,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>251</v>
       </c>
@@ -11198,7 +11326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>252</v>
       </c>
@@ -11253,7 +11381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>253</v>
       </c>
@@ -11306,7 +11434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>255</v>
       </c>
@@ -11359,7 +11487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>256</v>
       </c>
@@ -11412,7 +11540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>257</v>
       </c>
@@ -11465,7 +11593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>259</v>
       </c>
@@ -11491,7 +11619,7 @@
         <v>45</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>71</v>
@@ -11520,7 +11648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>260</v>
       </c>
@@ -11573,7 +11701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>261</v>
       </c>
@@ -11626,7 +11754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>262</v>
       </c>
@@ -11679,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>263</v>
       </c>
@@ -11732,7 +11860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>264</v>
       </c>
@@ -11785,7 +11913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>265</v>
       </c>
@@ -11838,7 +11966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>266</v>
       </c>
@@ -11891,7 +12019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>267</v>
       </c>
@@ -11944,7 +12072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>268</v>
       </c>
@@ -11997,7 +12125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>269</v>
       </c>
@@ -12050,7 +12178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>270</v>
       </c>
@@ -12103,7 +12231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>271</v>
       </c>
@@ -12156,7 +12284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>272</v>
       </c>
@@ -12209,7 +12337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>273</v>
       </c>
@@ -12262,7 +12390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A131" s="12">
         <v>274</v>
       </c>
@@ -12324,7 +12452,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="132" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>275</v>
       </c>
@@ -12377,7 +12505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A133" s="14">
         <v>276</v>
       </c>
@@ -12441,7 +12569,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>277</v>
       </c>
@@ -12500,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>278</v>
       </c>
@@ -12553,7 +12681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>279</v>
       </c>
@@ -12606,7 +12734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>280</v>
       </c>
@@ -12659,7 +12787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>281</v>
       </c>
@@ -12712,7 +12840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>282</v>
       </c>
@@ -12765,7 +12893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>283</v>
       </c>
@@ -12820,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>284</v>
       </c>
@@ -12873,7 +13001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>285</v>
       </c>
@@ -12926,7 +13054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>286</v>
       </c>
@@ -12981,7 +13109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>287</v>
       </c>
@@ -13034,7 +13162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>288</v>
       </c>
@@ -13087,7 +13215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>289</v>
       </c>
@@ -13140,7 +13268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>290</v>
       </c>
@@ -13193,7 +13321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>291</v>
       </c>
@@ -13246,7 +13374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>292</v>
       </c>
@@ -13301,7 +13429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>293</v>
       </c>
@@ -13354,7 +13482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>294</v>
       </c>
@@ -13409,7 +13537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>295</v>
       </c>
@@ -13462,7 +13590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>296</v>
       </c>
@@ -13515,7 +13643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>297</v>
       </c>
@@ -13568,7 +13696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>298</v>
       </c>
@@ -13621,7 +13749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>300</v>
       </c>
@@ -13674,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>301</v>
       </c>
@@ -13727,7 +13855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>302</v>
       </c>
@@ -13780,7 +13908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>303</v>
       </c>
@@ -13833,7 +13961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>304</v>
       </c>
@@ -13886,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>305</v>
       </c>
@@ -13939,7 +14067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>306</v>
       </c>
@@ -13965,7 +14093,7 @@
         <v>45</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>71</v>
@@ -13994,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>307</v>
       </c>
@@ -14047,7 +14175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>308</v>
       </c>
@@ -14100,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>309</v>
       </c>
@@ -14153,7 +14281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>310</v>
       </c>
@@ -14206,7 +14334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>311</v>
       </c>
@@ -14259,7 +14387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>312</v>
       </c>
@@ -14312,7 +14440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>313</v>
       </c>
@@ -14365,7 +14493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>314</v>
       </c>
@@ -14418,7 +14546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>315</v>
       </c>
@@ -14471,7 +14599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>316</v>
       </c>
@@ -14524,7 +14652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>317</v>
       </c>
@@ -14577,7 +14705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>318</v>
       </c>
@@ -14630,7 +14758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>319</v>
       </c>
@@ -14683,7 +14811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>320</v>
       </c>
@@ -14736,7 +14864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>321</v>
       </c>
@@ -14789,7 +14917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A178" s="12">
         <v>323</v>
       </c>
@@ -14853,7 +14981,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>324</v>
       </c>
@@ -14906,7 +15034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A180" s="12">
         <v>325</v>
       </c>
@@ -14970,7 +15098,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="181" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>326</v>
       </c>
@@ -15023,7 +15151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A182" s="12">
         <v>327</v>
       </c>
@@ -15080,7 +15208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>328</v>
       </c>
@@ -15133,7 +15261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>329</v>
       </c>
@@ -15186,7 +15314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>331</v>
       </c>
@@ -15246,7 +15374,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="186" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A186" s="12">
         <v>332</v>
       </c>
@@ -15308,7 +15436,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="187" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>334</v>
       </c>
@@ -15372,7 +15500,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="188" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>335</v>
       </c>
@@ -15430,7 +15558,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>336</v>
       </c>
@@ -15483,7 +15611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>337</v>
       </c>
@@ -15536,7 +15664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>338</v>
       </c>
@@ -15593,7 +15721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>339</v>
       </c>
@@ -15657,7 +15785,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="193" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>340</v>
       </c>
@@ -15710,7 +15838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>341</v>
       </c>
@@ -15763,7 +15891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>344</v>
       </c>
@@ -15816,7 +15944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A196" s="32">
         <v>345</v>
       </c>
@@ -15878,7 +16006,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="197" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>346</v>
       </c>
@@ -15931,7 +16059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>347</v>
       </c>
@@ -15984,7 +16112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>348</v>
       </c>
@@ -16037,7 +16165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>349</v>
       </c>
@@ -16090,7 +16218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>350</v>
       </c>
@@ -16143,7 +16271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>351</v>
       </c>
@@ -16196,7 +16324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>352</v>
       </c>
@@ -16249,7 +16377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A204" s="32">
         <v>353</v>
       </c>
@@ -16309,7 +16437,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="205" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>354</v>
       </c>
@@ -16362,7 +16490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>355</v>
       </c>
@@ -16415,7 +16543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>356</v>
       </c>
@@ -16468,7 +16596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>357</v>
       </c>
@@ -16521,7 +16649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>358</v>
       </c>
@@ -16574,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>359</v>
       </c>
@@ -16627,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>360</v>
       </c>
@@ -16680,12 +16808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:22" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>361</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>81</v>
@@ -16742,7 +16870,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="213" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>362</v>
       </c>
@@ -16753,7 +16881,7 @@
         <v>67</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>69</v>
@@ -16795,7 +16923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>363</v>
       </c>
@@ -16806,7 +16934,7 @@
         <v>67</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>69</v>
@@ -16848,7 +16976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A215" s="12">
         <v>364</v>
       </c>
@@ -16910,7 +17038,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="216" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>365</v>
       </c>
@@ -16921,7 +17049,7 @@
         <v>81</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>69</v>
@@ -16963,7 +17091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>366</v>
       </c>
@@ -16974,7 +17102,7 @@
         <v>67</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E217" s="4" t="s">
         <v>94</v>
@@ -17016,7 +17144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:22" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>367</v>
       </c>
@@ -17080,7 +17208,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="219" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>368</v>
       </c>
@@ -17133,7 +17261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A220" s="14">
         <v>369</v>
       </c>
@@ -17193,7 +17321,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>370</v>
       </c>
@@ -17246,7 +17374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>371</v>
       </c>
@@ -17299,7 +17427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>372</v>
       </c>
@@ -17352,7 +17480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>373</v>
       </c>
@@ -17405,7 +17533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>374</v>
       </c>
@@ -17416,7 +17544,7 @@
         <v>67</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>69</v>
@@ -17458,7 +17586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>375</v>
       </c>
@@ -17469,7 +17597,7 @@
         <v>67</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>69</v>
@@ -17511,7 +17639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>376</v>
       </c>
@@ -17573,7 +17701,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="228" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>377</v>
       </c>
@@ -17633,7 +17761,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="229" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>378</v>
       </c>
@@ -17686,7 +17814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A230" s="12">
         <v>379</v>
       </c>
@@ -17748,7 +17876,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="231" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>380</v>
       </c>
@@ -17801,7 +17929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>381</v>
       </c>
@@ -17854,7 +17982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>382</v>
       </c>
@@ -17907,7 +18035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>383</v>
       </c>
@@ -17960,7 +18088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>384</v>
       </c>
@@ -18013,7 +18141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A236" s="12">
         <v>385</v>
       </c>
@@ -18075,7 +18203,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="237" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>386</v>
       </c>
@@ -18128,7 +18256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>387</v>
       </c>
@@ -18183,7 +18311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>388</v>
       </c>
@@ -18236,7 +18364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>389</v>
       </c>
@@ -18289,7 +18417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>390</v>
       </c>
@@ -18342,7 +18470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>391</v>
       </c>
@@ -18395,7 +18523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>392</v>
       </c>
@@ -18448,7 +18576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>393</v>
       </c>
@@ -18501,7 +18629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>394</v>
       </c>
@@ -18554,7 +18682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>395</v>
       </c>
@@ -18607,7 +18735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>396</v>
       </c>
@@ -18660,7 +18788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>397</v>
       </c>
@@ -18713,7 +18841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>398</v>
       </c>
@@ -18766,7 +18894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>399</v>
       </c>
@@ -18819,7 +18947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>400</v>
       </c>
@@ -18872,7 +19000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>401</v>
       </c>
@@ -18927,7 +19055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>402</v>
       </c>
@@ -18980,7 +19108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>403</v>
       </c>
@@ -19033,7 +19161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>404</v>
       </c>
@@ -19086,7 +19214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>405</v>
       </c>
@@ -19139,7 +19267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>406</v>
       </c>
@@ -19192,7 +19320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>407</v>
       </c>
@@ -19245,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>408</v>
       </c>
@@ -19298,7 +19426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>409</v>
       </c>
@@ -19351,7 +19479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>410</v>
       </c>
@@ -19404,7 +19532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>411</v>
       </c>
@@ -19457,7 +19585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>412</v>
       </c>
@@ -19510,7 +19638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>413</v>
       </c>
@@ -19563,7 +19691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>414</v>
       </c>
@@ -19614,7 +19742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>415</v>
       </c>
@@ -19665,7 +19793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>416</v>
       </c>
@@ -19716,7 +19844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>417</v>
       </c>
@@ -19767,7 +19895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>418</v>
       </c>
@@ -19818,7 +19946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>419</v>
       </c>
@@ -19871,7 +19999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>420</v>
       </c>
@@ -19924,7 +20052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>421</v>
       </c>
@@ -19977,7 +20105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>422</v>
       </c>
@@ -20030,7 +20158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A274" s="33">
         <v>423</v>
       </c>
@@ -20090,7 +20218,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="275" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A275" s="33">
         <v>424</v>
       </c>
@@ -20150,7 +20278,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="276" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>425</v>
       </c>
@@ -20203,7 +20331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>426</v>
       </c>
@@ -20256,7 +20384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:22" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:22" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>82</v>
       </c>
@@ -20309,7 +20437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>83</v>
       </c>
@@ -20362,7 +20490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>93</v>
       </c>
@@ -20419,8 +20547,8 @@
       <c r="A281" s="4">
         <v>1</v>
       </c>
-      <c r="B281" s="13" t="s">
-        <v>452</v>
+      <c r="B281" s="12" t="s">
+        <v>928</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>81</v>
@@ -20472,15 +20600,15 @@
         <v>1</v>
       </c>
       <c r="V281" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>2</v>
       </c>
-      <c r="B282" s="13" t="s">
-        <v>454</v>
+      <c r="B282" s="12" t="s">
+        <v>453</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>81</v>
@@ -20534,15 +20662,15 @@
         <v>1</v>
       </c>
       <c r="V282" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>3</v>
       </c>
-      <c r="B283" s="13" t="s">
-        <v>455</v>
+      <c r="B283" s="12" t="s">
+        <v>454</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>81</v>
@@ -20596,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="V283" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.3">
@@ -20604,7 +20732,7 @@
         <v>4</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>81</v>
@@ -20658,7 +20786,7 @@
         <v>1</v>
       </c>
       <c r="V284" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.3">
@@ -20666,7 +20794,7 @@
         <v>5</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>81</v>
@@ -20718,8 +20846,8 @@
       <c r="A286" s="12">
         <v>6</v>
       </c>
-      <c r="B286" s="13" t="s">
-        <v>458</v>
+      <c r="B286" s="12" t="s">
+        <v>931</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>81</v>
@@ -20773,15 +20901,15 @@
         <v>1</v>
       </c>
       <c r="V286" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A287" s="12">
         <v>7</v>
       </c>
-      <c r="B287" s="13" t="s">
-        <v>459</v>
+      <c r="B287" s="12" t="s">
+        <v>457</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>81</v>
@@ -20835,15 +20963,15 @@
         <v>1</v>
       </c>
       <c r="V287" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="288" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>8</v>
       </c>
-      <c r="B288" s="13" t="s">
-        <v>460</v>
+      <c r="B288" s="12" t="s">
+        <v>458</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>81</v>
@@ -20895,8 +21023,8 @@
       <c r="A289" s="12">
         <v>9</v>
       </c>
-      <c r="B289" s="13" t="s">
-        <v>461</v>
+      <c r="B289" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>81</v>
@@ -20950,15 +21078,15 @@
         <v>1</v>
       </c>
       <c r="V289" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="290" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="12">
         <v>10</v>
       </c>
-      <c r="B290" s="13" t="s">
-        <v>462</v>
+      <c r="B290" s="12" t="s">
+        <v>460</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>81</v>
@@ -21014,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="V290" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="291" spans="1:22" x14ac:dyDescent="0.3">
@@ -21022,7 +21150,7 @@
         <v>11</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>81</v>
@@ -21078,7 +21206,7 @@
         <v>1</v>
       </c>
       <c r="V291" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="292" spans="1:22" x14ac:dyDescent="0.3">
@@ -21086,7 +21214,7 @@
         <v>12</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>81</v>
@@ -21138,7 +21266,7 @@
         <v>1</v>
       </c>
       <c r="V292" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="293" spans="1:22" x14ac:dyDescent="0.3">
@@ -21146,7 +21274,7 @@
         <v>13</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>81</v>
@@ -21200,15 +21328,15 @@
         <v>1</v>
       </c>
       <c r="V293" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="294" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="294" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A294" s="12">
         <v>14</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>81</v>
@@ -21262,15 +21390,15 @@
         <v>0</v>
       </c>
       <c r="V294" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="295" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="295" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>15</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>81</v>
@@ -21318,12 +21446,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>16</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>81</v>
@@ -21371,12 +21499,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>17</v>
       </c>
       <c r="B297" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>81</v>
@@ -21424,12 +21552,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>18</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>81</v>
@@ -21477,12 +21605,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>19</v>
       </c>
       <c r="B299" s="13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>81</v>
@@ -21530,12 +21658,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>20</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>81</v>
@@ -21583,12 +21711,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>21</v>
       </c>
       <c r="B301" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>81</v>
@@ -21636,12 +21764,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>22</v>
       </c>
       <c r="B302" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>81</v>
@@ -21689,12 +21817,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>23</v>
       </c>
       <c r="B303" s="13" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>81</v>
@@ -21742,12 +21870,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>24</v>
       </c>
       <c r="B304" s="13" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>81</v>
@@ -21795,12 +21923,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>25</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>81</v>
@@ -21848,12 +21976,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>26</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>81</v>
@@ -21901,12 +22029,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>27</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>81</v>
@@ -21954,12 +22082,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>28</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>81</v>
@@ -22007,12 +22135,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>29</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>81</v>
@@ -22060,12 +22188,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>30</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>81</v>
@@ -22113,12 +22241,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>31</v>
       </c>
       <c r="B311" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>81</v>
@@ -22164,18 +22292,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>32</v>
       </c>
       <c r="B312" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E312" s="4" t="s">
         <v>74</v>
@@ -22217,12 +22345,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>33</v>
       </c>
       <c r="B313" s="13" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>81</v>
@@ -22268,12 +22396,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>34</v>
       </c>
       <c r="B314" s="13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>81</v>
@@ -22321,18 +22449,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A315" s="27" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B315" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>74</v>
@@ -22374,12 +22502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A316" s="27" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B316" s="13" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>81</v>
@@ -22427,18 +22555,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B317" s="13" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E317" s="4" t="s">
         <v>74</v>
@@ -22480,12 +22608,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B318" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>81</v>
@@ -22533,12 +22661,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B319" s="13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>81</v>
@@ -22586,18 +22714,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E320" s="4" t="s">
         <v>74</v>
@@ -22639,12 +22767,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B321" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>81</v>
@@ -22692,12 +22820,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>42</v>
       </c>
       <c r="B322" s="13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>81</v>
@@ -22745,12 +22873,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>43</v>
       </c>
       <c r="B323" s="13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>81</v>
@@ -22798,12 +22926,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>44</v>
       </c>
       <c r="B324" s="13" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>81</v>
@@ -22851,12 +22979,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>45</v>
       </c>
       <c r="B325" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>81</v>
@@ -22904,12 +23032,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>46</v>
       </c>
       <c r="B326" s="13" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>81</v>
@@ -22957,12 +23085,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>47</v>
       </c>
       <c r="B327" s="13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>81</v>
@@ -23008,12 +23136,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>48</v>
       </c>
       <c r="B328" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>81</v>
@@ -23061,12 +23189,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>49</v>
       </c>
       <c r="B329" s="13" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>81</v>
@@ -23114,12 +23242,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B330" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>81</v>
@@ -23167,12 +23295,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B331" s="13" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>81</v>
@@ -23220,12 +23348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B332" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>81</v>
@@ -23273,12 +23401,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B333" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>81</v>
@@ -23326,12 +23454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B334" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>81</v>
@@ -23379,12 +23507,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B335" s="13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>81</v>
@@ -23432,12 +23560,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B336" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>81</v>
@@ -23485,12 +23613,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B337" s="13" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>81</v>
@@ -23538,12 +23666,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B338" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>81</v>
@@ -23591,12 +23719,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>59</v>
       </c>
       <c r="B339" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>81</v>
@@ -23644,12 +23772,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>60</v>
       </c>
       <c r="B340" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>81</v>
@@ -23697,12 +23825,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>61</v>
       </c>
       <c r="B341" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>81</v>
@@ -23750,12 +23878,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>62</v>
       </c>
       <c r="B342" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>81</v>
@@ -23803,12 +23931,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>63</v>
       </c>
       <c r="B343" s="13" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>81</v>
@@ -23856,12 +23984,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>64</v>
       </c>
       <c r="B344" s="13" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>81</v>
@@ -23909,12 +24037,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>65</v>
       </c>
       <c r="B345" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>81</v>
@@ -23962,12 +24090,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>66</v>
       </c>
       <c r="B346" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>81</v>
@@ -24015,12 +24143,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>67</v>
       </c>
       <c r="B347" s="13" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>81</v>
@@ -24068,12 +24196,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>75</v>
       </c>
       <c r="B348" s="13" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>81</v>
@@ -24121,12 +24249,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>76</v>
       </c>
       <c r="B349" s="13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>81</v>
@@ -24174,12 +24302,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A350" s="12">
         <v>96</v>
       </c>
       <c r="B350" s="13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>81</v>
@@ -24238,12 +24366,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="351" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B351" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>81</v>
@@ -24270,7 +24398,7 @@
         <v>145</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L351" s="4">
         <v>1</v>
@@ -24295,15 +24423,15 @@
         <v>0</v>
       </c>
       <c r="V351" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="352" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="352" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B352" s="13" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>81</v>
@@ -24330,7 +24458,7 @@
         <v>145</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L352" s="4">
         <v>1</v>
@@ -24355,15 +24483,15 @@
         <v>0</v>
       </c>
       <c r="V352" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="353" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="353" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B353" s="13" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>81</v>
@@ -24390,7 +24518,7 @@
         <v>145</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L353" s="4">
         <v>1</v>
@@ -24415,15 +24543,15 @@
         <v>0</v>
       </c>
       <c r="V353" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="354" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="354" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A354" s="12" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B354" s="13" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>81</v>
@@ -24450,7 +24578,7 @@
         <v>145</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L354" s="4">
         <v>1</v>
@@ -24475,15 +24603,15 @@
         <v>0</v>
       </c>
       <c r="V354" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="355" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="355" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B355" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>81</v>
@@ -24535,15 +24663,15 @@
         <v>0</v>
       </c>
       <c r="V355" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="356" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="356" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A356" s="12" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B356" s="13" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>81</v>
@@ -24595,15 +24723,15 @@
         <v>0</v>
       </c>
       <c r="V356" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="357" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="357" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B357" s="13" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>81</v>
@@ -24655,15 +24783,15 @@
         <v>0</v>
       </c>
       <c r="V357" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="358" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="358" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B358" s="13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>81</v>
@@ -24690,7 +24818,7 @@
         <v>145</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L358" s="4"/>
       <c r="M358" s="4"/>
@@ -24713,12 +24841,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B359" s="13" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>81</v>
@@ -24745,7 +24873,7 @@
         <v>145</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L359" s="4"/>
       <c r="M359" s="4"/>
@@ -24768,12 +24896,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B360" s="13" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>81</v>
@@ -24800,7 +24928,7 @@
         <v>145</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L360" s="4"/>
       <c r="M360" s="4"/>
@@ -24823,12 +24951,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B361" s="13" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>81</v>
@@ -24855,7 +24983,7 @@
         <v>145</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L361" s="4"/>
       <c r="M361" s="4"/>
@@ -24878,12 +25006,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B362" s="13" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>81</v>
@@ -24910,7 +25038,7 @@
         <v>145</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L362" s="4"/>
       <c r="M362" s="4"/>
@@ -24933,12 +25061,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B363" s="13" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>81</v>
@@ -24965,7 +25093,7 @@
         <v>145</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L363" s="4"/>
       <c r="M363" s="4"/>
@@ -24988,12 +25116,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B364" s="13" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>81</v>
@@ -25020,7 +25148,7 @@
         <v>145</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L364" s="4"/>
       <c r="M364" s="4"/>
@@ -25043,12 +25171,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B365" s="13" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>81</v>
@@ -25075,7 +25203,7 @@
         <v>145</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L365" s="4"/>
       <c r="M365" s="4"/>
@@ -25098,12 +25226,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B366" s="13" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>81</v>
@@ -25130,7 +25258,7 @@
         <v>145</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L366" s="4"/>
       <c r="M366" s="4"/>
@@ -25153,12 +25281,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B367" s="13" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>81</v>
@@ -25185,7 +25313,7 @@
         <v>145</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L367" s="4"/>
       <c r="M367" s="4"/>
@@ -25208,12 +25336,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B368" s="13" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>81</v>
@@ -25240,7 +25368,7 @@
         <v>145</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L368" s="4"/>
       <c r="M368" s="4"/>
@@ -25263,12 +25391,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B369" s="13" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>81</v>
@@ -25295,7 +25423,7 @@
         <v>145</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L369" s="4"/>
       <c r="M369" s="4"/>
@@ -25318,12 +25446,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B370" s="13" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>81</v>
@@ -25350,7 +25478,7 @@
         <v>145</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L370" s="4"/>
       <c r="M370" s="4"/>
@@ -25373,12 +25501,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B371" s="13" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>81</v>
@@ -25428,12 +25556,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B372" s="13" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>81</v>
@@ -25483,12 +25611,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B373" s="13" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>81</v>
@@ -25515,7 +25643,7 @@
         <v>145</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L373" s="4"/>
       <c r="M373" s="4"/>
@@ -25538,12 +25666,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B374" s="13" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>81</v>
@@ -25593,12 +25721,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B375" s="13" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>81</v>
@@ -25648,12 +25776,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B376" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>81</v>
@@ -25703,12 +25831,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B377" s="13" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>81</v>
@@ -25758,12 +25886,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B378" s="13" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>81</v>
@@ -25813,12 +25941,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B379" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>67</v>
@@ -25868,12 +25996,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B380" s="13" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>81</v>
@@ -25923,12 +26051,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B381" s="13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>67</v>
@@ -25976,12 +26104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B382" s="13" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>67</v>
@@ -26033,10 +26161,10 @@
     </row>
     <row r="383" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="B383" s="13" t="s">
-        <v>606</v>
+        <v>603</v>
+      </c>
+      <c r="B383" s="12" t="s">
+        <v>604</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>81</v>
@@ -26090,15 +26218,15 @@
         <v>1</v>
       </c>
       <c r="V383" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="384" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B384" s="13" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>81</v>
@@ -26148,15 +26276,15 @@
         <v>1</v>
       </c>
       <c r="V384" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="385" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="385" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>97</v>
       </c>
       <c r="B385" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>81</v>
@@ -26211,12 +26339,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="386" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>98</v>
       </c>
       <c r="B386" s="13" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>81</v>
@@ -26271,12 +26399,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="387" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>427</v>
       </c>
       <c r="B387" s="13" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>67</v>
@@ -26301,7 +26429,7 @@
         <v>379</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L387" s="4"/>
       <c r="M387" s="4"/>
@@ -26324,12 +26452,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>428</v>
       </c>
       <c r="B388" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>67</v>
@@ -26354,7 +26482,7 @@
         <v>379</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L388" s="4"/>
       <c r="M388" s="4"/>
@@ -26377,12 +26505,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>429</v>
       </c>
       <c r="B389" s="13" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>67</v>
@@ -26407,7 +26535,7 @@
         <v>379</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L389" s="4"/>
       <c r="M389" s="4"/>
@@ -26430,12 +26558,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>430</v>
       </c>
       <c r="B390" s="13" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>81</v>
@@ -26483,12 +26611,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>431</v>
       </c>
       <c r="B391" s="13" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>67</v>
@@ -26536,12 +26664,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>432</v>
       </c>
       <c r="B392" s="13" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>67</v>
@@ -26566,7 +26694,7 @@
         <v>115</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L392" s="4"/>
       <c r="M392" s="4"/>
@@ -26589,12 +26717,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>433</v>
       </c>
       <c r="B393" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>67</v>
@@ -26619,7 +26747,7 @@
         <v>379</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L393" s="4"/>
       <c r="M393" s="4"/>
@@ -26642,12 +26770,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>434</v>
       </c>
       <c r="B394" s="13" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>67</v>
@@ -26672,7 +26800,7 @@
         <v>379</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L394" s="4"/>
       <c r="M394" s="4"/>
@@ -26695,12 +26823,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>435</v>
       </c>
       <c r="B395" s="13" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>67</v>
@@ -26725,7 +26853,7 @@
         <v>379</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L395" s="4"/>
       <c r="M395" s="4"/>
@@ -26748,12 +26876,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>436</v>
       </c>
       <c r="B396" s="13" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>67</v>
@@ -26801,12 +26929,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B397" s="13" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>67</v>
@@ -26854,12 +26982,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B398" s="13" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>67</v>
@@ -26907,12 +27035,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>117</v>
       </c>
       <c r="B399" s="13" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>67</v>
@@ -26937,7 +27065,7 @@
         <v>379</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L399" s="4"/>
       <c r="M399" s="4"/>
@@ -26960,12 +27088,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A400" s="29">
         <v>109</v>
       </c>
       <c r="B400" s="13" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>67</v>
@@ -27015,15 +27143,15 @@
         <v>0</v>
       </c>
       <c r="V400" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="401" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="401" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B401" s="13" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>67</v>
@@ -27071,12 +27199,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B402" s="13" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>67</v>
@@ -27124,12 +27252,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B403" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>67</v>
@@ -27177,12 +27305,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B404" s="13" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>67</v>
@@ -27230,12 +27358,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>437</v>
       </c>
       <c r="B405" s="13" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>67</v>
@@ -27283,12 +27411,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B406" s="13" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>67</v>
@@ -27336,12 +27464,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B407" s="13" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>67</v>
@@ -27389,12 +27517,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B408" s="13" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>67</v>
@@ -27442,12 +27570,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B409" s="13" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>67</v>
@@ -27495,18 +27623,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B410" s="13" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E410" s="4" t="s">
         <v>94</v>
@@ -27548,12 +27676,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B411" s="13" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>67</v>
@@ -27601,12 +27729,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B412" s="13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>67</v>
@@ -27654,18 +27782,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>438</v>
       </c>
       <c r="B413" s="13" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E413" s="4" t="s">
         <v>69</v>
@@ -27684,7 +27812,7 @@
         <v>145</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L413" s="4"/>
       <c r="M413" s="4"/>
@@ -27707,18 +27835,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>439</v>
       </c>
       <c r="B414" s="13" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E414" s="4" t="s">
         <v>69</v>
@@ -27737,7 +27865,7 @@
         <v>145</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L414" s="4"/>
       <c r="M414" s="4"/>
@@ -27760,18 +27888,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>440</v>
       </c>
       <c r="B415" s="13" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E415" s="4" t="s">
         <v>69</v>
@@ -27790,7 +27918,7 @@
         <v>145</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L415" s="4"/>
       <c r="M415" s="4"/>
@@ -27813,12 +27941,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>999</v>
       </c>
       <c r="B416" s="13" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>81</v>
@@ -27866,12 +27994,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>998</v>
       </c>
       <c r="B417" s="13" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>81</v>
@@ -27919,12 +28047,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>441</v>
       </c>
       <c r="B418" s="13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>81</v>
@@ -27972,12 +28100,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>442</v>
       </c>
       <c r="B419" s="13" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>67</v>
@@ -28025,12 +28153,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>443</v>
       </c>
       <c r="B420" s="13" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>67</v>
@@ -28078,12 +28206,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>444</v>
       </c>
       <c r="B421" s="13" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>67</v>
@@ -28108,7 +28236,7 @@
         <v>145</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L421" s="4"/>
       <c r="M421" s="4"/>
@@ -28131,12 +28259,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>445</v>
       </c>
       <c r="B422" s="13" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>67</v>
@@ -28184,12 +28312,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>446</v>
       </c>
       <c r="B423" s="13" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>67</v>
@@ -28237,12 +28365,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>447</v>
       </c>
       <c r="B424" s="13" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>67</v>
@@ -28290,12 +28418,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>448</v>
       </c>
       <c r="B425" s="13" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>67</v>
@@ -28343,12 +28471,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>449</v>
       </c>
       <c r="B426" s="13" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>67</v>
@@ -28357,7 +28485,7 @@
         <v>297</v>
       </c>
       <c r="E426" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F426" s="4" t="s">
         <v>70</v>
@@ -28373,7 +28501,7 @@
         <v>115</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L426" s="4"/>
       <c r="M426" s="4"/>
@@ -28396,12 +28524,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>450</v>
       </c>
       <c r="B427" s="13" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>67</v>
@@ -28426,7 +28554,7 @@
         <v>115</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L427" s="4"/>
       <c r="M427" s="4"/>
@@ -28449,12 +28577,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>451</v>
       </c>
       <c r="B428" s="13" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>67</v>
@@ -28502,12 +28630,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>452</v>
       </c>
       <c r="B429" s="13" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>67</v>
@@ -28555,12 +28683,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>453</v>
       </c>
       <c r="B430" s="13" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>67</v>
@@ -28608,12 +28736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>454</v>
       </c>
       <c r="B431" s="13" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>81</v>
@@ -28661,12 +28789,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>455</v>
       </c>
       <c r="B432" s="13" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>81</v>
@@ -28714,12 +28842,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>456</v>
       </c>
       <c r="B433" s="13" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>67</v>
@@ -28769,12 +28897,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>457</v>
       </c>
       <c r="B434" s="13" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>67</v>
@@ -28824,12 +28952,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>458</v>
       </c>
       <c r="B435" s="13" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>67</v>
@@ -28877,12 +29005,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>459</v>
       </c>
       <c r="B436" s="13" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>67</v>
@@ -28930,12 +29058,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>460</v>
       </c>
       <c r="B437" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>67</v>
@@ -28992,12 +29120,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="438" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>462</v>
       </c>
       <c r="B438" s="13" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>67</v>
@@ -29045,12 +29173,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>463</v>
       </c>
       <c r="B439" s="13" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>81</v>
@@ -29107,12 +29235,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="440" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>464</v>
       </c>
       <c r="B440" s="13" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>67</v>
@@ -29160,12 +29288,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>465</v>
       </c>
       <c r="B441" s="13" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>81</v>
@@ -29186,13 +29314,13 @@
         <v>45</v>
       </c>
       <c r="I441" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J441" s="4" t="s">
         <v>145</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L441" s="4"/>
       <c r="M441" s="4">
@@ -29220,12 +29348,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="442" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>466</v>
       </c>
       <c r="B442" s="13" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>81</v>
@@ -29282,12 +29410,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="443" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>467</v>
       </c>
       <c r="B443" s="13" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>81</v>
@@ -29335,12 +29463,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>468</v>
       </c>
       <c r="B444" s="13" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>81</v>
@@ -29365,7 +29493,7 @@
         <v>145</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L444" s="4"/>
       <c r="M444" s="4"/>
@@ -29388,12 +29516,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>469</v>
       </c>
       <c r="B445" s="13" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>81</v>
@@ -29441,12 +29569,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>470</v>
       </c>
       <c r="B446" s="13" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>81</v>
@@ -29494,12 +29622,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>471</v>
       </c>
       <c r="B447" s="13" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>81</v>
@@ -29547,12 +29675,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>472</v>
       </c>
       <c r="B448" s="13" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>81</v>
@@ -29610,7 +29738,7 @@
         <v>900</v>
       </c>
       <c r="B449" s="13" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>81</v>
@@ -29637,7 +29765,7 @@
         <v>71</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="L449" s="4">
         <v>1</v>
@@ -29664,7 +29792,7 @@
         <v>1</v>
       </c>
       <c r="V449" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="450" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -29672,7 +29800,7 @@
         <v>901</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>81</v>
@@ -29728,15 +29856,15 @@
         <v>1</v>
       </c>
       <c r="V450" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="451" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>902</v>
       </c>
-      <c r="B451" s="13" t="s">
-        <v>693</v>
+      <c r="B451" s="12" t="s">
+        <v>927</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>81</v>
@@ -29792,7 +29920,7 @@
         <v>1</v>
       </c>
       <c r="V451" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="452" spans="1:22" x14ac:dyDescent="0.3">
@@ -29800,7 +29928,7 @@
         <v>903</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>81</v>
@@ -29856,7 +29984,7 @@
         <v>1</v>
       </c>
       <c r="V452" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="453" spans="1:22" x14ac:dyDescent="0.3">
@@ -29864,7 +29992,7 @@
         <v>904</v>
       </c>
       <c r="B453" s="13" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>81</v>
@@ -29885,7 +30013,7 @@
         <v>30</v>
       </c>
       <c r="I453" s="13" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="J453" s="4" t="s">
         <v>151</v>
@@ -29920,15 +30048,15 @@
         <v>1</v>
       </c>
       <c r="V453" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="454" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>905</v>
       </c>
-      <c r="B454" s="13" t="s">
-        <v>696</v>
+      <c r="B454" s="12" t="s">
+        <v>693</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>81</v>
@@ -29984,15 +30112,15 @@
         <v>1</v>
       </c>
       <c r="V454" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>906</v>
       </c>
-      <c r="B455" s="13" t="s">
-        <v>815</v>
+      <c r="B455" s="12" t="s">
+        <v>810</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>81</v>
@@ -30048,15 +30176,15 @@
         <v>1</v>
       </c>
       <c r="V455" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="456" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>907</v>
       </c>
-      <c r="B456" s="13" t="s">
-        <v>697</v>
+      <c r="B456" s="12" t="s">
+        <v>694</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>81</v>
@@ -30083,7 +30211,7 @@
         <v>145</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L456" s="4">
         <v>1</v>
@@ -30112,7 +30240,7 @@
         <v>1</v>
       </c>
       <c r="V456" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="457" spans="1:22" x14ac:dyDescent="0.3">
@@ -30120,7 +30248,7 @@
         <v>908</v>
       </c>
       <c r="B457" s="13" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>81</v>
@@ -30147,7 +30275,7 @@
         <v>71</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="L457" s="4">
         <v>1</v>
@@ -30176,15 +30304,15 @@
         <v>1</v>
       </c>
       <c r="V457" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="458" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="458" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>473</v>
       </c>
       <c r="B458" s="13" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>81</v>
@@ -30239,12 +30367,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="459" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A459" s="34" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B459" s="35" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>81</v>
@@ -30296,15 +30424,15 @@
         <v>0</v>
       </c>
       <c r="V459" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="460" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="460" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A460" s="34" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B460" s="35" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>81</v>
@@ -30356,15 +30484,15 @@
         <v>0</v>
       </c>
       <c r="V460" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="461" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="461" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>81</v>
@@ -30416,15 +30544,15 @@
         <v>0</v>
       </c>
       <c r="V461" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="462" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="462" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>81</v>
@@ -30476,15 +30604,15 @@
         <v>0</v>
       </c>
       <c r="V462" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="463" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="463" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>81</v>
@@ -30536,15 +30664,15 @@
         <v>0</v>
       </c>
       <c r="V463" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="464" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="464" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A464" s="26" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>81</v>
@@ -30598,15 +30726,15 @@
         <v>0</v>
       </c>
       <c r="V464" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="465" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="465" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>81</v>
@@ -30633,7 +30761,7 @@
         <v>95</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L465" s="4"/>
       <c r="M465" s="4"/>
@@ -30658,21 +30786,21 @@
         <v>0</v>
       </c>
       <c r="V465" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="466" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="466" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E466" s="4" t="s">
         <v>69</v>
@@ -30718,21 +30846,21 @@
         <v>0</v>
       </c>
       <c r="V466" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="467" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="467" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D467" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E467" s="4" t="s">
         <v>69</v>
@@ -30778,15 +30906,15 @@
         <v>0</v>
       </c>
       <c r="V467" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="468" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="468" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>81</v>
@@ -30838,21 +30966,21 @@
         <v>0</v>
       </c>
       <c r="V468" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="469" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="469" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E469" s="4" t="s">
         <v>69</v>
@@ -30898,21 +31026,21 @@
         <v>0</v>
       </c>
       <c r="V469" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="470" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="470" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E470" s="4" t="s">
         <v>69</v>
@@ -30958,15 +31086,15 @@
         <v>0</v>
       </c>
       <c r="V470" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="471" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="471" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>81</v>
@@ -30987,13 +31115,13 @@
         <v>45</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J471" s="4" t="s">
         <v>145</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L471" s="4"/>
       <c r="M471" s="4"/>
@@ -31018,15 +31146,15 @@
         <v>0</v>
       </c>
       <c r="V471" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="472" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="472" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>81</v>
@@ -31078,15 +31206,15 @@
         <v>0</v>
       </c>
       <c r="V472" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="473" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="473" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>81</v>
@@ -31138,15 +31266,15 @@
         <v>0</v>
       </c>
       <c r="V473" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="474" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="474" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>81</v>
@@ -31198,15 +31326,15 @@
         <v>0</v>
       </c>
       <c r="V474" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="475" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="475" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A475" s="27" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>81</v>
@@ -31254,12 +31382,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A476" s="27" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B476" s="28" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>81</v>
@@ -31307,12 +31435,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A477" s="27" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>81</v>
@@ -31360,12 +31488,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A478" s="27" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>81</v>
@@ -31413,12 +31541,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A479" s="27" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>81</v>
@@ -31466,18 +31594,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D480" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E480" s="4" t="s">
         <v>74</v>
@@ -31519,12 +31647,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>81</v>
@@ -31570,18 +31698,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D482" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E482" s="4" t="s">
         <v>74</v>
@@ -31623,18 +31751,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E483" s="4" t="s">
         <v>74</v>
@@ -31676,18 +31804,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D484" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E484" s="4" t="s">
         <v>74</v>
@@ -31729,12 +31857,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>81</v>
@@ -31782,12 +31910,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>81</v>
@@ -31835,12 +31963,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A487" s="29">
         <v>484</v>
       </c>
       <c r="B487" s="29" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>67</v>
@@ -31865,7 +31993,7 @@
         <v>115</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L487" s="4"/>
       <c r="M487" s="4"/>
@@ -31888,12 +32016,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>476</v>
       </c>
       <c r="B488" s="13" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>81</v>
@@ -31947,15 +32075,15 @@
         <v>0</v>
       </c>
       <c r="V488" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="489" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="489" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>474</v>
       </c>
       <c r="B489" s="13" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>81</v>
@@ -32007,15 +32135,15 @@
         <v>0</v>
       </c>
       <c r="V489" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="490" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="490" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>525</v>
       </c>
       <c r="B490" s="13" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>81</v>
@@ -32057,12 +32185,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B491" s="13" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>81</v>
@@ -32104,12 +32232,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B492" s="13" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>81</v>
@@ -32151,12 +32279,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B493" s="13" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>81</v>
@@ -32202,8 +32330,8 @@
       <c r="A494" s="4">
         <v>909</v>
       </c>
-      <c r="B494" s="4" t="s">
-        <v>802</v>
+      <c r="B494" s="12" t="s">
+        <v>799</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>81</v>
@@ -32259,15 +32387,15 @@
         <v>1</v>
       </c>
       <c r="V494" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="495" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>910</v>
       </c>
-      <c r="B495" s="4" t="s">
-        <v>803</v>
+      <c r="B495" s="12" t="s">
+        <v>800</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>81</v>
@@ -32323,15 +32451,15 @@
         <v>1</v>
       </c>
       <c r="V495" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="496" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>911</v>
       </c>
-      <c r="B496" s="4" t="s">
-        <v>804</v>
+      <c r="B496" s="12" t="s">
+        <v>801</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>81</v>
@@ -32387,15 +32515,15 @@
         <v>1</v>
       </c>
       <c r="V496" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="497" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>912</v>
       </c>
-      <c r="B497" s="4" t="s">
-        <v>805</v>
+      <c r="B497" s="12" t="s">
+        <v>802</v>
       </c>
       <c r="C497" s="4" t="s">
         <v>81</v>
@@ -32451,15 +32579,15 @@
         <v>1</v>
       </c>
       <c r="V497" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="498" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>913</v>
       </c>
-      <c r="B498" s="4" t="s">
-        <v>806</v>
+      <c r="B498" s="12" t="s">
+        <v>803</v>
       </c>
       <c r="C498" s="4" t="s">
         <v>81</v>
@@ -32480,7 +32608,7 @@
         <v>45</v>
       </c>
       <c r="I498" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J498" s="4"/>
       <c r="K498" s="4"/>
@@ -32511,15 +32639,15 @@
         <v>1</v>
       </c>
       <c r="V498" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="499" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>914</v>
       </c>
-      <c r="B499" s="4" t="s">
-        <v>808</v>
+      <c r="B499" s="12" t="s">
+        <v>805</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>81</v>
@@ -32571,15 +32699,15 @@
         <v>1</v>
       </c>
       <c r="V499" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="500" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A500" s="4">
         <v>915</v>
       </c>
-      <c r="B500" s="4" t="s">
-        <v>809</v>
+      <c r="B500" s="12" t="s">
+        <v>806</v>
       </c>
       <c r="C500" s="4" t="s">
         <v>81</v>
@@ -32600,7 +32728,7 @@
         <v>45</v>
       </c>
       <c r="I500" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J500" s="4"/>
       <c r="K500" s="4"/>
@@ -32631,15 +32759,15 @@
         <v>1</v>
       </c>
       <c r="V500" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="501" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>916</v>
       </c>
-      <c r="B501" s="4" t="s">
-        <v>810</v>
+      <c r="B501" s="12" t="s">
+        <v>807</v>
       </c>
       <c r="C501" s="4" t="s">
         <v>81</v>
@@ -32660,7 +32788,7 @@
         <v>45</v>
       </c>
       <c r="I501" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J501" s="4"/>
       <c r="K501" s="4"/>
@@ -32691,15 +32819,15 @@
         <v>1</v>
       </c>
       <c r="V501" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="502" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A502" s="4">
         <v>917</v>
       </c>
-      <c r="B502" s="4" t="s">
-        <v>811</v>
+      <c r="B502" s="12" t="s">
+        <v>932</v>
       </c>
       <c r="C502" s="4" t="s">
         <v>81</v>
@@ -32720,7 +32848,7 @@
         <v>45</v>
       </c>
       <c r="I502" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J502" s="4"/>
       <c r="K502" s="4"/>
@@ -32751,21 +32879,21 @@
         <v>1</v>
       </c>
       <c r="V502" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="503" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>918</v>
       </c>
-      <c r="B503" s="4" t="s">
-        <v>812</v>
+      <c r="B503" s="12" t="s">
+        <v>934</v>
       </c>
       <c r="C503" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D503" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E503" s="4" t="s">
         <v>83</v>
@@ -32780,7 +32908,7 @@
         <v>45</v>
       </c>
       <c r="I503" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J503" s="4"/>
       <c r="K503" s="4"/>
@@ -32811,21 +32939,21 @@
         <v>1</v>
       </c>
       <c r="V503" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="504" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A504" s="4">
         <v>919</v>
       </c>
-      <c r="B504" s="4" t="s">
-        <v>813</v>
+      <c r="B504" s="12" t="s">
+        <v>808</v>
       </c>
       <c r="C504" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E504" s="4" t="s">
         <v>83</v>
@@ -32840,7 +32968,7 @@
         <v>45</v>
       </c>
       <c r="I504" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J504" s="4"/>
       <c r="K504" s="4"/>
@@ -32871,21 +32999,21 @@
         <v>1</v>
       </c>
       <c r="V504" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="505" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>920</v>
       </c>
-      <c r="B505" s="4" t="s">
-        <v>816</v>
+      <c r="B505" s="12" t="s">
+        <v>811</v>
       </c>
       <c r="C505" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D505" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E505" s="4" t="s">
         <v>83</v>
@@ -32900,7 +33028,7 @@
         <v>45</v>
       </c>
       <c r="I505" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J505" s="4"/>
       <c r="K505" s="4"/>
@@ -32935,14 +33063,14 @@
       <c r="A506" s="29">
         <v>921</v>
       </c>
-      <c r="B506" s="29" t="s">
-        <v>819</v>
+      <c r="B506" s="35" t="s">
+        <v>814</v>
       </c>
       <c r="C506" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D506" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E506" s="4" t="s">
         <v>83</v>
@@ -32957,7 +33085,7 @@
         <v>45</v>
       </c>
       <c r="I506" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J506" s="4"/>
       <c r="K506" s="4"/>
@@ -32993,7 +33121,7 @@
         <v>922</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>81</v>
@@ -33050,7 +33178,7 @@
         <v>923</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C508" s="4" t="s">
         <v>81</v>
@@ -33064,17 +33192,21 @@
       <c r="F508" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G508" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H508" s="13" t="s">
-        <v>4</v>
+      <c r="G508" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H508" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="I508" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J508" s="4"/>
-      <c r="K508" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="J508" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K508" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="L508" s="4">
         <v>1</v>
       </c>
@@ -33106,8 +33238,8 @@
       <c r="A509" s="4">
         <v>924</v>
       </c>
-      <c r="B509" s="4" t="s">
-        <v>821</v>
+      <c r="B509" s="12" t="s">
+        <v>816</v>
       </c>
       <c r="C509" s="4" t="s">
         <v>81</v>
@@ -33122,7 +33254,7 @@
         <v>70</v>
       </c>
       <c r="G509" s="13" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H509" s="13" t="s">
         <v>30</v>
@@ -33130,8 +33262,12 @@
       <c r="I509" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J509" s="4"/>
-      <c r="K509" s="4"/>
+      <c r="J509" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="K509" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="L509" s="4">
         <v>1</v>
       </c>
@@ -33164,7 +33300,7 @@
         <v>925</v>
       </c>
       <c r="B510" s="29" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>81</v>
@@ -33178,17 +33314,21 @@
       <c r="F510" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G510" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H510" s="13" t="s">
-        <v>36</v>
+      <c r="G510" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="I510" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J510" s="4"/>
-      <c r="K510" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="J510" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K510" s="4" t="s">
+        <v>690</v>
+      </c>
       <c r="L510" s="4">
         <v>1</v>
       </c>
@@ -33216,12 +33356,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A511" s="29">
         <v>487</v>
       </c>
       <c r="B511" s="29" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C511" s="4" t="s">
         <v>67</v>
@@ -33261,12 +33401,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A512" s="29">
         <v>490</v>
       </c>
       <c r="B512" s="29" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C512" s="4" t="s">
         <v>81</v>
@@ -33306,12 +33446,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A513" s="29">
         <v>491</v>
       </c>
       <c r="B513" s="29" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C513" s="4" t="s">
         <v>81</v>
@@ -33351,12 +33491,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A514" s="29">
         <v>492</v>
       </c>
       <c r="B514" s="29" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>81</v>
@@ -33396,12 +33536,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A515" s="29">
         <v>493</v>
       </c>
       <c r="B515" s="29" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>81</v>
@@ -33441,12 +33581,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A516" s="29">
         <v>494</v>
       </c>
       <c r="B516" s="29" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>81</v>
@@ -33486,12 +33626,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A517" s="29">
         <v>495</v>
       </c>
       <c r="B517" s="29" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>81</v>
@@ -33531,12 +33671,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A518" s="29">
         <v>496</v>
       </c>
       <c r="B518" s="29" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C518" s="4" t="s">
         <v>81</v>
@@ -33576,12 +33716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A519" s="29">
         <v>498</v>
       </c>
       <c r="B519" s="29" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C519" s="4" t="s">
         <v>81</v>
@@ -33621,12 +33761,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A520" s="29">
         <v>499</v>
       </c>
       <c r="B520" s="29" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>81</v>
@@ -33666,12 +33806,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A521" s="29">
         <v>500</v>
       </c>
       <c r="B521" s="29" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C521" s="4" t="s">
         <v>81</v>
@@ -33711,12 +33851,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A522" s="29">
         <v>501</v>
       </c>
       <c r="B522" s="29" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="C522" s="4" t="s">
         <v>81</v>
@@ -33756,12 +33896,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A523" s="29">
         <v>502</v>
       </c>
       <c r="B523" s="29" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="C523" s="4" t="s">
         <v>81</v>
@@ -33801,18 +33941,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A524" s="29">
         <v>503</v>
       </c>
       <c r="B524" s="29" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D524" s="29" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E524" s="4" t="s">
         <v>94</v>
@@ -33846,12 +33986,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A525" s="29">
         <v>504</v>
       </c>
       <c r="B525" s="29" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>81</v>
@@ -33891,12 +34031,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A526" s="29">
         <v>505</v>
       </c>
       <c r="B526" s="29" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C526" s="4" t="s">
         <v>81</v>
@@ -33936,12 +34076,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A527" s="29">
         <v>508</v>
       </c>
       <c r="B527" s="29" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C527" s="4" t="s">
         <v>81</v>
@@ -33981,12 +34121,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A528" s="29">
         <v>522</v>
       </c>
       <c r="B528" s="29" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C528" s="4" t="s">
         <v>81</v>
@@ -34026,12 +34166,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A529" s="29">
         <v>527</v>
       </c>
       <c r="B529" s="29" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="C529" s="4" t="s">
         <v>81</v>
@@ -34071,12 +34211,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A530" s="29">
         <v>528</v>
       </c>
       <c r="B530" s="29" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C530" s="4" t="s">
         <v>81</v>
@@ -34118,12 +34258,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A531" s="29">
         <v>541</v>
       </c>
       <c r="B531" s="29" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="C531" s="4" t="s">
         <v>67</v>
@@ -34165,12 +34305,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A532" s="29">
         <v>542</v>
       </c>
       <c r="B532" s="29" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="C532" s="4" t="s">
         <v>81</v>
@@ -34212,12 +34352,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A533" s="29">
         <v>546</v>
       </c>
       <c r="B533" s="29" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C533" s="4" t="s">
         <v>81</v>
@@ -34259,12 +34399,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A534" s="29">
         <v>547</v>
       </c>
       <c r="B534" s="29" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C534" s="4" t="s">
         <v>81</v>
@@ -34306,12 +34446,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A535" s="29">
         <v>552</v>
       </c>
       <c r="B535" s="29" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C535" s="4" t="s">
         <v>81</v>
@@ -34351,12 +34491,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A536" s="29">
         <v>553</v>
       </c>
       <c r="B536" s="29" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C536" s="4" t="s">
         <v>81</v>
@@ -34396,12 +34536,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A537" s="29">
         <v>556</v>
       </c>
       <c r="B537" s="29" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C537" s="4" t="s">
         <v>81</v>
@@ -34441,12 +34581,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A538" s="29">
         <v>485</v>
       </c>
       <c r="B538" s="29" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="C538" s="4" t="s">
         <v>67</v>
@@ -34486,12 +34626,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A539" s="29">
         <v>488</v>
       </c>
       <c r="B539" s="29" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C539" s="4" t="s">
         <v>67</v>
@@ -34531,12 +34671,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A540" s="29">
         <v>509</v>
       </c>
       <c r="B540" s="29" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C540" s="4" t="s">
         <v>81</v>
@@ -34576,12 +34716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A541" s="29">
         <v>475</v>
       </c>
       <c r="B541" s="29" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C541" s="4" t="s">
         <v>81</v>
@@ -34621,18 +34761,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A542" s="29">
         <v>477</v>
       </c>
       <c r="B542" s="29" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C542" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D542" s="29" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E542" s="4" t="s">
         <v>69</v>
@@ -34666,18 +34806,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A543" s="29">
         <v>478</v>
       </c>
       <c r="B543" s="29" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C543" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D543" s="29" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E543" s="4" t="s">
         <v>69</v>
@@ -34711,18 +34851,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A544" s="29">
         <v>479</v>
       </c>
       <c r="B544" s="29" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C544" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D544" s="29" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E544" s="4" t="s">
         <v>69</v>
@@ -34756,18 +34896,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A545" s="29">
         <v>480</v>
       </c>
       <c r="B545" s="29" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C545" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D545" s="29" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E545" s="4" t="s">
         <v>69</v>
@@ -34801,12 +34941,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A546" s="29">
         <v>481</v>
       </c>
       <c r="B546" s="29" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C546" s="4" t="s">
         <v>67</v>
@@ -34846,12 +34986,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A547" s="29">
         <v>486</v>
       </c>
       <c r="B547" s="29" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C547" s="4" t="s">
         <v>67</v>
@@ -34891,12 +35031,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A548" s="29">
         <v>506</v>
       </c>
       <c r="B548" s="29" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C548" s="4" t="s">
         <v>81</v>
@@ -34936,12 +35076,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A549" s="29">
         <v>507</v>
       </c>
       <c r="B549" s="29" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C549" s="4" t="s">
         <v>81</v>
@@ -34981,12 +35121,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A550" s="29">
         <v>514</v>
       </c>
       <c r="B550" s="29" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C550" s="4" t="s">
         <v>67</v>
@@ -35026,12 +35166,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A551" s="29">
         <v>515</v>
       </c>
       <c r="B551" s="29" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C551" s="4" t="s">
         <v>81</v>
@@ -35071,12 +35211,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A552" s="29">
         <v>516</v>
       </c>
       <c r="B552" s="29" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C552" s="4" t="s">
         <v>67</v>
@@ -35116,12 +35256,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A553" s="29">
         <v>519</v>
       </c>
       <c r="B553" s="29" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C553" s="4" t="s">
         <v>67</v>
@@ -35161,7 +35301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A554" s="29">
         <v>523</v>
       </c>
@@ -35206,7 +35346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A555" s="29">
         <v>524</v>
       </c>
@@ -35253,12 +35393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A556" s="29">
         <v>530</v>
       </c>
       <c r="B556" s="29" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>81</v>
@@ -35298,12 +35438,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A557" s="29">
         <v>531</v>
       </c>
       <c r="B557" s="29" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C557" s="4" t="s">
         <v>81</v>
@@ -35343,12 +35483,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A558" s="29">
         <v>532</v>
       </c>
       <c r="B558" s="29" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="C558" s="4" t="s">
         <v>81</v>
@@ -35390,12 +35530,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A559" s="29">
         <v>533</v>
       </c>
       <c r="B559" s="29" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="C559" s="4" t="s">
         <v>81</v>
@@ -35437,12 +35577,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A560" s="29">
         <v>534</v>
       </c>
       <c r="B560" s="29" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C560" s="4" t="s">
         <v>81</v>
@@ -35484,12 +35624,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A561" s="29">
         <v>535</v>
       </c>
       <c r="B561" s="29" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C561" s="4" t="s">
         <v>81</v>
@@ -35531,12 +35671,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A562" s="29">
         <v>536</v>
       </c>
       <c r="B562" s="29" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C562" s="4" t="s">
         <v>81</v>
@@ -35578,12 +35718,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A563" s="29">
         <v>537</v>
       </c>
       <c r="B563" s="29" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C563" s="4" t="s">
         <v>81</v>
@@ -35623,12 +35763,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A564" s="29">
         <v>538</v>
       </c>
       <c r="B564" s="29" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C564" s="4" t="s">
         <v>67</v>
@@ -35668,12 +35808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A565" s="29">
         <v>539</v>
       </c>
       <c r="B565" s="29" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="C565" s="4" t="s">
         <v>67</v>
@@ -35713,12 +35853,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A566" s="29">
         <v>540</v>
       </c>
       <c r="B566" s="29" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C566" s="4" t="s">
         <v>81</v>
@@ -35758,12 +35898,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A567" s="29">
         <v>543</v>
       </c>
       <c r="B567" s="29" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C567" s="4" t="s">
         <v>67</v>
@@ -35803,12 +35943,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A568" s="29">
         <v>544</v>
       </c>
       <c r="B568" s="29" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C568" s="4" t="s">
         <v>67</v>
@@ -35850,12 +35990,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A569" s="29">
         <v>550</v>
       </c>
       <c r="B569" s="29" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C569" s="4" t="s">
         <v>67</v>
@@ -35895,12 +36035,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A570" s="29">
         <v>551</v>
       </c>
       <c r="B570" s="29" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C570" s="4" t="s">
         <v>67</v>
@@ -35940,12 +36080,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A571" s="29">
         <v>554</v>
       </c>
       <c r="B571" s="29" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C571" s="4" t="s">
         <v>81</v>
@@ -35985,12 +36125,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A572" s="29">
         <v>555</v>
       </c>
       <c r="B572" s="29" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C572" s="4" t="s">
         <v>81</v>
@@ -36030,12 +36170,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A573" s="29">
         <v>510</v>
       </c>
       <c r="B573" s="29" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="C573" s="4" t="s">
         <v>67</v>
@@ -36075,12 +36215,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A574" s="29">
         <v>511</v>
       </c>
       <c r="B574" s="29" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="C574" s="4" t="s">
         <v>67</v>
@@ -36120,12 +36260,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A575" s="29">
         <v>513</v>
       </c>
       <c r="B575" s="29" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C575" s="4" t="s">
         <v>67</v>
@@ -36165,7 +36305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A576" s="29">
         <v>518</v>
       </c>
@@ -36210,12 +36350,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A577" s="29">
         <v>526</v>
       </c>
       <c r="B577" s="29" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C577" s="4" t="s">
         <v>67</v>
@@ -36255,12 +36395,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A578" s="29">
         <v>529</v>
       </c>
       <c r="B578" s="29" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="C578" s="4" t="s">
         <v>67</v>
@@ -36300,177 +36440,369 @@
         <v>0</v>
       </c>
     </row>
+    <row r="579" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A579" s="4">
+        <v>928</v>
+      </c>
+      <c r="B579" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="C579" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E579" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F579" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G579" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H579" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I579" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J579" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="K579" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="L579" s="4">
+        <v>1</v>
+      </c>
+      <c r="M579" s="4">
+        <v>1</v>
+      </c>
+      <c r="N579" s="4">
+        <v>1</v>
+      </c>
+      <c r="O579" s="4">
+        <v>1</v>
+      </c>
+      <c r="P579" s="4"/>
+      <c r="Q579" s="4">
+        <v>1</v>
+      </c>
+      <c r="R579" s="4"/>
+      <c r="S579" s="4">
+        <v>86</v>
+      </c>
+      <c r="T579" s="4">
+        <v>0</v>
+      </c>
+      <c r="U579" s="31">
+        <v>1</v>
+      </c>
+      <c r="V579" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="580" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A580" s="4">
+        <v>927</v>
+      </c>
+      <c r="B580" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E580" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F580" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G580" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H580" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I580" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J580" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K580" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L580" s="4">
+        <v>1</v>
+      </c>
+      <c r="M580" s="4">
+        <v>1</v>
+      </c>
+      <c r="N580" s="4">
+        <v>1</v>
+      </c>
+      <c r="O580" s="4">
+        <v>1</v>
+      </c>
+      <c r="P580" s="4"/>
+      <c r="Q580" s="4">
+        <v>1</v>
+      </c>
+      <c r="R580" s="4"/>
+      <c r="S580" s="4">
+        <v>86</v>
+      </c>
+      <c r="T580" s="4">
+        <v>0</v>
+      </c>
+      <c r="U580" s="31">
+        <v>1</v>
+      </c>
+      <c r="V580" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="581" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A581" s="29">
+        <v>926</v>
+      </c>
+      <c r="B581" s="35" t="s">
+        <v>933</v>
+      </c>
+      <c r="C581" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E581" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F581" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G581" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H581" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I581" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="J581" s="4"/>
+      <c r="K581" s="4"/>
+      <c r="L581" s="4">
+        <v>1</v>
+      </c>
+      <c r="M581" s="4">
+        <v>1</v>
+      </c>
+      <c r="N581" s="4">
+        <v>1</v>
+      </c>
+      <c r="O581" s="4">
+        <v>1</v>
+      </c>
+      <c r="P581" s="4"/>
+      <c r="Q581" s="4">
+        <v>1</v>
+      </c>
+      <c r="R581" s="4"/>
+      <c r="S581" s="4">
+        <v>82</v>
+      </c>
+      <c r="T581" s="4">
+        <v>0</v>
+      </c>
+      <c r="U581" s="31">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:V578" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="20">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="86" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A351:A354">
-    <cfRule type="duplicateValues" dxfId="85" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A355:A396">
-    <cfRule type="duplicateValues" dxfId="84" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A358:A365">
-    <cfRule type="duplicateValues" dxfId="83" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A366">
-    <cfRule type="duplicateValues" dxfId="82" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A367">
-    <cfRule type="duplicateValues" dxfId="81" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A368">
-    <cfRule type="duplicateValues" dxfId="80" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369">
-    <cfRule type="duplicateValues" dxfId="79" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A396">
-    <cfRule type="duplicateValues" dxfId="78" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A383">
-    <cfRule type="duplicateValues" dxfId="77" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A397">
-    <cfRule type="duplicateValues" dxfId="76" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A459:A474">
-    <cfRule type="duplicateValues" dxfId="75" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
-    <cfRule type="duplicateValues" dxfId="63" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="55" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A504:A505">
+    <cfRule type="duplicateValues" dxfId="59" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A506">
+    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A507:A508">
+    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
     <cfRule type="duplicateValues" dxfId="48" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="39" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A509">
-    <cfRule type="duplicateValues" dxfId="35" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="23" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
-    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B495:B496">
-    <cfRule type="duplicateValues" dxfId="19" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="15" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
-    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="11" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
-    <cfRule type="duplicateValues" dxfId="9" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="7" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="5" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A579:A580">
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B579:B580">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B581">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -36489,10 +36821,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="43" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36500,7 +36832,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36508,7 +36840,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36524,47 +36856,47 @@
         <v>23</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="s">
+        <v>775</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>778</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36572,7 +36904,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36580,7 +36912,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -36601,13 +36933,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36615,7 +36947,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>5</v>
@@ -36626,7 +36958,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>8</v>
@@ -36637,7 +36969,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>7</v>
@@ -36648,7 +36980,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>10</v>
@@ -36662,7 +36994,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36673,7 +37005,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36684,7 +37016,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -36695,7 +37027,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36714,10 +37046,10 @@
         <v>23</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36725,10 +37057,10 @@
         <v>23</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36736,7 +37068,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>26</v>
@@ -36747,51 +37079,51 @@
         <v>23</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>765</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>768</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
+        <v>769</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>772</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>773</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>14</v>
@@ -36799,10 +37131,10 @@
     </row>
     <row r="19" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>43</v>
@@ -36810,10 +37142,10 @@
     </row>
     <row r="20" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>44</v>
@@ -36821,21 +37153,21 @@
     </row>
     <row r="21" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>42</v>
@@ -36843,10 +37175,10 @@
     </row>
     <row r="23" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
+        <v>775</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>778</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>781</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>40</v>
@@ -36854,32 +37186,32 @@
     </row>
     <row r="24" spans="1:3" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
+        <v>775</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>778</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>781</v>
-      </c>
       <c r="C24" s="21" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>47</v>
@@ -36887,21 +37219,21 @@
     </row>
     <row r="27" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C28" s="21" t="s">
         <v>48</v>
@@ -36912,10 +37244,10 @@
         <v>29</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36923,10 +37255,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36934,10 +37266,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36945,10 +37277,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="22" t="s">
+        <v>784</v>
+      </c>
+      <c r="C32" s="23" t="s">
         <v>787</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36956,10 +37288,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36967,10 +37299,10 @@
         <v>29</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="34.799999999999997" x14ac:dyDescent="0.3">
@@ -36978,10 +37310,10 @@
         <v>29</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -36999,34 +37331,34 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B1" s="48" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="46" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -37034,7 +37366,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37042,7 +37374,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37050,7 +37382,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -37058,7 +37390,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37066,7 +37398,7 @@
         <v>71</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37074,7 +37406,7 @@
         <v>71</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37082,7 +37414,7 @@
         <v>71</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37090,7 +37422,7 @@
         <v>71</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37098,7 +37430,7 @@
         <v>71</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37106,7 +37438,7 @@
         <v>71</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -37114,7 +37446,7 @@
         <v>89</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37130,7 +37462,7 @@
         <v>89</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37138,7 +37470,7 @@
         <v>89</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -37146,7 +37478,7 @@
         <v>145</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37154,7 +37486,7 @@
         <v>145</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37162,7 +37494,7 @@
         <v>145</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37170,23 +37502,23 @@
         <v>145</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="156" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="46" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A24" s="46" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -37194,7 +37526,7 @@
         <v>142</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37202,7 +37534,7 @@
         <v>142</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -37210,7 +37542,7 @@
         <v>138</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37218,7 +37550,7 @@
         <v>138</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37226,7 +37558,7 @@
         <v>379</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -37234,7 +37566,7 @@
         <v>103</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37242,7 +37574,7 @@
         <v>103</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37250,7 +37582,7 @@
         <v>103</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
@@ -37258,7 +37590,7 @@
         <v>103</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37266,7 +37598,7 @@
         <v>103</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -37274,7 +37606,7 @@
         <v>95</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37282,7 +37614,7 @@
         <v>95</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37290,7 +37622,7 @@
         <v>95</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -37298,7 +37630,7 @@
         <v>332</v>
       </c>
       <c r="B38" s="44" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37306,7 +37638,7 @@
         <v>332</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
@@ -37314,7 +37646,7 @@
         <v>332</v>
       </c>
       <c r="B40" s="44" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -37323,26 +37655,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37577,10 +37889,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37597,20 +37940,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2338" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A426938-EF02-4BC9-A198-FFC240C3553C}"/>
+  <xr:revisionPtr revIDLastSave="2349" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7A8018-2346-41CB-B420-92535DB98A94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3941,47 +3941,7 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{B753E483-50E8-4755-BA53-9118C26C170F}"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{ADCD9E6A-B374-41A4-9E99-CB4D3005E09B}"/>
   </cellStyles>
-  <dxfs count="99">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="95">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -36628,181 +36588,181 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A351:A354">
-    <cfRule type="duplicateValues" dxfId="97" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A355:A396">
-    <cfRule type="duplicateValues" dxfId="96" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A358:A365">
-    <cfRule type="duplicateValues" dxfId="95" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A366">
-    <cfRule type="duplicateValues" dxfId="94" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A367">
-    <cfRule type="duplicateValues" dxfId="93" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A368">
-    <cfRule type="duplicateValues" dxfId="92" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369">
-    <cfRule type="duplicateValues" dxfId="91" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A396">
-    <cfRule type="duplicateValues" dxfId="90" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A383">
-    <cfRule type="duplicateValues" dxfId="89" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A397">
-    <cfRule type="duplicateValues" dxfId="88" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A459:A474">
-    <cfRule type="duplicateValues" dxfId="87" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="86" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="83" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="79" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
-    <cfRule type="duplicateValues" dxfId="75" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="71" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="67" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="63" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="59" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="51" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
-    <cfRule type="duplicateValues" dxfId="47" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="43" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A579:A580">
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="35" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
-    <cfRule type="duplicateValues" dxfId="33" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B495:B496">
-    <cfRule type="duplicateValues" dxfId="31" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="29" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="27" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
-    <cfRule type="duplicateValues" dxfId="25" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="23" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
-    <cfRule type="duplicateValues" dxfId="21" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="17" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="15" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -37655,6 +37615,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -37889,17 +37860,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -37910,6 +37870,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37928,17 +37899,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2451" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B448E3-9086-43F1-AB2B-8FB31C2511AC}"/>
+  <xr:revisionPtr revIDLastSave="2453" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62EED7A3-6BD5-4A84-9A9F-9220A6013717}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41758,7 +41758,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="213" priority="113"/>
   </conditionalFormatting>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -75770,8 +75770,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
     <cfRule type="duplicateValues" dxfId="94" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
     <cfRule type="duplicateValues" dxfId="92" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
     <cfRule type="duplicateValues" dxfId="91" priority="85"/>
@@ -75780,34 +75780,34 @@
     <cfRule type="duplicateValues" dxfId="88" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="84" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
     <cfRule type="duplicateValues" dxfId="87" priority="82"/>
     <cfRule type="duplicateValues" dxfId="86" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
+    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
     <cfRule type="duplicateValues" dxfId="80" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
+    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="70"/>
     <cfRule type="duplicateValues" dxfId="76" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
     <cfRule type="duplicateValues" dxfId="75" priority="61"/>
     <cfRule type="duplicateValues" dxfId="74" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
     <cfRule type="duplicateValues" dxfId="72" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
+    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
     <cfRule type="duplicateValues" dxfId="69" priority="55"/>
     <cfRule type="duplicateValues" dxfId="68" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
     <cfRule type="duplicateValues" dxfId="67" priority="49"/>
@@ -75816,22 +75816,22 @@
     <cfRule type="duplicateValues" dxfId="64" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
     <cfRule type="duplicateValues" dxfId="63" priority="39"/>
     <cfRule type="duplicateValues" dxfId="62" priority="40"/>
     <cfRule type="duplicateValues" dxfId="61" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
     <cfRule type="duplicateValues" dxfId="59" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="46"/>
     <cfRule type="duplicateValues" dxfId="56" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
+    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
     <cfRule type="duplicateValues" dxfId="54" priority="31"/>
     <cfRule type="duplicateValues" dxfId="53" priority="33"/>
     <cfRule type="duplicateValues" dxfId="52" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
     <cfRule type="duplicateValues" dxfId="51" priority="21"/>
@@ -75840,34 +75840,34 @@
     <cfRule type="duplicateValues" dxfId="48" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="44" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="17"/>
     <cfRule type="duplicateValues" dxfId="47" priority="18"/>
     <cfRule type="duplicateValues" dxfId="46" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A582:A583">
+    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
     <cfRule type="duplicateValues" dxfId="42" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="11"/>
     <cfRule type="duplicateValues" dxfId="40" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A585:A592">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
     <cfRule type="duplicateValues" dxfId="39" priority="3"/>
     <cfRule type="duplicateValues" dxfId="38" priority="4"/>
     <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
     <cfRule type="duplicateValues" dxfId="35" priority="27"/>
     <cfRule type="duplicateValues" dxfId="34" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="33" priority="30"/>
     <cfRule type="duplicateValues" dxfId="32" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
+    <cfRule type="duplicateValues" dxfId="31" priority="95"/>
     <cfRule type="duplicateValues" dxfId="30" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
     <cfRule type="duplicateValues" dxfId="29" priority="86"/>
@@ -75882,28 +75882,28 @@
     <cfRule type="duplicateValues" dxfId="24" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
+    <cfRule type="duplicateValues" dxfId="23" priority="72"/>
     <cfRule type="duplicateValues" dxfId="22" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
     <cfRule type="duplicateValues" dxfId="21" priority="62"/>
     <cfRule type="duplicateValues" dxfId="20" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
+    <cfRule type="duplicateValues" dxfId="19" priority="60"/>
     <cfRule type="duplicateValues" dxfId="18" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
+    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
     <cfRule type="duplicateValues" dxfId="16" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
     <cfRule type="duplicateValues" dxfId="15" priority="38"/>
     <cfRule type="duplicateValues" dxfId="14" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
+    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
     <cfRule type="duplicateValues" dxfId="12" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
     <cfRule type="duplicateValues" dxfId="11" priority="32"/>
@@ -75914,20 +75914,20 @@
     <cfRule type="duplicateValues" dxfId="8" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
     <cfRule type="duplicateValues" dxfId="6" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582:B583">
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
     <cfRule type="duplicateValues" dxfId="2" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585:B592">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -76780,15 +76780,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -77023,6 +77014,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -77035,14 +77035,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -77061,6 +77053,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2453" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62EED7A3-6BD5-4A84-9A9F-9220A6013717}"/>
+  <xr:revisionPtr revIDLastSave="2475" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7712E354-5FB0-4F59-A7B6-34EF38AD806A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6231,10 +6231,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -23620,7 +23616,9 @@
         <v>166</v>
       </c>
       <c r="L285" s="4"/>
-      <c r="M285" s="4"/>
+      <c r="M285" s="4">
+        <v>1</v>
+      </c>
       <c r="N285" s="4"/>
       <c r="O285" s="4">
         <v>1</v>
@@ -23809,7 +23807,9 @@
         <v>88</v>
       </c>
       <c r="L288" s="4"/>
-      <c r="M288" s="4"/>
+      <c r="M288" s="4">
+        <v>1</v>
+      </c>
       <c r="N288" s="4"/>
       <c r="O288" s="4">
         <v>1</v>
@@ -37461,7 +37461,7 @@
       <c r="S513" s="4"/>
       <c r="T513" s="4"/>
       <c r="U513" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V513" t="s">
         <v>952</v>
@@ -41207,7 +41207,7 @@
       <c r="S585" s="4"/>
       <c r="T585" s="4"/>
       <c r="U585" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V585" t="s">
         <v>951</v>
@@ -41258,7 +41258,7 @@
       <c r="S586" s="4"/>
       <c r="T586" s="4"/>
       <c r="U586" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V586" t="s">
         <v>952</v>
@@ -41309,7 +41309,7 @@
       <c r="S587" s="4"/>
       <c r="T587" s="4"/>
       <c r="U587" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V587" t="s">
         <v>952</v>
@@ -41360,7 +41360,7 @@
       <c r="S588" s="4"/>
       <c r="T588" s="4"/>
       <c r="U588" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V588" t="s">
         <v>951</v>
@@ -41411,7 +41411,7 @@
       <c r="S589" s="4"/>
       <c r="T589" s="4"/>
       <c r="U589" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V589" t="s">
         <v>951</v>
@@ -41462,7 +41462,7 @@
       <c r="S590" s="4"/>
       <c r="T590" s="4"/>
       <c r="U590" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V590" t="s">
         <v>952</v>
@@ -41513,7 +41513,7 @@
       <c r="S591" s="4"/>
       <c r="T591" s="4"/>
       <c r="U591" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V591" t="s">
         <v>952</v>
@@ -41564,7 +41564,7 @@
       <c r="S592" s="4"/>
       <c r="T592" s="4"/>
       <c r="U592" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V592" t="s">
         <v>951</v>
@@ -76780,6 +76780,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -77014,15 +77023,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -77035,6 +77035,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -77053,14 +77061,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2475" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7712E354-5FB0-4F59-A7B6-34EF38AD806A}"/>
+  <xr:revisionPtr revIDLastSave="2495" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3379351E-04EE-4600-BF73-76FBA0887C84}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -27574,7 +27574,9 @@
         <v>1</v>
       </c>
       <c r="N351" s="4"/>
-      <c r="O351" s="4"/>
+      <c r="O351" s="4">
+        <v>0</v>
+      </c>
       <c r="P351" s="4"/>
       <c r="Q351" s="4">
         <v>1</v>
@@ -27637,7 +27639,9 @@
         <v>1</v>
       </c>
       <c r="N352" s="4"/>
-      <c r="O352" s="4"/>
+      <c r="O352" s="4">
+        <v>0</v>
+      </c>
       <c r="P352" s="4"/>
       <c r="Q352" s="4">
         <v>1</v>
@@ -27700,7 +27704,9 @@
         <v>1</v>
       </c>
       <c r="N353" s="4"/>
-      <c r="O353" s="4"/>
+      <c r="O353" s="4">
+        <v>0</v>
+      </c>
       <c r="P353" s="4"/>
       <c r="Q353" s="4">
         <v>1</v>
@@ -27763,7 +27769,9 @@
         <v>1</v>
       </c>
       <c r="N354" s="4"/>
-      <c r="O354" s="4"/>
+      <c r="O354" s="4">
+        <v>0</v>
+      </c>
       <c r="P354" s="4"/>
       <c r="Q354" s="4">
         <v>1</v>
@@ -27826,7 +27834,9 @@
         <v>1</v>
       </c>
       <c r="N355" s="4"/>
-      <c r="O355" s="4"/>
+      <c r="O355" s="4">
+        <v>0</v>
+      </c>
       <c r="P355" s="4"/>
       <c r="Q355" s="4">
         <v>1</v>
@@ -27889,7 +27899,9 @@
         <v>1</v>
       </c>
       <c r="N356" s="4"/>
-      <c r="O356" s="4"/>
+      <c r="O356" s="4">
+        <v>0</v>
+      </c>
       <c r="P356" s="4"/>
       <c r="Q356" s="4">
         <v>1</v>
@@ -27952,7 +27964,9 @@
         <v>1</v>
       </c>
       <c r="N357" s="4"/>
-      <c r="O357" s="4"/>
+      <c r="O357" s="4">
+        <v>0</v>
+      </c>
       <c r="P357" s="4"/>
       <c r="Q357" s="4">
         <v>1</v>
@@ -29414,7 +29428,9 @@
       <c r="L381" s="4"/>
       <c r="M381" s="4"/>
       <c r="N381" s="4"/>
-      <c r="O381" s="4"/>
+      <c r="O381" s="4">
+        <v>0</v>
+      </c>
       <c r="P381" s="4"/>
       <c r="Q381" s="4">
         <v>1</v>
@@ -36039,7 +36055,9 @@
       <c r="L490" s="4"/>
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
-      <c r="O490" s="4"/>
+      <c r="O490" s="4">
+        <v>0</v>
+      </c>
       <c r="P490" s="4"/>
       <c r="Q490" s="4"/>
       <c r="R490" s="4"/>
@@ -36092,7 +36110,9 @@
       <c r="L491" s="4"/>
       <c r="M491" s="4"/>
       <c r="N491" s="4"/>
-      <c r="O491" s="4"/>
+      <c r="O491" s="4">
+        <v>0</v>
+      </c>
       <c r="P491" s="4"/>
       <c r="Q491" s="4"/>
       <c r="R491" s="4"/>
@@ -36145,7 +36165,9 @@
       <c r="L492" s="4"/>
       <c r="M492" s="4"/>
       <c r="N492" s="4"/>
-      <c r="O492" s="4"/>
+      <c r="O492" s="4">
+        <v>0</v>
+      </c>
       <c r="P492" s="4"/>
       <c r="Q492" s="4"/>
       <c r="R492" s="4"/>
@@ -36198,7 +36220,9 @@
       <c r="L493" s="4"/>
       <c r="M493" s="4"/>
       <c r="N493" s="4"/>
-      <c r="O493" s="4"/>
+      <c r="O493" s="4">
+        <v>0</v>
+      </c>
       <c r="P493" s="4"/>
       <c r="Q493" s="4"/>
       <c r="R493" s="4"/>
@@ -41758,6 +41782,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="213" priority="113"/>
   </conditionalFormatting>
@@ -76780,12 +76805,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77024,20 +77051,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -77062,12 +77090,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2495" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3379351E-04EE-4600-BF73-76FBA0887C84}"/>
+  <xr:revisionPtr revIDLastSave="2475" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7712E354-5FB0-4F59-A7B6-34EF38AD806A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -27574,9 +27574,7 @@
         <v>1</v>
       </c>
       <c r="N351" s="4"/>
-      <c r="O351" s="4">
-        <v>0</v>
-      </c>
+      <c r="O351" s="4"/>
       <c r="P351" s="4"/>
       <c r="Q351" s="4">
         <v>1</v>
@@ -27639,9 +27637,7 @@
         <v>1</v>
       </c>
       <c r="N352" s="4"/>
-      <c r="O352" s="4">
-        <v>0</v>
-      </c>
+      <c r="O352" s="4"/>
       <c r="P352" s="4"/>
       <c r="Q352" s="4">
         <v>1</v>
@@ -27704,9 +27700,7 @@
         <v>1</v>
       </c>
       <c r="N353" s="4"/>
-      <c r="O353" s="4">
-        <v>0</v>
-      </c>
+      <c r="O353" s="4"/>
       <c r="P353" s="4"/>
       <c r="Q353" s="4">
         <v>1</v>
@@ -27769,9 +27763,7 @@
         <v>1</v>
       </c>
       <c r="N354" s="4"/>
-      <c r="O354" s="4">
-        <v>0</v>
-      </c>
+      <c r="O354" s="4"/>
       <c r="P354" s="4"/>
       <c r="Q354" s="4">
         <v>1</v>
@@ -27834,9 +27826,7 @@
         <v>1</v>
       </c>
       <c r="N355" s="4"/>
-      <c r="O355" s="4">
-        <v>0</v>
-      </c>
+      <c r="O355" s="4"/>
       <c r="P355" s="4"/>
       <c r="Q355" s="4">
         <v>1</v>
@@ -27899,9 +27889,7 @@
         <v>1</v>
       </c>
       <c r="N356" s="4"/>
-      <c r="O356" s="4">
-        <v>0</v>
-      </c>
+      <c r="O356" s="4"/>
       <c r="P356" s="4"/>
       <c r="Q356" s="4">
         <v>1</v>
@@ -27964,9 +27952,7 @@
         <v>1</v>
       </c>
       <c r="N357" s="4"/>
-      <c r="O357" s="4">
-        <v>0</v>
-      </c>
+      <c r="O357" s="4"/>
       <c r="P357" s="4"/>
       <c r="Q357" s="4">
         <v>1</v>
@@ -29428,9 +29414,7 @@
       <c r="L381" s="4"/>
       <c r="M381" s="4"/>
       <c r="N381" s="4"/>
-      <c r="O381" s="4">
-        <v>0</v>
-      </c>
+      <c r="O381" s="4"/>
       <c r="P381" s="4"/>
       <c r="Q381" s="4">
         <v>1</v>
@@ -36055,9 +36039,7 @@
       <c r="L490" s="4"/>
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
-      <c r="O490" s="4">
-        <v>0</v>
-      </c>
+      <c r="O490" s="4"/>
       <c r="P490" s="4"/>
       <c r="Q490" s="4"/>
       <c r="R490" s="4"/>
@@ -36110,9 +36092,7 @@
       <c r="L491" s="4"/>
       <c r="M491" s="4"/>
       <c r="N491" s="4"/>
-      <c r="O491" s="4">
-        <v>0</v>
-      </c>
+      <c r="O491" s="4"/>
       <c r="P491" s="4"/>
       <c r="Q491" s="4"/>
       <c r="R491" s="4"/>
@@ -36165,9 +36145,7 @@
       <c r="L492" s="4"/>
       <c r="M492" s="4"/>
       <c r="N492" s="4"/>
-      <c r="O492" s="4">
-        <v>0</v>
-      </c>
+      <c r="O492" s="4"/>
       <c r="P492" s="4"/>
       <c r="Q492" s="4"/>
       <c r="R492" s="4"/>
@@ -36220,9 +36198,7 @@
       <c r="L493" s="4"/>
       <c r="M493" s="4"/>
       <c r="N493" s="4"/>
-      <c r="O493" s="4">
-        <v>0</v>
-      </c>
+      <c r="O493" s="4"/>
       <c r="P493" s="4"/>
       <c r="Q493" s="4"/>
       <c r="R493" s="4"/>
@@ -41782,7 +41758,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="213" priority="113"/>
   </conditionalFormatting>
@@ -76805,14 +76780,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77051,21 +77024,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -77090,9 +77062,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2475" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7712E354-5FB0-4F59-A7B6-34EF38AD806A}"/>
+  <xr:revisionPtr revIDLastSave="2480" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F8BAD3C-B111-4C85-86E9-7F200D9C345E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41758,6 +41758,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="213" priority="113"/>
   </conditionalFormatting>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2480" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F8BAD3C-B111-4C85-86E9-7F200D9C345E}"/>
+  <xr:revisionPtr revIDLastSave="2495" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7639F763-167E-4600-A1F6-77B45704D782}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33237,7 +33237,7 @@
       <c r="M445" s="4"/>
       <c r="N445" s="4"/>
       <c r="O445" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P445" s="4"/>
       <c r="Q445" s="4">
@@ -41758,7 +41758,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="213" priority="113"/>
   </conditionalFormatting>
@@ -76781,6 +76780,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -76789,7 +76799,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -77024,18 +77034,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -77043,7 +77053,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -77060,15 +77070,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2495" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7639F763-167E-4600-A1F6-77B45704D782}"/>
+  <xr:revisionPtr revIDLastSave="2500" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB196692-4D73-4FD7-AE22-B1050FAC196F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11767" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11767" uniqueCount="955">
   <si>
     <t>Linea</t>
   </si>
@@ -3569,6 +3569,9 @@
   </si>
   <si>
     <t>Impacto (Transformaciones)</t>
+  </si>
+  <si>
+    <t>Operación de Nuevos Negocios y CI</t>
   </si>
 </sst>
 </file>
@@ -4007,7 +4010,27 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{B753E483-50E8-4755-BA53-9118C26C170F}"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{ADCD9E6A-B374-41A4-9E99-CB4D3005E09B}"/>
   </cellStyles>
-  <dxfs count="214">
+  <dxfs count="216">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -19649,8 +19672,8 @@
       <c r="C219" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D219" s="4" t="s">
-        <v>370</v>
+      <c r="D219" s="29" t="s">
+        <v>954</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>72</v>
@@ -19889,8 +19912,8 @@
       <c r="C223" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D223" s="4" t="s">
-        <v>370</v>
+      <c r="D223" s="29" t="s">
+        <v>954</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>72</v>
@@ -41759,201 +41782,207 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="213" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A351:A354">
+    <cfRule type="duplicateValues" dxfId="214" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A355:A396">
+    <cfRule type="duplicateValues" dxfId="213" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A358:A365">
     <cfRule type="duplicateValues" dxfId="212" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A355:A396">
-    <cfRule type="duplicateValues" dxfId="211" priority="123"/>
+  <conditionalFormatting sqref="A366">
+    <cfRule type="duplicateValues" dxfId="211" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A358:A365">
+  <conditionalFormatting sqref="A367">
     <cfRule type="duplicateValues" dxfId="210" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A366">
-    <cfRule type="duplicateValues" dxfId="209" priority="119"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A367">
-    <cfRule type="duplicateValues" dxfId="208" priority="118"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A368">
-    <cfRule type="duplicateValues" dxfId="207" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369">
-    <cfRule type="duplicateValues" dxfId="206" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A396">
-    <cfRule type="duplicateValues" dxfId="205" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A383">
-    <cfRule type="duplicateValues" dxfId="204" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A397">
-    <cfRule type="duplicateValues" dxfId="203" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A459:A474">
-    <cfRule type="duplicateValues" dxfId="202" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="201" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="198" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="194" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
+    <cfRule type="duplicateValues" dxfId="192" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="88"/>
     <cfRule type="duplicateValues" dxfId="190" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="186" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="182" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="178" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="67"/>
     <cfRule type="duplicateValues" dxfId="177" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="174" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="170" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="166" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="58"/>
     <cfRule type="duplicateValues" dxfId="165" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
+    <cfRule type="duplicateValues" dxfId="164" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="43"/>
     <cfRule type="duplicateValues" dxfId="162" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="158" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="154" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="150" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A585:A592">
-    <cfRule type="duplicateValues" dxfId="146" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="142" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="140" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="138" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
-    <cfRule type="duplicateValues" dxfId="136" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B495:B496">
-    <cfRule type="duplicateValues" dxfId="134" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="132" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="130" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B501:B502">
+    <cfRule type="duplicateValues" dxfId="130" priority="74"/>
     <cfRule type="duplicateValues" dxfId="129" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B501:B502">
+  <conditionalFormatting sqref="B503">
     <cfRule type="duplicateValues" dxfId="128" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="126" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
-    <cfRule type="duplicateValues" dxfId="124" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="122" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="120" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="118" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="116" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
-    <cfRule type="duplicateValues" dxfId="114" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="112" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582:B583">
-    <cfRule type="duplicateValues" dxfId="110" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585:B592">
-    <cfRule type="duplicateValues" dxfId="108" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D219">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D223">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -75733,201 +75762,201 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="106" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A351:A354">
-    <cfRule type="duplicateValues" dxfId="105" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A355:A396">
-    <cfRule type="duplicateValues" dxfId="104" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A358:A365">
-    <cfRule type="duplicateValues" dxfId="103" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A366">
-    <cfRule type="duplicateValues" dxfId="102" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A367">
-    <cfRule type="duplicateValues" dxfId="101" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A368">
-    <cfRule type="duplicateValues" dxfId="100" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369">
-    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A396">
-    <cfRule type="duplicateValues" dxfId="98" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A383">
-    <cfRule type="duplicateValues" dxfId="97" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A397">
-    <cfRule type="duplicateValues" dxfId="96" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A459:A474">
-    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="91" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="87" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
-    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="67" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="63" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="59" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
-    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="51" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A585:A592">
-    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="33" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="31" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
-    <cfRule type="duplicateValues" dxfId="29" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B495:B496">
-    <cfRule type="duplicateValues" dxfId="27" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="23" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
-    <cfRule type="duplicateValues" dxfId="21" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="19" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
-    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="15" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
-    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582:B583">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585:B592">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -76780,6 +76809,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
@@ -76788,15 +76826,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77035,20 +77064,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
     <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2500" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB196692-4D73-4FD7-AE22-B1050FAC196F}"/>
+  <xr:revisionPtr revIDLastSave="2502" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3739CDA3-0CAC-4F4B-9CCB-E3DFAA7118E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6254,6 +6254,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -6551,6 +6555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W595"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6645,7 +6650,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>68</v>
       </c>
@@ -6704,7 +6709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>69</v>
       </c>
@@ -6763,7 +6768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>73</v>
       </c>
@@ -6822,7 +6827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>74</v>
       </c>
@@ -6881,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>77</v>
       </c>
@@ -6946,7 +6951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>78</v>
       </c>
@@ -7007,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>79</v>
       </c>
@@ -7066,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>84</v>
       </c>
@@ -7125,7 +7130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>85</v>
       </c>
@@ -7184,7 +7189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>86</v>
       </c>
@@ -7243,7 +7248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>87</v>
       </c>
@@ -7302,7 +7307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>88</v>
       </c>
@@ -7361,7 +7366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>89</v>
       </c>
@@ -7420,7 +7425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>90</v>
       </c>
@@ -7479,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>91</v>
       </c>
@@ -7538,7 +7543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>92</v>
       </c>
@@ -7597,7 +7602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>94</v>
       </c>
@@ -7656,7 +7661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>95</v>
       </c>
@@ -7715,7 +7720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>100</v>
       </c>
@@ -7774,7 +7779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>104</v>
       </c>
@@ -7833,7 +7838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>106</v>
       </c>
@@ -7892,7 +7897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>108</v>
       </c>
@@ -7951,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>110</v>
       </c>
@@ -8010,7 +8015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>111</v>
       </c>
@@ -8069,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>112</v>
       </c>
@@ -8128,7 +8133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>113</v>
       </c>
@@ -8187,7 +8192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>114</v>
       </c>
@@ -8246,7 +8251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>115</v>
       </c>
@@ -8305,7 +8310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>116</v>
       </c>
@@ -8364,7 +8369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>118</v>
       </c>
@@ -8423,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>121</v>
       </c>
@@ -8482,7 +8487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>122</v>
       </c>
@@ -8541,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>124</v>
       </c>
@@ -8600,7 +8605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>125</v>
       </c>
@@ -8659,7 +8664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>126</v>
       </c>
@@ -8718,7 +8723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>127</v>
       </c>
@@ -8777,7 +8782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>128</v>
       </c>
@@ -8836,7 +8841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>133</v>
       </c>
@@ -8895,7 +8900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>136</v>
       </c>
@@ -8954,7 +8959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>137</v>
       </c>
@@ -9013,7 +9018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>139</v>
       </c>
@@ -9072,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>143</v>
       </c>
@@ -9133,7 +9138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>144</v>
       </c>
@@ -9194,7 +9199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>145</v>
       </c>
@@ -9253,7 +9258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>146</v>
       </c>
@@ -9312,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>147</v>
       </c>
@@ -9373,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>148</v>
       </c>
@@ -9438,7 +9443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>150</v>
       </c>
@@ -9497,7 +9502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>151</v>
       </c>
@@ -9556,7 +9561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>157</v>
       </c>
@@ -9615,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>159</v>
       </c>
@@ -9674,7 +9679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>167</v>
       </c>
@@ -9733,7 +9738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>171</v>
       </c>
@@ -9792,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>172</v>
       </c>
@@ -9853,7 +9858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>174</v>
       </c>
@@ -9912,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>176</v>
       </c>
@@ -9973,7 +9978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>193</v>
       </c>
@@ -10038,7 +10043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>194</v>
       </c>
@@ -10103,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>195</v>
       </c>
@@ -10164,7 +10169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>196</v>
       </c>
@@ -10223,7 +10228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>197</v>
       </c>
@@ -10282,7 +10287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>199</v>
       </c>
@@ -10341,7 +10346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>200</v>
       </c>
@@ -10404,7 +10409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>202</v>
       </c>
@@ -10469,7 +10474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>203</v>
       </c>
@@ -10534,7 +10539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>204</v>
       </c>
@@ -10599,7 +10604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>205</v>
       </c>
@@ -10662,7 +10667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>206</v>
       </c>
@@ -10725,7 +10730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>207</v>
       </c>
@@ -10788,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>208</v>
       </c>
@@ -10847,7 +10852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>210</v>
       </c>
@@ -10906,7 +10911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>213</v>
       </c>
@@ -10965,7 +10970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>214</v>
       </c>
@@ -11024,7 +11029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>215</v>
       </c>
@@ -11083,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>216</v>
       </c>
@@ -11142,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>217</v>
       </c>
@@ -11201,7 +11206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>218</v>
       </c>
@@ -11260,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>219</v>
       </c>
@@ -11319,7 +11324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>220</v>
       </c>
@@ -11378,7 +11383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>221</v>
       </c>
@@ -11437,7 +11442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>222</v>
       </c>
@@ -11496,7 +11501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>223</v>
       </c>
@@ -11555,7 +11560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>224</v>
       </c>
@@ -11614,7 +11619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>225</v>
       </c>
@@ -11673,7 +11678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>226</v>
       </c>
@@ -11732,7 +11737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>227</v>
       </c>
@@ -11791,7 +11796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>228</v>
       </c>
@@ -11854,7 +11859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>230</v>
       </c>
@@ -11913,7 +11918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>231</v>
       </c>
@@ -11972,7 +11977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>232</v>
       </c>
@@ -12031,7 +12036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>233</v>
       </c>
@@ -12090,7 +12095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>234</v>
       </c>
@@ -12149,7 +12154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>235</v>
       </c>
@@ -12208,7 +12213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>236</v>
       </c>
@@ -12267,7 +12272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>237</v>
       </c>
@@ -12328,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>238</v>
       </c>
@@ -12387,7 +12392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>239</v>
       </c>
@@ -12446,7 +12451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>240</v>
       </c>
@@ -12507,7 +12512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>241</v>
       </c>
@@ -12566,7 +12571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>242</v>
       </c>
@@ -12625,7 +12630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>243</v>
       </c>
@@ -12684,7 +12689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>244</v>
       </c>
@@ -12747,7 +12752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>245</v>
       </c>
@@ -12814,7 +12819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>246</v>
       </c>
@@ -12871,7 +12876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>247</v>
       </c>
@@ -12930,7 +12935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>248</v>
       </c>
@@ -12991,7 +12996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>249</v>
       </c>
@@ -13054,7 +13059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>254</v>
       </c>
@@ -13113,7 +13118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>251</v>
       </c>
@@ -13174,7 +13179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>252</v>
       </c>
@@ -13235,7 +13240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>253</v>
       </c>
@@ -13294,7 +13299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>255</v>
       </c>
@@ -13353,7 +13358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>256</v>
       </c>
@@ -13412,7 +13417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>257</v>
       </c>
@@ -13471,7 +13476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>259</v>
       </c>
@@ -13532,7 +13537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>260</v>
       </c>
@@ -13591,7 +13596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>261</v>
       </c>
@@ -13650,7 +13655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>262</v>
       </c>
@@ -13709,7 +13714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>263</v>
       </c>
@@ -13768,7 +13773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>264</v>
       </c>
@@ -13827,7 +13832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>265</v>
       </c>
@@ -13886,7 +13891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>266</v>
       </c>
@@ -13945,7 +13950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>267</v>
       </c>
@@ -14004,7 +14009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>268</v>
       </c>
@@ -14063,7 +14068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>269</v>
       </c>
@@ -14122,7 +14127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>270</v>
       </c>
@@ -14181,7 +14186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>271</v>
       </c>
@@ -14240,7 +14245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>272</v>
       </c>
@@ -14299,7 +14304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>273</v>
       </c>
@@ -14358,7 +14363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12">
         <v>274</v>
       </c>
@@ -14423,7 +14428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>275</v>
       </c>
@@ -14482,7 +14487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14">
         <v>276</v>
       </c>
@@ -14549,7 +14554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>277</v>
       </c>
@@ -14614,7 +14619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>278</v>
       </c>
@@ -14673,7 +14678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>279</v>
       </c>
@@ -14732,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>280</v>
       </c>
@@ -14791,7 +14796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>281</v>
       </c>
@@ -14850,7 +14855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>282</v>
       </c>
@@ -14909,7 +14914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>283</v>
       </c>
@@ -14970,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>284</v>
       </c>
@@ -15029,7 +15034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>285</v>
       </c>
@@ -15088,7 +15093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>286</v>
       </c>
@@ -15149,7 +15154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>287</v>
       </c>
@@ -15208,7 +15213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>288</v>
       </c>
@@ -15267,7 +15272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>289</v>
       </c>
@@ -15326,7 +15331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>290</v>
       </c>
@@ -15385,7 +15390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>291</v>
       </c>
@@ -15444,7 +15449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>292</v>
       </c>
@@ -15505,7 +15510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>293</v>
       </c>
@@ -15564,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>294</v>
       </c>
@@ -15625,7 +15630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>295</v>
       </c>
@@ -15684,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>296</v>
       </c>
@@ -15743,7 +15748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>297</v>
       </c>
@@ -15802,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>298</v>
       </c>
@@ -15861,7 +15866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>300</v>
       </c>
@@ -15920,7 +15925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>301</v>
       </c>
@@ -15979,7 +15984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>302</v>
       </c>
@@ -16038,7 +16043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>303</v>
       </c>
@@ -16097,7 +16102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>304</v>
       </c>
@@ -16156,7 +16161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>305</v>
       </c>
@@ -16215,7 +16220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>306</v>
       </c>
@@ -16276,7 +16281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>307</v>
       </c>
@@ -16335,7 +16340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>308</v>
       </c>
@@ -16394,7 +16399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>309</v>
       </c>
@@ -16453,7 +16458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>310</v>
       </c>
@@ -16512,7 +16517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>311</v>
       </c>
@@ -16571,7 +16576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>312</v>
       </c>
@@ -16630,7 +16635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>313</v>
       </c>
@@ -16689,7 +16694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>314</v>
       </c>
@@ -16748,7 +16753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>315</v>
       </c>
@@ -16807,7 +16812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>316</v>
       </c>
@@ -16866,7 +16871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>317</v>
       </c>
@@ -16925,7 +16930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>318</v>
       </c>
@@ -16984,7 +16989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>319</v>
       </c>
@@ -17043,7 +17048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>320</v>
       </c>
@@ -17102,7 +17107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>321</v>
       </c>
@@ -17161,7 +17166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12">
         <v>323</v>
       </c>
@@ -17228,7 +17233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>324</v>
       </c>
@@ -17287,7 +17292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12">
         <v>325</v>
       </c>
@@ -17354,7 +17359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>326</v>
       </c>
@@ -17413,7 +17418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12">
         <v>327</v>
       </c>
@@ -17476,7 +17481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>328</v>
       </c>
@@ -17535,7 +17540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>329</v>
       </c>
@@ -17594,7 +17599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>331</v>
       </c>
@@ -17657,7 +17662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12">
         <v>332</v>
       </c>
@@ -17722,7 +17727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>334</v>
       </c>
@@ -17789,7 +17794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>335</v>
       </c>
@@ -17850,7 +17855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>336</v>
       </c>
@@ -17909,7 +17914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>337</v>
       </c>
@@ -17968,7 +17973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>338</v>
       </c>
@@ -18031,7 +18036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>339</v>
       </c>
@@ -18098,7 +18103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>340</v>
       </c>
@@ -18157,7 +18162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>341</v>
       </c>
@@ -18216,7 +18221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>344</v>
       </c>
@@ -18275,7 +18280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="32">
         <v>345</v>
       </c>
@@ -18340,7 +18345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>346</v>
       </c>
@@ -18399,7 +18404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>347</v>
       </c>
@@ -18458,7 +18463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>348</v>
       </c>
@@ -18517,7 +18522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>349</v>
       </c>
@@ -18576,7 +18581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>350</v>
       </c>
@@ -18635,7 +18640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>351</v>
       </c>
@@ -18694,7 +18699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>352</v>
       </c>
@@ -18753,7 +18758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="32">
         <v>353</v>
       </c>
@@ -18816,7 +18821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>354</v>
       </c>
@@ -18875,7 +18880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>355</v>
       </c>
@@ -18934,7 +18939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>356</v>
       </c>
@@ -18993,7 +18998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>357</v>
       </c>
@@ -19052,7 +19057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>358</v>
       </c>
@@ -19111,7 +19116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>359</v>
       </c>
@@ -19170,7 +19175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>360</v>
       </c>
@@ -19229,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:23" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>361</v>
       </c>
@@ -19294,7 +19299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>362</v>
       </c>
@@ -19353,7 +19358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>363</v>
       </c>
@@ -19412,7 +19417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12">
         <v>364</v>
       </c>
@@ -19477,7 +19482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>365</v>
       </c>
@@ -19536,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>366</v>
       </c>
@@ -19595,7 +19600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:23" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>367</v>
       </c>
@@ -19662,7 +19667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>368</v>
       </c>
@@ -19721,7 +19726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="14">
         <v>369</v>
       </c>
@@ -19784,7 +19789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>370</v>
       </c>
@@ -19843,7 +19848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>371</v>
       </c>
@@ -19902,7 +19907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>372</v>
       </c>
@@ -19961,7 +19966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>373</v>
       </c>
@@ -20020,7 +20025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>374</v>
       </c>
@@ -20079,7 +20084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>375</v>
       </c>
@@ -20138,7 +20143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>376</v>
       </c>
@@ -20203,7 +20208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>377</v>
       </c>
@@ -20266,7 +20271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>378</v>
       </c>
@@ -20325,7 +20330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12">
         <v>379</v>
       </c>
@@ -20390,7 +20395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>380</v>
       </c>
@@ -20449,7 +20454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>381</v>
       </c>
@@ -20508,7 +20513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>382</v>
       </c>
@@ -20567,7 +20572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>383</v>
       </c>
@@ -20626,7 +20631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>384</v>
       </c>
@@ -20685,7 +20690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12">
         <v>385</v>
       </c>
@@ -20750,7 +20755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>386</v>
       </c>
@@ -20809,7 +20814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>387</v>
       </c>
@@ -20870,7 +20875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>388</v>
       </c>
@@ -20929,7 +20934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>389</v>
       </c>
@@ -20988,7 +20993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>390</v>
       </c>
@@ -21047,7 +21052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>391</v>
       </c>
@@ -21106,7 +21111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>392</v>
       </c>
@@ -21165,7 +21170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>393</v>
       </c>
@@ -21224,7 +21229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>394</v>
       </c>
@@ -21283,7 +21288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>395</v>
       </c>
@@ -21342,7 +21347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>396</v>
       </c>
@@ -21401,7 +21406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>397</v>
       </c>
@@ -21460,7 +21465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>398</v>
       </c>
@@ -21519,7 +21524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>399</v>
       </c>
@@ -21578,7 +21583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>400</v>
       </c>
@@ -21637,7 +21642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>401</v>
       </c>
@@ -21698,7 +21703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>402</v>
       </c>
@@ -21757,7 +21762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>403</v>
       </c>
@@ -21816,7 +21821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>404</v>
       </c>
@@ -21875,7 +21880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>405</v>
       </c>
@@ -21934,7 +21939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>406</v>
       </c>
@@ -21993,7 +21998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>407</v>
       </c>
@@ -22052,7 +22057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>408</v>
       </c>
@@ -22111,7 +22116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>409</v>
       </c>
@@ -22170,7 +22175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>410</v>
       </c>
@@ -22229,7 +22234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>411</v>
       </c>
@@ -22288,7 +22293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>412</v>
       </c>
@@ -22347,7 +22352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>413</v>
       </c>
@@ -22406,7 +22411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>414</v>
       </c>
@@ -22463,7 +22468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>415</v>
       </c>
@@ -22520,7 +22525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>416</v>
       </c>
@@ -22577,7 +22582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>417</v>
       </c>
@@ -22634,7 +22639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>418</v>
       </c>
@@ -22691,7 +22696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>419</v>
       </c>
@@ -22750,7 +22755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>420</v>
       </c>
@@ -22809,7 +22814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>421</v>
       </c>
@@ -22868,7 +22873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>422</v>
       </c>
@@ -22927,7 +22932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="33">
         <v>423</v>
       </c>
@@ -22990,7 +22995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="33">
         <v>424</v>
       </c>
@@ -23053,7 +23058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>425</v>
       </c>
@@ -23112,7 +23117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>426</v>
       </c>
@@ -23171,7 +23176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:23" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>82</v>
       </c>
@@ -23230,7 +23235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>83</v>
       </c>
@@ -23289,7 +23294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>93</v>
       </c>
@@ -24185,7 +24190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12">
         <v>14</v>
       </c>
@@ -24250,7 +24255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>15</v>
       </c>
@@ -24309,7 +24314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>16</v>
       </c>
@@ -24368,7 +24373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>17</v>
       </c>
@@ -24427,7 +24432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>18</v>
       </c>
@@ -24486,7 +24491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>19</v>
       </c>
@@ -24545,7 +24550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>20</v>
       </c>
@@ -24604,7 +24609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>21</v>
       </c>
@@ -24663,7 +24668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>22</v>
       </c>
@@ -24722,7 +24727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>23</v>
       </c>
@@ -24781,7 +24786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>24</v>
       </c>
@@ -24840,7 +24845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>25</v>
       </c>
@@ -24899,7 +24904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>26</v>
       </c>
@@ -24958,7 +24963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>27</v>
       </c>
@@ -25017,7 +25022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>28</v>
       </c>
@@ -25076,7 +25081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>29</v>
       </c>
@@ -25135,7 +25140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>30</v>
       </c>
@@ -25194,7 +25199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>31</v>
       </c>
@@ -25251,7 +25256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>32</v>
       </c>
@@ -25310,7 +25315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>33</v>
       </c>
@@ -25367,7 +25372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>34</v>
       </c>
@@ -25426,7 +25431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="27" t="s">
         <v>478</v>
       </c>
@@ -25485,7 +25490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="27" t="s">
         <v>480</v>
       </c>
@@ -25544,7 +25549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>482</v>
       </c>
@@ -25603,7 +25608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>485</v>
       </c>
@@ -25662,7 +25667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>487</v>
       </c>
@@ -25721,7 +25726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>489</v>
       </c>
@@ -25780,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>492</v>
       </c>
@@ -25839,7 +25844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>42</v>
       </c>
@@ -25898,7 +25903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>43</v>
       </c>
@@ -25957,7 +25962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>44</v>
       </c>
@@ -26016,7 +26021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>45</v>
       </c>
@@ -26075,7 +26080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>46</v>
       </c>
@@ -26134,7 +26139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>47</v>
       </c>
@@ -26191,7 +26196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>48</v>
       </c>
@@ -26250,7 +26255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>49</v>
       </c>
@@ -26309,7 +26314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>502</v>
       </c>
@@ -26368,7 +26373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>504</v>
       </c>
@@ -26427,7 +26432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>506</v>
       </c>
@@ -26486,7 +26491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>508</v>
       </c>
@@ -26545,7 +26550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>510</v>
       </c>
@@ -26604,7 +26609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>512</v>
       </c>
@@ -26663,7 +26668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>514</v>
       </c>
@@ -26722,7 +26727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>516</v>
       </c>
@@ -26781,7 +26786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>518</v>
       </c>
@@ -26840,7 +26845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>59</v>
       </c>
@@ -26899,7 +26904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>60</v>
       </c>
@@ -26958,7 +26963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>61</v>
       </c>
@@ -27017,7 +27022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>62</v>
       </c>
@@ -27076,7 +27081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>63</v>
       </c>
@@ -27135,7 +27140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>64</v>
       </c>
@@ -27194,7 +27199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>65</v>
       </c>
@@ -27253,7 +27258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>66</v>
       </c>
@@ -27312,7 +27317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>67</v>
       </c>
@@ -27371,7 +27376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>75</v>
       </c>
@@ -27430,7 +27435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>76</v>
       </c>
@@ -27489,7 +27494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="12">
         <v>96</v>
       </c>
@@ -27556,7 +27561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
         <v>532</v>
       </c>
@@ -27619,7 +27624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
         <v>535</v>
       </c>
@@ -27682,7 +27687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
         <v>537</v>
       </c>
@@ -27745,7 +27750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="12" t="s">
         <v>539</v>
       </c>
@@ -27808,7 +27813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
         <v>541</v>
       </c>
@@ -27871,7 +27876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="12" t="s">
         <v>543</v>
       </c>
@@ -27934,7 +27939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
         <v>545</v>
       </c>
@@ -27997,7 +28002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>547</v>
       </c>
@@ -28058,7 +28063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>549</v>
       </c>
@@ -28119,7 +28124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>551</v>
       </c>
@@ -28180,7 +28185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>553</v>
       </c>
@@ -28241,7 +28246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>555</v>
       </c>
@@ -28302,7 +28307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>557</v>
       </c>
@@ -28363,7 +28368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>559</v>
       </c>
@@ -28424,7 +28429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>561</v>
       </c>
@@ -28485,7 +28490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>563</v>
       </c>
@@ -28546,7 +28551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>565</v>
       </c>
@@ -28607,7 +28612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>567</v>
       </c>
@@ -28668,7 +28673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>569</v>
       </c>
@@ -28729,7 +28734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>571</v>
       </c>
@@ -28790,7 +28795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>573</v>
       </c>
@@ -28851,7 +28856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>575</v>
       </c>
@@ -28912,7 +28917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>577</v>
       </c>
@@ -28973,7 +28978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>579</v>
       </c>
@@ -29034,7 +29039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>581</v>
       </c>
@@ -29095,7 +29100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>583</v>
       </c>
@@ -29156,7 +29161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>585</v>
       </c>
@@ -29217,7 +29222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>587</v>
       </c>
@@ -29278,7 +29283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>589</v>
       </c>
@@ -29339,7 +29344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>591</v>
       </c>
@@ -29400,7 +29405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>593</v>
       </c>
@@ -29459,7 +29464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>595</v>
       </c>
@@ -29648,7 +29653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>97</v>
       </c>
@@ -29711,7 +29716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>98</v>
       </c>
@@ -29774,7 +29779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>427</v>
       </c>
@@ -29833,7 +29838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>428</v>
       </c>
@@ -29892,7 +29897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>429</v>
       </c>
@@ -29951,7 +29956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>430</v>
       </c>
@@ -30010,7 +30015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>431</v>
       </c>
@@ -30069,7 +30074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>432</v>
       </c>
@@ -30128,7 +30133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>433</v>
       </c>
@@ -30187,7 +30192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>434</v>
       </c>
@@ -30246,7 +30251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>435</v>
       </c>
@@ -30305,7 +30310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>436</v>
       </c>
@@ -30364,7 +30369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>615</v>
       </c>
@@ -30423,7 +30428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>617</v>
       </c>
@@ -30482,7 +30487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>117</v>
       </c>
@@ -30541,7 +30546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="29">
         <v>109</v>
       </c>
@@ -30602,7 +30607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>621</v>
       </c>
@@ -30661,7 +30666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>623</v>
       </c>
@@ -30720,7 +30725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>625</v>
       </c>
@@ -30779,7 +30784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>627</v>
       </c>
@@ -30838,7 +30843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>437</v>
       </c>
@@ -30897,7 +30902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>630</v>
       </c>
@@ -30956,7 +30961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>632</v>
       </c>
@@ -31015,7 +31020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>634</v>
       </c>
@@ -31074,7 +31079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>636</v>
       </c>
@@ -31133,7 +31138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>638</v>
       </c>
@@ -31192,7 +31197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>641</v>
       </c>
@@ -31251,7 +31256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>643</v>
       </c>
@@ -31310,7 +31315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>438</v>
       </c>
@@ -31369,7 +31374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>439</v>
       </c>
@@ -31428,7 +31433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>440</v>
       </c>
@@ -31487,7 +31492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>999</v>
       </c>
@@ -31546,7 +31551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>998</v>
       </c>
@@ -31605,7 +31610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>441</v>
       </c>
@@ -31664,7 +31669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>442</v>
       </c>
@@ -31723,7 +31728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>443</v>
       </c>
@@ -31782,7 +31787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>444</v>
       </c>
@@ -31841,7 +31846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>445</v>
       </c>
@@ -31900,7 +31905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>446</v>
       </c>
@@ -31959,7 +31964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>447</v>
       </c>
@@ -32018,7 +32023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>448</v>
       </c>
@@ -32077,7 +32082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>449</v>
       </c>
@@ -32136,7 +32141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>450</v>
       </c>
@@ -32195,7 +32200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>451</v>
       </c>
@@ -32254,7 +32259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>452</v>
       </c>
@@ -32313,7 +32318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>453</v>
       </c>
@@ -32372,7 +32377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>454</v>
       </c>
@@ -32431,7 +32436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>455</v>
       </c>
@@ -32490,7 +32495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>456</v>
       </c>
@@ -32551,7 +32556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>457</v>
       </c>
@@ -32612,7 +32617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>458</v>
       </c>
@@ -32671,7 +32676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>459</v>
       </c>
@@ -32730,7 +32735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>460</v>
       </c>
@@ -32795,7 +32800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>462</v>
       </c>
@@ -32854,7 +32859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>463</v>
       </c>
@@ -32919,7 +32924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>464</v>
       </c>
@@ -32978,7 +32983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>465</v>
       </c>
@@ -33041,7 +33046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>466</v>
       </c>
@@ -33106,7 +33111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>467</v>
       </c>
@@ -33165,7 +33170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>468</v>
       </c>
@@ -33224,7 +33229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>469</v>
       </c>
@@ -33283,7 +33288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>470</v>
       </c>
@@ -33342,7 +33347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>471</v>
       </c>
@@ -33401,7 +33406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>472</v>
       </c>
@@ -34063,7 +34068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>473</v>
       </c>
@@ -34126,7 +34131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="34" t="s">
         <v>691</v>
       </c>
@@ -34189,7 +34194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="34" t="s">
         <v>693</v>
       </c>
@@ -34252,7 +34257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>695</v>
       </c>
@@ -34315,7 +34320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>697</v>
       </c>
@@ -34378,7 +34383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>699</v>
       </c>
@@ -34441,7 +34446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="26" t="s">
         <v>701</v>
       </c>
@@ -34506,7 +34511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>703</v>
       </c>
@@ -34569,7 +34574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>705</v>
       </c>
@@ -34632,7 +34637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>707</v>
       </c>
@@ -34695,7 +34700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>709</v>
       </c>
@@ -34758,7 +34763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>711</v>
       </c>
@@ -34821,7 +34826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>713</v>
       </c>
@@ -34884,7 +34889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>715</v>
       </c>
@@ -34947,7 +34952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>717</v>
       </c>
@@ -35010,7 +35015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>719</v>
       </c>
@@ -35073,7 +35078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>721</v>
       </c>
@@ -35136,7 +35141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="27" t="s">
         <v>723</v>
       </c>
@@ -35195,7 +35200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="27" t="s">
         <v>725</v>
       </c>
@@ -35254,7 +35259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="27" t="s">
         <v>727</v>
       </c>
@@ -35313,7 +35318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="27" t="s">
         <v>729</v>
       </c>
@@ -35372,7 +35377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="27" t="s">
         <v>731</v>
       </c>
@@ -35431,7 +35436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>733</v>
       </c>
@@ -35490,7 +35495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>735</v>
       </c>
@@ -35547,7 +35552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>737</v>
       </c>
@@ -35606,7 +35611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>739</v>
       </c>
@@ -35665,7 +35670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>741</v>
       </c>
@@ -35724,7 +35729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>743</v>
       </c>
@@ -35783,7 +35788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>745</v>
       </c>
@@ -35842,7 +35847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="29">
         <v>484</v>
       </c>
@@ -35901,7 +35906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>476</v>
       </c>
@@ -35966,7 +35971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>474</v>
       </c>
@@ -36029,7 +36034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>525</v>
       </c>
@@ -36082,7 +36087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>786</v>
       </c>
@@ -36135,7 +36140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>788</v>
       </c>
@@ -36188,7 +36193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>790</v>
       </c>
@@ -37340,7 +37345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="29">
         <v>487</v>
       </c>
@@ -37391,7 +37396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="29">
         <v>490</v>
       </c>
@@ -37442,7 +37447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="29">
         <v>491</v>
       </c>
@@ -37493,7 +37498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="29">
         <v>492</v>
       </c>
@@ -37544,7 +37549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="29">
         <v>493</v>
       </c>
@@ -37595,7 +37600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="29">
         <v>494</v>
       </c>
@@ -37646,7 +37651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="29">
         <v>495</v>
       </c>
@@ -37697,7 +37702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="29">
         <v>496</v>
       </c>
@@ -37748,7 +37753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="29">
         <v>498</v>
       </c>
@@ -37799,7 +37804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="29">
         <v>499</v>
       </c>
@@ -37850,7 +37855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="29">
         <v>500</v>
       </c>
@@ -37901,7 +37906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="29">
         <v>501</v>
       </c>
@@ -37952,7 +37957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="29">
         <v>502</v>
       </c>
@@ -38003,7 +38008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="29">
         <v>503</v>
       </c>
@@ -38054,7 +38059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="29">
         <v>504</v>
       </c>
@@ -38105,7 +38110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="29">
         <v>505</v>
       </c>
@@ -38156,7 +38161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="29">
         <v>508</v>
       </c>
@@ -38207,7 +38212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="29">
         <v>522</v>
       </c>
@@ -38258,7 +38263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="29">
         <v>527</v>
       </c>
@@ -38309,7 +38314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="29">
         <v>528</v>
       </c>
@@ -38362,7 +38367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="29">
         <v>541</v>
       </c>
@@ -38415,7 +38420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="29">
         <v>542</v>
       </c>
@@ -38468,7 +38473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="29">
         <v>546</v>
       </c>
@@ -38521,7 +38526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="29">
         <v>547</v>
       </c>
@@ -38574,7 +38579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="29">
         <v>552</v>
       </c>
@@ -38625,7 +38630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="29">
         <v>553</v>
       </c>
@@ -38676,7 +38681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="29">
         <v>556</v>
       </c>
@@ -38727,7 +38732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="29">
         <v>485</v>
       </c>
@@ -38778,7 +38783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="29">
         <v>488</v>
       </c>
@@ -38829,7 +38834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="29">
         <v>509</v>
       </c>
@@ -38880,7 +38885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="29">
         <v>475</v>
       </c>
@@ -38931,7 +38936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="29">
         <v>477</v>
       </c>
@@ -38982,7 +38987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="29">
         <v>478</v>
       </c>
@@ -39033,7 +39038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="29">
         <v>479</v>
       </c>
@@ -39084,7 +39089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="29">
         <v>480</v>
       </c>
@@ -39135,7 +39140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="29">
         <v>481</v>
       </c>
@@ -39186,7 +39191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="29">
         <v>486</v>
       </c>
@@ -39237,7 +39242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="29">
         <v>506</v>
       </c>
@@ -39288,7 +39293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="29">
         <v>507</v>
       </c>
@@ -39339,7 +39344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="29">
         <v>514</v>
       </c>
@@ -39390,7 +39395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="29">
         <v>515</v>
       </c>
@@ -39441,7 +39446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="29">
         <v>516</v>
       </c>
@@ -39492,7 +39497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="29">
         <v>519</v>
       </c>
@@ -39543,7 +39548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="29">
         <v>523</v>
       </c>
@@ -39594,7 +39599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="29">
         <v>524</v>
       </c>
@@ -39647,7 +39652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="29">
         <v>530</v>
       </c>
@@ -39698,7 +39703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="29">
         <v>531</v>
       </c>
@@ -39749,7 +39754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="29">
         <v>532</v>
       </c>
@@ -39802,7 +39807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="29">
         <v>533</v>
       </c>
@@ -39855,7 +39860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="29">
         <v>534</v>
       </c>
@@ -39908,7 +39913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="29">
         <v>535</v>
       </c>
@@ -39961,7 +39966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="29">
         <v>536</v>
       </c>
@@ -40014,7 +40019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="29">
         <v>537</v>
       </c>
@@ -40065,7 +40070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="29">
         <v>538</v>
       </c>
@@ -40116,7 +40121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="29">
         <v>539</v>
       </c>
@@ -40167,7 +40172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="29">
         <v>540</v>
       </c>
@@ -40218,7 +40223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="29">
         <v>543</v>
       </c>
@@ -40269,7 +40274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="29">
         <v>544</v>
       </c>
@@ -40322,7 +40327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="29">
         <v>550</v>
       </c>
@@ -40373,7 +40378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="29">
         <v>551</v>
       </c>
@@ -40424,7 +40429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="29">
         <v>554</v>
       </c>
@@ -40475,7 +40480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="29">
         <v>555</v>
       </c>
@@ -40526,7 +40531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="29">
         <v>510</v>
       </c>
@@ -40577,7 +40582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="29">
         <v>511</v>
       </c>
@@ -40628,7 +40633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="29">
         <v>513</v>
       </c>
@@ -40679,7 +40684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="29">
         <v>518</v>
       </c>
@@ -40730,7 +40735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="29">
         <v>526</v>
       </c>
@@ -40781,7 +40786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="29">
         <v>529</v>
       </c>
@@ -41029,7 +41034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="29">
         <v>967</v>
       </c>
@@ -41082,7 +41087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="29">
         <v>976</v>
       </c>
@@ -41135,7 +41140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="52">
         <v>978</v>
       </c>
@@ -41188,7 +41193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="29">
         <v>555</v>
       </c>
@@ -41239,7 +41244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="29">
         <v>969</v>
       </c>
@@ -41290,7 +41295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="29">
         <v>970</v>
       </c>
@@ -41341,7 +41346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="29">
         <v>972</v>
       </c>
@@ -41392,7 +41397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="29">
         <v>973</v>
       </c>
@@ -41443,7 +41448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="29">
         <v>800</v>
       </c>
@@ -41494,7 +41499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="29">
         <v>974</v>
       </c>
@@ -41545,7 +41550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="29">
         <v>975</v>
       </c>
@@ -41596,7 +41601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4">
         <v>519</v>
       </c>
@@ -41657,7 +41662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4">
         <v>977</v>
       </c>
@@ -41718,7 +41723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4">
         <v>979</v>
       </c>
@@ -41781,6 +41786,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="20">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="215" priority="115"/>
   </conditionalFormatting>
@@ -41818,9 +41830,9 @@
     <cfRule type="duplicateValues" dxfId="204" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="203" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
     <cfRule type="duplicateValues" dxfId="200" priority="97"/>
@@ -41849,74 +41861,74 @@
   <conditionalFormatting sqref="A501:A502">
     <cfRule type="duplicateValues" dxfId="184" priority="73"/>
     <cfRule type="duplicateValues" dxfId="183" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="180" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="69"/>
     <cfRule type="duplicateValues" dxfId="179" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
     <cfRule type="duplicateValues" dxfId="176" priority="61"/>
     <cfRule type="duplicateValues" dxfId="175" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="172" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="51"/>
     <cfRule type="duplicateValues" dxfId="170" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="168" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
-    <cfRule type="duplicateValues" dxfId="164" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="45"/>
     <cfRule type="duplicateValues" dxfId="163" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="47"/>
     <cfRule type="duplicateValues" dxfId="161" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="160" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="156" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="25"/>
     <cfRule type="duplicateValues" dxfId="153" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="152" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A585:A592">
-    <cfRule type="duplicateValues" dxfId="148" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
     <cfRule type="duplicateValues" dxfId="144" priority="39"/>
     <cfRule type="duplicateValues" dxfId="143" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="142" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="140" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
     <cfRule type="duplicateValues" dxfId="138" priority="98"/>
@@ -41927,20 +41939,20 @@
     <cfRule type="duplicateValues" dxfId="135" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="134" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="132" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
-    <cfRule type="duplicateValues" dxfId="130" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="128" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
     <cfRule type="duplicateValues" dxfId="126" priority="66"/>
@@ -41951,20 +41963,20 @@
     <cfRule type="duplicateValues" dxfId="123" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="122" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
     <cfRule type="duplicateValues" dxfId="120" priority="44"/>
     <cfRule type="duplicateValues" dxfId="119" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="118" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
-    <cfRule type="duplicateValues" dxfId="116" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
     <cfRule type="duplicateValues" dxfId="114" priority="20"/>
@@ -41979,10 +41991,10 @@
     <cfRule type="duplicateValues" dxfId="109" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D219">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D223">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -75762,201 +75774,201 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
-    <cfRule type="duplicateValues" dxfId="108" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A351:A354">
-    <cfRule type="duplicateValues" dxfId="107" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A355:A396">
-    <cfRule type="duplicateValues" dxfId="106" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A358:A365">
-    <cfRule type="duplicateValues" dxfId="105" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A366">
-    <cfRule type="duplicateValues" dxfId="104" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A367">
-    <cfRule type="duplicateValues" dxfId="103" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A368">
-    <cfRule type="duplicateValues" dxfId="102" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A369">
-    <cfRule type="duplicateValues" dxfId="101" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A370:A396">
-    <cfRule type="duplicateValues" dxfId="100" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A383">
-    <cfRule type="duplicateValues" dxfId="99" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A397">
-    <cfRule type="duplicateValues" dxfId="98" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A459:A474">
-    <cfRule type="duplicateValues" dxfId="97" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A493">
-    <cfRule type="duplicateValues" dxfId="96" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A494">
-    <cfRule type="duplicateValues" dxfId="93" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A495:A496">
-    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A497:A499">
-    <cfRule type="duplicateValues" dxfId="85" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A500">
-    <cfRule type="duplicateValues" dxfId="81" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A501:A502">
-    <cfRule type="duplicateValues" dxfId="77" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A503">
-    <cfRule type="duplicateValues" dxfId="73" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A504:A505">
-    <cfRule type="duplicateValues" dxfId="69" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A506">
-    <cfRule type="duplicateValues" dxfId="65" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A507:A508">
-    <cfRule type="duplicateValues" dxfId="61" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A509">
-    <cfRule type="duplicateValues" dxfId="57" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A510:A578">
-    <cfRule type="duplicateValues" dxfId="53" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A579:A580">
-    <cfRule type="duplicateValues" dxfId="49" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A582:A583">
-    <cfRule type="duplicateValues" dxfId="45" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A585:A592">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="37" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B490:B493">
-    <cfRule type="duplicateValues" dxfId="33" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B494">
-    <cfRule type="duplicateValues" dxfId="31" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B495:B496">
-    <cfRule type="duplicateValues" dxfId="29" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B497:B499">
-    <cfRule type="duplicateValues" dxfId="27" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B500">
-    <cfRule type="duplicateValues" dxfId="25" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B501:B502">
-    <cfRule type="duplicateValues" dxfId="23" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B503">
-    <cfRule type="duplicateValues" dxfId="21" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B504:B505">
-    <cfRule type="duplicateValues" dxfId="19" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B506">
-    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B507:B508">
-    <cfRule type="duplicateValues" dxfId="15" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B509">
-    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B510:B578">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B579:B580">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B581">
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B582:B583">
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B585:B592">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -76809,26 +76821,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -77063,10 +77055,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -77083,20 +77106,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2502" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3739CDA3-0CAC-4F4B-9CCB-E3DFAA7118E0}"/>
+  <xr:revisionPtr revIDLastSave="2503" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BD37E7-E6EF-4121-A1A7-423A05607C86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6555,7 +6555,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W595"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6650,7 +6649,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>68</v>
       </c>
@@ -6709,7 +6708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>69</v>
       </c>
@@ -6768,7 +6767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>73</v>
       </c>
@@ -6827,7 +6826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>74</v>
       </c>
@@ -6886,7 +6885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>77</v>
       </c>
@@ -6951,7 +6950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>78</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>79</v>
       </c>
@@ -7071,7 +7070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>84</v>
       </c>
@@ -7130,7 +7129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>85</v>
       </c>
@@ -7189,7 +7188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>86</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>87</v>
       </c>
@@ -7307,7 +7306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>88</v>
       </c>
@@ -7366,7 +7365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>89</v>
       </c>
@@ -7425,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>90</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>91</v>
       </c>
@@ -7543,7 +7542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>92</v>
       </c>
@@ -7602,7 +7601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>94</v>
       </c>
@@ -7661,7 +7660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>95</v>
       </c>
@@ -7720,7 +7719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>100</v>
       </c>
@@ -7779,7 +7778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>104</v>
       </c>
@@ -7838,7 +7837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>106</v>
       </c>
@@ -7897,7 +7896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>108</v>
       </c>
@@ -7956,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>110</v>
       </c>
@@ -8015,7 +8014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>111</v>
       </c>
@@ -8074,7 +8073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>112</v>
       </c>
@@ -8133,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>113</v>
       </c>
@@ -8192,7 +8191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>114</v>
       </c>
@@ -8251,7 +8250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>115</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>116</v>
       </c>
@@ -8369,7 +8368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>118</v>
       </c>
@@ -8428,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>121</v>
       </c>
@@ -8487,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>122</v>
       </c>
@@ -8546,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>124</v>
       </c>
@@ -8605,7 +8604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>125</v>
       </c>
@@ -8664,7 +8663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>126</v>
       </c>
@@ -8723,7 +8722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>127</v>
       </c>
@@ -8782,7 +8781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>128</v>
       </c>
@@ -8841,7 +8840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>133</v>
       </c>
@@ -8900,7 +8899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>136</v>
       </c>
@@ -8959,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>137</v>
       </c>
@@ -9018,7 +9017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>139</v>
       </c>
@@ -9077,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>143</v>
       </c>
@@ -9138,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>144</v>
       </c>
@@ -9199,7 +9198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>145</v>
       </c>
@@ -9258,7 +9257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>146</v>
       </c>
@@ -9317,7 +9316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>147</v>
       </c>
@@ -9378,7 +9377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>148</v>
       </c>
@@ -9443,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>150</v>
       </c>
@@ -9502,7 +9501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>151</v>
       </c>
@@ -9561,7 +9560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>157</v>
       </c>
@@ -9620,7 +9619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>159</v>
       </c>
@@ -9679,7 +9678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>167</v>
       </c>
@@ -9738,7 +9737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>171</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>172</v>
       </c>
@@ -9858,7 +9857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>174</v>
       </c>
@@ -9917,7 +9916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>176</v>
       </c>
@@ -9978,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>193</v>
       </c>
@@ -10043,7 +10042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>194</v>
       </c>
@@ -10108,7 +10107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>195</v>
       </c>
@@ -10169,7 +10168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>196</v>
       </c>
@@ -10228,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>197</v>
       </c>
@@ -10287,7 +10286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>199</v>
       </c>
@@ -10346,7 +10345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>200</v>
       </c>
@@ -10409,7 +10408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>202</v>
       </c>
@@ -10474,7 +10473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>203</v>
       </c>
@@ -10539,7 +10538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>204</v>
       </c>
@@ -10604,7 +10603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>205</v>
       </c>
@@ -10667,7 +10666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>206</v>
       </c>
@@ -10730,7 +10729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>207</v>
       </c>
@@ -10793,7 +10792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>208</v>
       </c>
@@ -10852,7 +10851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>210</v>
       </c>
@@ -10911,7 +10910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>213</v>
       </c>
@@ -10970,7 +10969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>214</v>
       </c>
@@ -11029,7 +11028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>215</v>
       </c>
@@ -11088,7 +11087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>216</v>
       </c>
@@ -11147,7 +11146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>217</v>
       </c>
@@ -11206,7 +11205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>218</v>
       </c>
@@ -11265,7 +11264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>219</v>
       </c>
@@ -11324,7 +11323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>220</v>
       </c>
@@ -11383,7 +11382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>221</v>
       </c>
@@ -11442,7 +11441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>222</v>
       </c>
@@ -11501,7 +11500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>223</v>
       </c>
@@ -11560,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>224</v>
       </c>
@@ -11619,7 +11618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>225</v>
       </c>
@@ -11678,7 +11677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>226</v>
       </c>
@@ -11737,7 +11736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>227</v>
       </c>
@@ -11796,7 +11795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>228</v>
       </c>
@@ -11859,7 +11858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>230</v>
       </c>
@@ -11918,7 +11917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>231</v>
       </c>
@@ -11977,7 +11976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>232</v>
       </c>
@@ -12036,7 +12035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>233</v>
       </c>
@@ -12095,7 +12094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>234</v>
       </c>
@@ -12154,7 +12153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>235</v>
       </c>
@@ -12213,7 +12212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>236</v>
       </c>
@@ -12272,7 +12271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>237</v>
       </c>
@@ -12333,7 +12332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>238</v>
       </c>
@@ -12392,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>239</v>
       </c>
@@ -12451,7 +12450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>240</v>
       </c>
@@ -12512,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>241</v>
       </c>
@@ -12571,7 +12570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>242</v>
       </c>
@@ -12630,7 +12629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>243</v>
       </c>
@@ -12689,7 +12688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>244</v>
       </c>
@@ -12752,7 +12751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>245</v>
       </c>
@@ -12819,7 +12818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>246</v>
       </c>
@@ -12876,7 +12875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>247</v>
       </c>
@@ -12935,7 +12934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>248</v>
       </c>
@@ -12996,7 +12995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>249</v>
       </c>
@@ -13059,7 +13058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>254</v>
       </c>
@@ -13118,7 +13117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>251</v>
       </c>
@@ -13179,7 +13178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>252</v>
       </c>
@@ -13240,7 +13239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>253</v>
       </c>
@@ -13299,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>255</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>256</v>
       </c>
@@ -13417,7 +13416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>257</v>
       </c>
@@ -13476,7 +13475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>259</v>
       </c>
@@ -13537,7 +13536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>260</v>
       </c>
@@ -13596,7 +13595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>261</v>
       </c>
@@ -13655,7 +13654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>262</v>
       </c>
@@ -13714,7 +13713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>263</v>
       </c>
@@ -13773,7 +13772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>264</v>
       </c>
@@ -13832,7 +13831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>265</v>
       </c>
@@ -13891,7 +13890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>266</v>
       </c>
@@ -13950,7 +13949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>267</v>
       </c>
@@ -14009,7 +14008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>268</v>
       </c>
@@ -14068,7 +14067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>269</v>
       </c>
@@ -14127,7 +14126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>270</v>
       </c>
@@ -14186,7 +14185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>271</v>
       </c>
@@ -14245,7 +14244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>272</v>
       </c>
@@ -14304,7 +14303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>273</v>
       </c>
@@ -14363,7 +14362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" s="12">
         <v>274</v>
       </c>
@@ -14428,7 +14427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>275</v>
       </c>
@@ -14487,7 +14486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133" s="14">
         <v>276</v>
       </c>
@@ -14554,7 +14553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>277</v>
       </c>
@@ -14619,7 +14618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>278</v>
       </c>
@@ -14678,7 +14677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>279</v>
       </c>
@@ -14737,7 +14736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>280</v>
       </c>
@@ -14796,7 +14795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>281</v>
       </c>
@@ -14855,7 +14854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>282</v>
       </c>
@@ -14914,7 +14913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>283</v>
       </c>
@@ -14975,7 +14974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>284</v>
       </c>
@@ -15034,7 +15033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>285</v>
       </c>
@@ -15093,7 +15092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>286</v>
       </c>
@@ -15154,7 +15153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>287</v>
       </c>
@@ -15213,7 +15212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>288</v>
       </c>
@@ -15272,7 +15271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>289</v>
       </c>
@@ -15331,7 +15330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>290</v>
       </c>
@@ -15390,7 +15389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>291</v>
       </c>
@@ -15449,7 +15448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>292</v>
       </c>
@@ -15510,7 +15509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>293</v>
       </c>
@@ -15569,7 +15568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>294</v>
       </c>
@@ -15630,7 +15629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>295</v>
       </c>
@@ -15689,7 +15688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>296</v>
       </c>
@@ -15748,7 +15747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>297</v>
       </c>
@@ -15807,7 +15806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>298</v>
       </c>
@@ -15866,7 +15865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>300</v>
       </c>
@@ -15925,7 +15924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>301</v>
       </c>
@@ -15984,7 +15983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>302</v>
       </c>
@@ -16043,7 +16042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>303</v>
       </c>
@@ -16102,7 +16101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>304</v>
       </c>
@@ -16161,7 +16160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>305</v>
       </c>
@@ -16220,7 +16219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>306</v>
       </c>
@@ -16281,7 +16280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>307</v>
       </c>
@@ -16340,7 +16339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>308</v>
       </c>
@@ -16399,7 +16398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>309</v>
       </c>
@@ -16458,7 +16457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>310</v>
       </c>
@@ -16517,7 +16516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>311</v>
       </c>
@@ -16576,7 +16575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>312</v>
       </c>
@@ -16635,7 +16634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>313</v>
       </c>
@@ -16694,7 +16693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>314</v>
       </c>
@@ -16753,7 +16752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>315</v>
       </c>
@@ -16812,7 +16811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>316</v>
       </c>
@@ -16871,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>317</v>
       </c>
@@ -16930,7 +16929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>318</v>
       </c>
@@ -16989,7 +16988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>319</v>
       </c>
@@ -17048,7 +17047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>320</v>
       </c>
@@ -17107,7 +17106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>321</v>
       </c>
@@ -17166,7 +17165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" s="12">
         <v>323</v>
       </c>
@@ -17233,7 +17232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>324</v>
       </c>
@@ -17292,7 +17291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" s="12">
         <v>325</v>
       </c>
@@ -17359,7 +17358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>326</v>
       </c>
@@ -17418,7 +17417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" s="12">
         <v>327</v>
       </c>
@@ -17481,7 +17480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>328</v>
       </c>
@@ -17540,7 +17539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>329</v>
       </c>
@@ -17599,7 +17598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>331</v>
       </c>
@@ -17662,7 +17661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" s="12">
         <v>332</v>
       </c>
@@ -17727,7 +17726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>334</v>
       </c>
@@ -17794,7 +17793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>335</v>
       </c>
@@ -17855,7 +17854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>336</v>
       </c>
@@ -17914,7 +17913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>337</v>
       </c>
@@ -17973,7 +17972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>338</v>
       </c>
@@ -18036,7 +18035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>339</v>
       </c>
@@ -18103,7 +18102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>340</v>
       </c>
@@ -18162,7 +18161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>341</v>
       </c>
@@ -18221,7 +18220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>344</v>
       </c>
@@ -18280,7 +18279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A196" s="32">
         <v>345</v>
       </c>
@@ -18345,7 +18344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>346</v>
       </c>
@@ -18404,7 +18403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>347</v>
       </c>
@@ -18463,7 +18462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>348</v>
       </c>
@@ -18522,7 +18521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>349</v>
       </c>
@@ -18581,7 +18580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>350</v>
       </c>
@@ -18640,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>351</v>
       </c>
@@ -18699,7 +18698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>352</v>
       </c>
@@ -18758,7 +18757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A204" s="32">
         <v>353</v>
       </c>
@@ -18821,7 +18820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>354</v>
       </c>
@@ -18880,7 +18879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>355</v>
       </c>
@@ -18939,7 +18938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>356</v>
       </c>
@@ -18998,7 +18997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>357</v>
       </c>
@@ -19057,7 +19056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>358</v>
       </c>
@@ -19116,7 +19115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>359</v>
       </c>
@@ -19175,7 +19174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>360</v>
       </c>
@@ -19234,7 +19233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:23" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>361</v>
       </c>
@@ -19299,7 +19298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>362</v>
       </c>
@@ -19358,7 +19357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>363</v>
       </c>
@@ -19417,7 +19416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A215" s="12">
         <v>364</v>
       </c>
@@ -19482,7 +19481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>365</v>
       </c>
@@ -19541,7 +19540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>366</v>
       </c>
@@ -19600,7 +19599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:23" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>367</v>
       </c>
@@ -19667,7 +19666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>368</v>
       </c>
@@ -19726,7 +19725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A220" s="14">
         <v>369</v>
       </c>
@@ -19789,7 +19788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>370</v>
       </c>
@@ -19848,7 +19847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>371</v>
       </c>
@@ -19907,7 +19906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>372</v>
       </c>
@@ -19966,7 +19965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>373</v>
       </c>
@@ -20025,7 +20024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>374</v>
       </c>
@@ -20084,7 +20083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>375</v>
       </c>
@@ -20143,7 +20142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>376</v>
       </c>
@@ -20208,7 +20207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>377</v>
       </c>
@@ -20271,7 +20270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>378</v>
       </c>
@@ -20330,7 +20329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A230" s="12">
         <v>379</v>
       </c>
@@ -20395,7 +20394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>380</v>
       </c>
@@ -20454,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>381</v>
       </c>
@@ -20513,7 +20512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>382</v>
       </c>
@@ -20572,7 +20571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>383</v>
       </c>
@@ -20631,7 +20630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>384</v>
       </c>
@@ -20690,7 +20689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A236" s="12">
         <v>385</v>
       </c>
@@ -20755,7 +20754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>386</v>
       </c>
@@ -20814,7 +20813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>387</v>
       </c>
@@ -20875,7 +20874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>388</v>
       </c>
@@ -20934,7 +20933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>389</v>
       </c>
@@ -20993,7 +20992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>390</v>
       </c>
@@ -21052,7 +21051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>391</v>
       </c>
@@ -21111,7 +21110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>392</v>
       </c>
@@ -21170,7 +21169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>393</v>
       </c>
@@ -21229,7 +21228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>394</v>
       </c>
@@ -21288,7 +21287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>395</v>
       </c>
@@ -21347,7 +21346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>396</v>
       </c>
@@ -21406,7 +21405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>397</v>
       </c>
@@ -21465,7 +21464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>398</v>
       </c>
@@ -21524,7 +21523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>399</v>
       </c>
@@ -21583,7 +21582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>400</v>
       </c>
@@ -21642,7 +21641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>401</v>
       </c>
@@ -21703,7 +21702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>402</v>
       </c>
@@ -21762,7 +21761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>403</v>
       </c>
@@ -21821,7 +21820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>404</v>
       </c>
@@ -21880,7 +21879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>405</v>
       </c>
@@ -21939,7 +21938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>406</v>
       </c>
@@ -21998,7 +21997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>407</v>
       </c>
@@ -22057,7 +22056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>408</v>
       </c>
@@ -22116,7 +22115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>409</v>
       </c>
@@ -22175,7 +22174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>410</v>
       </c>
@@ -22234,7 +22233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>411</v>
       </c>
@@ -22293,7 +22292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>412</v>
       </c>
@@ -22352,7 +22351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>413</v>
       </c>
@@ -22411,7 +22410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>414</v>
       </c>
@@ -22468,7 +22467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>415</v>
       </c>
@@ -22525,7 +22524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>416</v>
       </c>
@@ -22582,7 +22581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>417</v>
       </c>
@@ -22639,7 +22638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>418</v>
       </c>
@@ -22696,7 +22695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>419</v>
       </c>
@@ -22755,7 +22754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>420</v>
       </c>
@@ -22814,7 +22813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>421</v>
       </c>
@@ -22873,7 +22872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>422</v>
       </c>
@@ -22932,7 +22931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A274" s="33">
         <v>423</v>
       </c>
@@ -22995,7 +22994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A275" s="33">
         <v>424</v>
       </c>
@@ -23058,7 +23057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>425</v>
       </c>
@@ -23117,7 +23116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>426</v>
       </c>
@@ -23176,7 +23175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="26.1" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:23" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>82</v>
       </c>
@@ -23235,7 +23234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>83</v>
       </c>
@@ -23294,7 +23293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>93</v>
       </c>
@@ -24190,7 +24189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A294" s="12">
         <v>14</v>
       </c>
@@ -24255,7 +24254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>15</v>
       </c>
@@ -24314,7 +24313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>16</v>
       </c>
@@ -24373,7 +24372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>17</v>
       </c>
@@ -24432,7 +24431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>18</v>
       </c>
@@ -24491,7 +24490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>19</v>
       </c>
@@ -24550,7 +24549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>20</v>
       </c>
@@ -24609,7 +24608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>21</v>
       </c>
@@ -24668,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>22</v>
       </c>
@@ -24727,7 +24726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>23</v>
       </c>
@@ -24786,7 +24785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>24</v>
       </c>
@@ -24845,7 +24844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>25</v>
       </c>
@@ -24904,7 +24903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>26</v>
       </c>
@@ -24963,7 +24962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>27</v>
       </c>
@@ -25022,7 +25021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>28</v>
       </c>
@@ -25081,7 +25080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>29</v>
       </c>
@@ -25140,7 +25139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>30</v>
       </c>
@@ -25199,7 +25198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>31</v>
       </c>
@@ -25256,7 +25255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>32</v>
       </c>
@@ -25315,7 +25314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>33</v>
       </c>
@@ -25372,7 +25371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>34</v>
       </c>
@@ -25431,7 +25430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A315" s="27" t="s">
         <v>478</v>
       </c>
@@ -25490,7 +25489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A316" s="27" t="s">
         <v>480</v>
       </c>
@@ -25549,7 +25548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>482</v>
       </c>
@@ -25608,7 +25607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>485</v>
       </c>
@@ -25667,7 +25666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>487</v>
       </c>
@@ -25726,7 +25725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>489</v>
       </c>
@@ -25785,7 +25784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>492</v>
       </c>
@@ -25844,7 +25843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>42</v>
       </c>
@@ -25903,7 +25902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>43</v>
       </c>
@@ -25962,7 +25961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>44</v>
       </c>
@@ -26021,7 +26020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>45</v>
       </c>
@@ -26080,7 +26079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>46</v>
       </c>
@@ -26139,7 +26138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>47</v>
       </c>
@@ -26196,7 +26195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>48</v>
       </c>
@@ -26255,7 +26254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>49</v>
       </c>
@@ -26314,7 +26313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>502</v>
       </c>
@@ -26373,7 +26372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>504</v>
       </c>
@@ -26432,7 +26431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>506</v>
       </c>
@@ -26491,7 +26490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>508</v>
       </c>
@@ -26550,7 +26549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>510</v>
       </c>
@@ -26609,7 +26608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>512</v>
       </c>
@@ -26668,7 +26667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>514</v>
       </c>
@@ -26727,7 +26726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>516</v>
       </c>
@@ -26786,7 +26785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>518</v>
       </c>
@@ -26845,7 +26844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>59</v>
       </c>
@@ -26904,7 +26903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>60</v>
       </c>
@@ -26963,7 +26962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>61</v>
       </c>
@@ -27022,7 +27021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>62</v>
       </c>
@@ -27081,7 +27080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>63</v>
       </c>
@@ -27140,7 +27139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>64</v>
       </c>
@@ -27199,7 +27198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>65</v>
       </c>
@@ -27258,7 +27257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>66</v>
       </c>
@@ -27317,7 +27316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>67</v>
       </c>
@@ -27376,7 +27375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>75</v>
       </c>
@@ -27435,7 +27434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>76</v>
       </c>
@@ -27494,7 +27493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A350" s="12">
         <v>96</v>
       </c>
@@ -27561,7 +27560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
         <v>532</v>
       </c>
@@ -27624,7 +27623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
         <v>535</v>
       </c>
@@ -27687,7 +27686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
         <v>537</v>
       </c>
@@ -27750,7 +27749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A354" s="12" t="s">
         <v>539</v>
       </c>
@@ -27813,7 +27812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
         <v>541</v>
       </c>
@@ -27876,7 +27875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A356" s="12" t="s">
         <v>543</v>
       </c>
@@ -27939,7 +27938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
         <v>545</v>
       </c>
@@ -28002,7 +28001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>547</v>
       </c>
@@ -28063,7 +28062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>549</v>
       </c>
@@ -28124,7 +28123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>551</v>
       </c>
@@ -28185,7 +28184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>553</v>
       </c>
@@ -28246,7 +28245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>555</v>
       </c>
@@ -28307,7 +28306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>557</v>
       </c>
@@ -28368,7 +28367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>559</v>
       </c>
@@ -28429,7 +28428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>561</v>
       </c>
@@ -28490,7 +28489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>563</v>
       </c>
@@ -28551,7 +28550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>565</v>
       </c>
@@ -28612,7 +28611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>567</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>569</v>
       </c>
@@ -28734,7 +28733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>571</v>
       </c>
@@ -28795,7 +28794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>573</v>
       </c>
@@ -28856,7 +28855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>575</v>
       </c>
@@ -28917,7 +28916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>577</v>
       </c>
@@ -28978,7 +28977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>579</v>
       </c>
@@ -29039,7 +29038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>581</v>
       </c>
@@ -29100,7 +29099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>583</v>
       </c>
@@ -29161,7 +29160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>585</v>
       </c>
@@ -29222,7 +29221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>587</v>
       </c>
@@ -29283,7 +29282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>589</v>
       </c>
@@ -29344,7 +29343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>591</v>
       </c>
@@ -29405,7 +29404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>593</v>
       </c>
@@ -29464,7 +29463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>595</v>
       </c>
@@ -29653,7 +29652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>97</v>
       </c>
@@ -29716,7 +29715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>98</v>
       </c>
@@ -29779,7 +29778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>427</v>
       </c>
@@ -29838,7 +29837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>428</v>
       </c>
@@ -29897,7 +29896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>429</v>
       </c>
@@ -29956,7 +29955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>430</v>
       </c>
@@ -30015,7 +30014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>431</v>
       </c>
@@ -30074,7 +30073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>432</v>
       </c>
@@ -30133,7 +30132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>433</v>
       </c>
@@ -30192,7 +30191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>434</v>
       </c>
@@ -30251,7 +30250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>435</v>
       </c>
@@ -30310,7 +30309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>436</v>
       </c>
@@ -30369,7 +30368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>615</v>
       </c>
@@ -30428,7 +30427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>617</v>
       </c>
@@ -30487,7 +30486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>117</v>
       </c>
@@ -30546,7 +30545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A400" s="29">
         <v>109</v>
       </c>
@@ -30607,7 +30606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>621</v>
       </c>
@@ -30666,7 +30665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>623</v>
       </c>
@@ -30725,7 +30724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>625</v>
       </c>
@@ -30784,7 +30783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>627</v>
       </c>
@@ -30843,7 +30842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>437</v>
       </c>
@@ -30902,7 +30901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>630</v>
       </c>
@@ -30961,7 +30960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>632</v>
       </c>
@@ -31020,7 +31019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>634</v>
       </c>
@@ -31079,7 +31078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>636</v>
       </c>
@@ -31138,7 +31137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>638</v>
       </c>
@@ -31197,7 +31196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>641</v>
       </c>
@@ -31256,7 +31255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>643</v>
       </c>
@@ -31315,7 +31314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>438</v>
       </c>
@@ -31374,7 +31373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>439</v>
       </c>
@@ -31433,7 +31432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>440</v>
       </c>
@@ -31492,7 +31491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>999</v>
       </c>
@@ -31551,7 +31550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>998</v>
       </c>
@@ -31610,7 +31609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>441</v>
       </c>
@@ -31669,7 +31668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>442</v>
       </c>
@@ -31728,7 +31727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>443</v>
       </c>
@@ -31787,7 +31786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>444</v>
       </c>
@@ -31846,7 +31845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>445</v>
       </c>
@@ -31905,7 +31904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>446</v>
       </c>
@@ -31964,7 +31963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>447</v>
       </c>
@@ -32023,7 +32022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>448</v>
       </c>
@@ -32082,7 +32081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>449</v>
       </c>
@@ -32141,7 +32140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>450</v>
       </c>
@@ -32200,7 +32199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>451</v>
       </c>
@@ -32259,7 +32258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>452</v>
       </c>
@@ -32318,7 +32317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>453</v>
       </c>
@@ -32377,7 +32376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>454</v>
       </c>
@@ -32436,7 +32435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>455</v>
       </c>
@@ -32495,7 +32494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>456</v>
       </c>
@@ -32556,7 +32555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>457</v>
       </c>
@@ -32617,7 +32616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>458</v>
       </c>
@@ -32676,7 +32675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>459</v>
       </c>
@@ -32735,7 +32734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>460</v>
       </c>
@@ -32800,7 +32799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>462</v>
       </c>
@@ -32859,7 +32858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>463</v>
       </c>
@@ -32924,7 +32923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>464</v>
       </c>
@@ -32983,7 +32982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>465</v>
       </c>
@@ -33046,7 +33045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>466</v>
       </c>
@@ -33111,7 +33110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>467</v>
       </c>
@@ -33170,7 +33169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>468</v>
       </c>
@@ -33229,7 +33228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>469</v>
       </c>
@@ -33288,7 +33287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>470</v>
       </c>
@@ -33347,7 +33346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>471</v>
       </c>
@@ -33406,7 +33405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>472</v>
       </c>
@@ -34068,7 +34067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>473</v>
       </c>
@@ -34131,7 +34130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A459" s="34" t="s">
         <v>691</v>
       </c>
@@ -34194,7 +34193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A460" s="34" t="s">
         <v>693</v>
       </c>
@@ -34257,7 +34256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>695</v>
       </c>
@@ -34320,7 +34319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>697</v>
       </c>
@@ -34383,7 +34382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>699</v>
       </c>
@@ -34446,7 +34445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A464" s="26" t="s">
         <v>701</v>
       </c>
@@ -34511,7 +34510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>703</v>
       </c>
@@ -34574,7 +34573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>705</v>
       </c>
@@ -34637,7 +34636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>707</v>
       </c>
@@ -34700,7 +34699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>709</v>
       </c>
@@ -34763,7 +34762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>711</v>
       </c>
@@ -34826,7 +34825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>713</v>
       </c>
@@ -34889,7 +34888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>715</v>
       </c>
@@ -34952,7 +34951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>717</v>
       </c>
@@ -35015,7 +35014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>719</v>
       </c>
@@ -35078,7 +35077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>721</v>
       </c>
@@ -35141,7 +35140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A475" s="27" t="s">
         <v>723</v>
       </c>
@@ -35200,7 +35199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A476" s="27" t="s">
         <v>725</v>
       </c>
@@ -35259,7 +35258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A477" s="27" t="s">
         <v>727</v>
       </c>
@@ -35318,7 +35317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A478" s="27" t="s">
         <v>729</v>
       </c>
@@ -35377,7 +35376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A479" s="27" t="s">
         <v>731</v>
       </c>
@@ -35436,7 +35435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>733</v>
       </c>
@@ -35495,7 +35494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>735</v>
       </c>
@@ -35552,7 +35551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>737</v>
       </c>
@@ -35611,7 +35610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>739</v>
       </c>
@@ -35670,7 +35669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>741</v>
       </c>
@@ -35729,7 +35728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>743</v>
       </c>
@@ -35788,7 +35787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>745</v>
       </c>
@@ -35847,7 +35846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A487" s="29">
         <v>484</v>
       </c>
@@ -35906,7 +35905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>476</v>
       </c>
@@ -35971,7 +35970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>474</v>
       </c>
@@ -36034,7 +36033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>525</v>
       </c>
@@ -36087,7 +36086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>786</v>
       </c>
@@ -36140,7 +36139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>788</v>
       </c>
@@ -36193,7 +36192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>790</v>
       </c>
@@ -37345,7 +37344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A511" s="29">
         <v>487</v>
       </c>
@@ -37396,7 +37395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A512" s="29">
         <v>490</v>
       </c>
@@ -37447,7 +37446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A513" s="29">
         <v>491</v>
       </c>
@@ -37498,7 +37497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A514" s="29">
         <v>492</v>
       </c>
@@ -37549,7 +37548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A515" s="29">
         <v>493</v>
       </c>
@@ -37600,7 +37599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A516" s="29">
         <v>494</v>
       </c>
@@ -37651,7 +37650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A517" s="29">
         <v>495</v>
       </c>
@@ -37702,7 +37701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A518" s="29">
         <v>496</v>
       </c>
@@ -37753,7 +37752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A519" s="29">
         <v>498</v>
       </c>
@@ -37804,7 +37803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A520" s="29">
         <v>499</v>
       </c>
@@ -37855,7 +37854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A521" s="29">
         <v>500</v>
       </c>
@@ -37906,7 +37905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A522" s="29">
         <v>501</v>
       </c>
@@ -37957,7 +37956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A523" s="29">
         <v>502</v>
       </c>
@@ -38008,7 +38007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A524" s="29">
         <v>503</v>
       </c>
@@ -38059,7 +38058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A525" s="29">
         <v>504</v>
       </c>
@@ -38110,7 +38109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A526" s="29">
         <v>505</v>
       </c>
@@ -38161,7 +38160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A527" s="29">
         <v>508</v>
       </c>
@@ -38212,7 +38211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A528" s="29">
         <v>522</v>
       </c>
@@ -38263,7 +38262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A529" s="29">
         <v>527</v>
       </c>
@@ -38314,7 +38313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A530" s="29">
         <v>528</v>
       </c>
@@ -38367,7 +38366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A531" s="29">
         <v>541</v>
       </c>
@@ -38420,7 +38419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A532" s="29">
         <v>542</v>
       </c>
@@ -38473,7 +38472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A533" s="29">
         <v>546</v>
       </c>
@@ -38526,7 +38525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A534" s="29">
         <v>547</v>
       </c>
@@ -38579,7 +38578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A535" s="29">
         <v>552</v>
       </c>
@@ -38630,7 +38629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A536" s="29">
         <v>553</v>
       </c>
@@ -38681,7 +38680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A537" s="29">
         <v>556</v>
       </c>
@@ -38732,7 +38731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A538" s="29">
         <v>485</v>
       </c>
@@ -38783,7 +38782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A539" s="29">
         <v>488</v>
       </c>
@@ -38834,7 +38833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A540" s="29">
         <v>509</v>
       </c>
@@ -38885,7 +38884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A541" s="29">
         <v>475</v>
       </c>
@@ -38936,7 +38935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A542" s="29">
         <v>477</v>
       </c>
@@ -38987,7 +38986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A543" s="29">
         <v>478</v>
       </c>
@@ -39038,7 +39037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A544" s="29">
         <v>479</v>
       </c>
@@ -39089,7 +39088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A545" s="29">
         <v>480</v>
       </c>
@@ -39140,7 +39139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A546" s="29">
         <v>481</v>
       </c>
@@ -39191,7 +39190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A547" s="29">
         <v>486</v>
       </c>
@@ -39242,7 +39241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A548" s="29">
         <v>506</v>
       </c>
@@ -39293,7 +39292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A549" s="29">
         <v>507</v>
       </c>
@@ -39344,7 +39343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A550" s="29">
         <v>514</v>
       </c>
@@ -39395,7 +39394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A551" s="29">
         <v>515</v>
       </c>
@@ -39446,7 +39445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A552" s="29">
         <v>516</v>
       </c>
@@ -39497,7 +39496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A553" s="29">
         <v>519</v>
       </c>
@@ -39548,7 +39547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A554" s="29">
         <v>523</v>
       </c>
@@ -39599,7 +39598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A555" s="29">
         <v>524</v>
       </c>
@@ -39652,7 +39651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A556" s="29">
         <v>530</v>
       </c>
@@ -39703,7 +39702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A557" s="29">
         <v>531</v>
       </c>
@@ -39754,7 +39753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A558" s="29">
         <v>532</v>
       </c>
@@ -39807,7 +39806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A559" s="29">
         <v>533</v>
       </c>
@@ -39860,7 +39859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A560" s="29">
         <v>534</v>
       </c>
@@ -39913,7 +39912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A561" s="29">
         <v>535</v>
       </c>
@@ -39966,7 +39965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A562" s="29">
         <v>536</v>
       </c>
@@ -40019,7 +40018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A563" s="29">
         <v>537</v>
       </c>
@@ -40070,7 +40069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A564" s="29">
         <v>538</v>
       </c>
@@ -40121,7 +40120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A565" s="29">
         <v>539</v>
       </c>
@@ -40172,7 +40171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A566" s="29">
         <v>540</v>
       </c>
@@ -40223,7 +40222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A567" s="29">
         <v>543</v>
       </c>
@@ -40274,7 +40273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A568" s="29">
         <v>544</v>
       </c>
@@ -40327,7 +40326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A569" s="29">
         <v>550</v>
       </c>
@@ -40378,7 +40377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A570" s="29">
         <v>551</v>
       </c>
@@ -40429,7 +40428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A571" s="29">
         <v>554</v>
       </c>
@@ -40480,7 +40479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A572" s="29">
         <v>555</v>
       </c>
@@ -40531,7 +40530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A573" s="29">
         <v>510</v>
       </c>
@@ -40582,7 +40581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A574" s="29">
         <v>511</v>
       </c>
@@ -40633,7 +40632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A575" s="29">
         <v>513</v>
       </c>
@@ -40684,7 +40683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A576" s="29">
         <v>518</v>
       </c>
@@ -40735,7 +40734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A577" s="29">
         <v>526</v>
       </c>
@@ -40786,7 +40785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A578" s="29">
         <v>529</v>
       </c>
@@ -41034,7 +41033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A582" s="29">
         <v>967</v>
       </c>
@@ -41087,7 +41086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A583" s="29">
         <v>976</v>
       </c>
@@ -41140,7 +41139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A584" s="52">
         <v>978</v>
       </c>
@@ -41193,7 +41192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A585" s="29">
         <v>555</v>
       </c>
@@ -41244,7 +41243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A586" s="29">
         <v>969</v>
       </c>
@@ -41295,7 +41294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A587" s="29">
         <v>970</v>
       </c>
@@ -41346,7 +41345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A588" s="29">
         <v>972</v>
       </c>
@@ -41397,7 +41396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A589" s="29">
         <v>973</v>
       </c>
@@ -41448,7 +41447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A590" s="29">
         <v>800</v>
       </c>
@@ -41499,7 +41498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A591" s="29">
         <v>974</v>
       </c>
@@ -41550,7 +41549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A592" s="29">
         <v>975</v>
       </c>
@@ -41601,7 +41600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A593" s="4">
         <v>519</v>
       </c>
@@ -41662,7 +41661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A594" s="4">
         <v>977</v>
       </c>
@@ -41723,7 +41722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A595" s="4">
         <v>979</v>
       </c>
@@ -41786,13 +41785,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="20">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="215" priority="115"/>
   </conditionalFormatting>

--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2503" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9BD37E7-E6EF-4121-A1A7-423A05607C86}"/>
+  <xr:revisionPtr revIDLastSave="2508" documentId="13_ncr:1_{F0BBE5C6-CAE9-4853-BBB4-310E5D3E7ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{265A4E53-187F-43C5-AD3B-E7C804CC3B85}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6254,10 +6254,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -8227,7 +8223,7 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="4"/>
       <c r="Q28" s="4">
@@ -41785,6 +41781,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:W595" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A109">
     <cfRule type="duplicateValues" dxfId="215" priority="115"/>
   </conditionalFormatting>
@@ -76813,6 +76810,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -77047,27 +77064,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0065C2A-D54D-4F3D-A68A-F49590152888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -77084,23 +77100,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Indicadores por CMI.xlsx
+++ b/data/raw/Indicadores por CMI.xlsx
@@ -76810,15 +76810,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
@@ -76827,6 +76818,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77065,20 +77065,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F29CE81-ECA4-464A-90AD-CBCC4B67C9CD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
     <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A465C7F-6E2C-46F5-B371-BD23E458BF78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
